--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0021.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0021.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dùng 100 Cuộn Film để hồi phục 24 Cuộn Film.</t>
+          <t>Dùng 100 Cuộn Phim để hồi phục 24 Cuộn Phim.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dùng 100 Cuộn Film để tăng Cấp Đội lên 2.</t>
+          <t>Dùng 100 Cuộn Phim để tăng Cấp Đội lên 2.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Để lại và khôi phục 12 Cuộn Film</t>
+          <t>Để lại và khôi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội lên 1.</t>
+          <t>Tăng Cấp Đội lên 1.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Win the battle để tăng Cấp Đội lên 5</t>
+          <t>Chiến thắng trận đấu để tăng Cấp Đội lên 5</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dùng 200 Dream Fragments để tăng Cấp Đội thêm 8</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để tăng Cấp Đội thêm 8</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dùng 200 Dream Fragments để giảm 30% chi phí Cuộn Film và tăng tầm nhìn thêm 1</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để giảm 30% chi phí Cuộn Phim và tăng tầm nhìn thêm 1</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film</t>
+          <t>Hồi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Restore 0-24 Cuộn Film</t>
+          <t>Hồi phục 0-24 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Giảm tối đa Cuộn Film đi 30%, hồi phục toàn bộ Cuộn Film</t>
+          <t>Giảm tối đa Cuộn Phim đi 30%, hồi phục toàn bộ Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dùng 12 Cuộn Film để tăng Cấp Đội ngẫu nhiên từ 3-8.</t>
+          <t>Dùng 12 Cuộn Phim để tăng Cấp Đội ngẫu nhiên từ 3-8.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film</t>
+          <t>Hồi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Restore 24 Cuộn Film</t>
+          <t>Hồi phục 24 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội lên 5</t>
+          <t>Tăng Cấp Đội lên 5</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Dùng 200 Dream Fragments để tăng lượng Dream Fragments nhận được thêm 15%</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để tăng lượng Mảnh Giấc Mơ nhận được thêm 15%</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Dùng 200 Dream Fragments để tăng lượng Cuộn Film nhận được thêm 15%</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để tăng lượng Cuộn Phim nhận được thêm 15%</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Restore 12-24 Cuộn Film</t>
+          <t>Hồi phục 12-24 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội lên 3-8.</t>
+          <t>Tăng Cấp Đội lên 3-8.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Chiến thắng trận chiến khó để khôi phục 40 Cuộn Film</t>
+          <t>Chiến thắng trận chiến khó để khôi phục 40 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Dùng 24 Cuộn Film để tăng lượng Cuộn Film nhận được lên 50%</t>
+          <t>Dùng 24 Cuộn Phim để tăng lượng Cuộn Phim nhận được lên 50%</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Dùng 100 Dream Fragments để tăng Cấp Đội lên 5.</t>
+          <t>Dùng 100 Mảnh Giấc Mơ để tăng Cấp Đội lên 5.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chiến thắng trận chiến khó để khôi phục 24 Cuộn Film</t>
+          <t>Chiến thắng trận chiến khó để khôi phục 24 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Restore 24 Cuộn Film và tăng tầm nhìn thêm 1</t>
+          <t>Hồi phục 24 Cuộn Phim và tăng tầm nhìn thêm 1</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội lên 3.</t>
+          <t>Tăng Cấp Đội lên 3.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Nghỉ ngơi đi và hồi phục 24 Cuộn Film.</t>
+          <t>Nghỉ ngơi đi và hồi phục 24 Cuộn Phim.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>"Vì ta không thể thuyết phục được ngươi, nên ta chỉ yêu cầu một điều: đừng để sức mạnh nuốt chửng ngươi. Và đừng có dám chết trên chiến trường. Nếu ngươi làm vậy, ta sẽ coi đó là sự phản bội."</t>
+          <t>"Vì tao không thể thuyết phục được mày, nên tao chỉ yêu cầu một điều: đừng để sức mạnh nuốt chửng mày. Và đừng có dám chết trên chiến trường. Nếu mày làm vậy, tao sẽ coi đó là sự phản bội."</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Increase Cấp Đội.</t>
+          <t>Tăng Cấp Đội.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>"Tham gia Dự án Resonance! Trở thành lực lượng biến hình tinh nhuệ! Sở hữu sức mạnh kỳ lạ mới, và đánh đuổi lũ quái vật khốn kiếp khỏi quê hương chúng ta!"</t>
+          <t>"Tham gia Dự án Cộng Hưởng! Trở thành lực lượng biến hình tinh nhuệ! Sở hữu sức mạnh kỳ lạ mới, và đánh đuổi lũ quái vật khốn kiếp khỏi quê hương chúng ta!"</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Restore 12 Cuộn Film</t>
+          <t>Hồi phục 12 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Restore 40 Cuộn Film</t>
+          <t>Hồi phục 40 Cuộn Phim</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Cậu rút vũ khí đối đầu với con quái vật méo mó này (Tấn Công của cậu trong trận này tăng 20%).</t>
+          <t>Cậu rút vũ khí đối đầu với con quái vật méo mó này (ATK của cậu trong trận này tăng 20%).</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Một robot canh gác. (Tấn Công của bạn trong trận này tăng 20%.)</t>
+          <t>Một robot canh gác. (ATK của bạn trong trận này tăng 20%.)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>"Sau đó, Black Cat và Cat Trắng, đứng giữa đống hoang tàn, lại chia rẽ nhau. Liệu họ có nên, như Black Cat đề xuất, dùng đống đổ nát ấy làm chất dinh dưỡng cho những giấc mơ và gửi chúng qua cánh cổng? Hay, như Cat Trắng mong muốn, khôi phục lại tất cả những gì bên trong những giấc mơ đó?"</t>
+          <t>"Sau đó, Mèo Đen và Mèo Trắng, đứng giữa đống hoang tàn, lại chia rẽ nhau. Liệu họ có nên, như Mèo Đen đề xuất, dùng đống đổ nát ấy làm chất dinh dưỡng cho những giấc mơ và gửi chúng qua cánh cổng? Hay, như Mèo Trắng mong muốn, khôi phục lại tất cả những gì bên trong những giấc mơ đó?"</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>"Kết quả thí nghiệm đã được xác minh. Giả thuyết của chúng ta là đúng. *Nó* cũng có nguồn Resonance tương ứng... Nhưng chúng ta không ngờ nó lại ở nơi xa xôi đến vậy."</t>
+          <t>"Kết quả thí nghiệm đã được xác minh. Giả thuyết của chúng ta là đúng. *Nó* cũng có nguồn Cộng Hưởng tương ứng... Nhưng chúng ta không ngờ nó lại ở nơi xa xôi đến vậy."</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>"Nhưng càng chôn vùi bản thân như thế, càng đánh mất kết nối với thế giới thực. Rốt cuộc, mọi nghiên cứu về Resonance đều vì con người mà nó được tạo ra để giúp đỡ."</t>
+          <t>"Nhưng càng chôn vùi bản thân như thế, càng đánh mất kết nối với thế giới thực. Rốt cuộc, mọi nghiên cứu về Cộng Hưởng đều vì con người mà nó được tạo ra để giúp đỡ."</t>
         </is>
       </c>
     </row>
@@ -4417,9 +4417,9 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, gây Sát Thương Attack Phối Hợp sẽ kích hoạt các hiệu ứng sau, mỗi {0} giây một lần:
-Triệu hồi thêm một Đòn Đánh Từ Quỹ Đạo, gây Sát Thương Physical bằng {1} Attack khi trúng mục tiêu. Có {2} xác suất triệu hồi thêm một Đòn Đánh Từ Quỹ Đạo nữa, gây Sát Thương Physical bằng {3} Attack khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
+Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, gây Sát Thương ATK Phối Hợp sẽ kích hoạt các hiệu ứng sau, mỗi {0} giây một lần:
+Triệu hồi thêm một Đòn Đánh Từ Quỹ Đạo, gây Sát Thương Vật Lý bằng {1} ATK khi trúng mục tiêu. Có {2} xác suất triệu hồi thêm một Đòn Đánh Từ Quỹ Đạo nữa, gây Sát Thương Vật Lý bằng {3} ATK khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -4485,8 +4485,8 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, gây Sát Thương Attack Phối Hợp sẽ tung thêm một đòn tấn công gây Sát Thương Physical bằng {0} Attack, kích hoạt mỗi {1} giây một lần. Sát Thương từ Đòn Đánh Từ Quỹ Đạo được Khuếch Đại thêm {2}.</t>
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
+Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, gây Sát Thương ATK Phối Hợp sẽ tung thêm một đòn tấn công gây Sát Thương Vật Lý bằng {0} ATK, kích hoạt mỗi {1} giây một lần. Sát Thương từ Đòn Đánh Từ Quỹ Đạo được Khuếch Đại thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -4557,13 +4557,13 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
 Kích hoạt Cơn Bùng Nổ Đồng Điệu sẽ tung ra một chuỗi Tuyệt Kỹ Cổ Tích siêu hoành tráng theo thứ tự sau:
-- Summon &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; loạt đạn Cổ Vật {Cus:Sap,S=Barrage P=Barrages SapTag=0} gây Glacio DMG bằng {1} Tấn Công.
-- Summon {2} Dây Leo Ảo Khổng Lồ, mỗi dây gây tổng Spectro DMG bằng {3} Tấn Công và hồi {4} HP tối đa cho Synergy Giả đang hoạt động.
-- Summon {5} Xoáy Nightmare hút mục tiêu xung quanh. Mỗi Xoáy Nightmare tung ra {6} đòn tấn công, mỗi đòn gây Havoc DMG bằng {7} Tấn Công.
-- Summon Hỗn Chiến Cuồng Nhiệt {8} lần. Mỗi lần Hỗn Chiến tung ra {9} đòn tấn công, mỗi đòn gây Glacio DMG bằng {10} Tấn Công.
-- Summon {11} đợt Đòn Đánh Chiến Binh, mỗi đợt gây tổng Fusion DMG bằng {12} Tấn Công.</t>
+- Triệu hồi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; loạt đạn Cổ Vật {Cus:Sap,S=Barrage P=Barrages SapTag=0} gây Sát Thương Glacio bằng {1} ATK.
+- Triệu hồi {2} Dây Leo Ảo Khổng Lồ, mỗi dây gây tổng Sát Thương Spectro bằng {3} ATK và hồi {4} HP tối đa cho Resonator đang hoạt động.
+- Triệu hồi {5} Xoáy Ác Mộng hút mục tiêu xung quanh. Mỗi Xoáy Ác Mộng tung ra {6} đòn tấn công, mỗi đòn gây Sát Thương Havoc bằng {7} ATK.
+- Triệu hồi Hỗn Chiến Cuồng Nhiệt {8} lần. Mỗi lần Hỗn Chiến tung ra {9} đòn tấn công, mỗi đòn gây Sát Thương Glacio bằng {10} ATK.
+- Triệu hồi {11} đợt Đòn Đánh Chiến Binh, mỗi đợt gây tổng Sát Thương Fusion bằng {12} ATK.</t>
         </is>
       </c>
     </row>
@@ -4629,8 +4629,8 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, Sát Thương gây ra bởi tất cả Synergy Giả trong đội sẽ được Khuếch Đại thêm {0}.</t>
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
+Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, Sát Thương gây ra bởi tất cả Resonator trong đội sẽ được Khuếch Đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -4697,9 +4697,9 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Kích hoạt khi có &lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>Kích hoạt khi có &lt;color=Highlight&gt;3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi ở trạng thái Đồng Bộ Bùng Nổ:
-Synergy Giả ở trên không sẽ nhận được 1 lớp Vũ Điệu Không Trung mỗi {0} giây, kéo dài {1} giây. Mỗi lớp tăng Crit. Rate thêm {2}, tối đa {3} lớp. Attack trên không sẽ triệu hồi Đất Cháy, gây sát thương bằng {4} Attack, kích hoạt mỗi {5} giây một lần.</t>
+Resonator ở trên không sẽ nhận được 1 lớp Vũ Điệu Không Trung mỗi {0} giây, kéo dài {1} giây. Mỗi lớp tăng Crit. Rate thêm {2}, tối đa {3} lớp. ATK trên không sẽ triệu hồi Đất Cháy, gây DMG bằng {4} ATK, kích hoạt mỗi {5} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -4766,9 +4766,9 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-ATK tăng 60%. Scorched Earth gây thêm Burn lên mục tiêu trong 6 giây, mỗi giây gây DMG bằng 100% ATK.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+ATK tăng thêm 60%. Đất Cháy còn gây hiệu ứng Bỏng lên mục tiêu trong 6 giây, mỗi giây gây DMG bằng 100% ATK.</t>
         </is>
       </c>
     </row>
@@ -4837,11 +4837,11 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-- Resonators nhận thêm {0} điểm Shield và tung chiêu Wall Breaker một lần khi kích hoạt Synergy Burst.
-- Wall Breaker: Gây DMG bằng {1} điểm Shield hiện tại lên mục tiêu và nhận Shield dựa trên {2} HP tối đa khi trúng đích.
-- Tự động tung chiêu Wall Breaker mỗi {3}.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+- Resonator nhận thêm {0} điểm Khiên và tung đòn Phá Tường một lần khi kích hoạt Đồng Bộ Bùng Nổ.
+- Phá Tường: Gây DMG bằng {1} số điểm Khiên hiện tại lên mục tiêu và nhận Khiên dựa trên {2} HP tối đa khi trúng đích.
+- Tự động tung đòn Phá Tường mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -4908,9 +4908,9 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-DMG gây bởi Wall Breaker được Khuếch Đại thêm {0}. Wall Breaker khi trúng mục tiêu sẽ tạo thêm một Lớp Shield dựa trên {1} ATK và một Lớp Shield khác dựa trên {2} DEF.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+DMG gây ra bởi Phá Tường được Khuếch Đại thêm {0}. Khi trúng đích, Phá Tường còn tạo thêm Khiên dựa trên {1} ATK và một lớp Khiên khác dựa trên {2} Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -4979,11 +4979,11 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated if the team's active Resonator is Rover&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt nếu Resonator đang hoạt động trong đội là Rover&lt;/color&gt;
 - Khi Concerto Energy đạt tối đa, tự động triệu hồi các Phantom Rover thuộc các Thuộc Tính khác để tung ra một loạt đòn tấn công, tiêu hao toàn bộ Concerto Energy.
- - Phantom Rover: Spectro tung 5 đòn tấn công liên tiếp, gây Spectro DMG bằng {0} Tấn Công tổng cộng. Mỗi đòn gây &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Spectro Frazzle và kích hoạt ngay Sát Thương từ lượng Spectro Frazzle đã tích lũy.
-- Phantom Rover: Havoc tung 11 đòn tấn công liên tiếp, gây Havoc DMG bằng {2} Tấn Công tổng cộng. Mỗi đòn tăng &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Strength. Mỗi tầng Strength tăng Crit. DMG thêm {4} trong {5} giây, tối đa {6} tầng.
-- Phantom Rover: Aero tung 7 đòn tấn công liên tiếp, gây Aero DMG bằng {7} Tấn Công tổng cộng. Mỗi đòn gây &lt;SapTag=8&gt;{8}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Aero Erosion và kích hoạt ngay Sát Thương từ lượng Aero Erosion đã tích lũy.</t>
+ - Phantom Rover: Spectro tung 5 đòn tấn công liên tiếp, gây Sát Thương Spectro bằng {0} ATK tổng cộng. Mỗi đòn gây &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Spectro Frazzle và kích hoạt ngay Sát Thương từ lượng Spectro Frazzle đã tích lũy.
+- Phantom Rover: Havoc tung 11 đòn tấn công liên tiếp, gây Sát Thương Havoc bằng {2} ATK tổng cộng. Mỗi đòn tăng &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Strength. Mỗi tầng Strength tăng Crit. DMG thêm {4} trong {5} giây, tối đa {6} tầng.
+- Phantom Rover: Aero tung 7 đòn tấn công liên tiếp, gây Sát Thương Aero bằng {7} ATK tổng cộng. Mỗi đòn gây &lt;SapTag=8&gt;{8}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Aero Erosion và kích hoạt ngay Sát Thương từ lượng Aero Erosion đã tích lũy.</t>
         </is>
       </c>
     </row>
@@ -5052,11 +5052,11 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated if the team's active Resonator is Rover&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt nếu Resonator đang hoạt động trong đội là Rover&lt;/color&gt;
 Rover nhận các hiệu ứng thưởng đặc trưng theo Thuộc Tính:
-- Rover: Spectro: Khi đánh trúng mục tiêu bằng Basic Attack, gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Spectro Frazzle, kích hoạt mỗi {1} giây một lần. Crit. DMG của Rover tăng {2} mỗi khi mục tiêu chịu Sát Thương từ Status Tiêu Cực, tối đa {3} tầng.
-- Rover: Havoc: Giảm Cooldown chiêu của Resonance Skill đi {4}. Sát Thương gây ra bởi Resonance Skill của Rover hồi phục HP bằng {5} Attack, kích hoạt mỗi {6} giây một lần.
-- Rover: Aero: Increase Crit. DMG thêm {7} khi Rover ở trên không.</t>
+- Rover: Spectro: Khi đánh trúng mục tiêu bằng Đòn Cơ Bản, gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Spectro Frazzle, kích hoạt mỗi {1} giây một lần. Crit. DMG của Rover tăng {2} mỗi khi mục tiêu chịu Sát Thương từ Trạng Thái Tiêu Cực, tối đa {3} tầng.
+- Rover: Havoc: Giảm thời gian hồi chiêu của Resonance Skill đi {4}. Sát Thương gây ra bởi Resonance Skill của Rover hồi phục HP bằng {5} ATK, kích hoạt mỗi {6} giây một lần.
+- Rover: Aero: Tăng Crit. DMG thêm {7} khi Rover ở trên không.</t>
         </is>
       </c>
     </row>
@@ -5125,9 +5125,9 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>&lt;color=Highlight&gt;Kích hoạt nếu Resonator đang hoạt động trong đội là Rover&lt;/color&gt;
-- Nếu Rover không thuộc thuộc tính Spectro: Gây sát thương Basic Attack lên mục tiêu &lt;color=Highlight&gt;{0}&lt;/color&gt; lần sẽ triệu hồi Phantom Rover: Spectro để tung ra 1 đợt tấn công. Mỗi đợt gây Spectro DMG bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; Attack.
-- Nếu Rover không thuộc thuộc tính Havoc: Gây sát thương Resonance Skill lên mục tiêu &lt;color=Highlight&gt;{2}&lt;/color&gt; lần sẽ triệu hồi Phantom Rover: Havoc để tung ra 1 đợt tấn công. Mỗi đợt gây Havoc DMG bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; Attack.
-- Nếu Rover không thuộc thuộc tính Aero: Gây sát thương Heavy Attack lên mục tiêu &lt;color=Highlight&gt;{4}&lt;/color&gt; lần sẽ triệu hồi Phantom Rover: Aero để tung ra 1 đợt tấn công. Mỗi đợt gây Aero DMG bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; Attack.</t>
+- Nếu Rover không thuộc thuộc tính Spectro: Gây DMG Đòn Basic Attack lên mục tiêu &lt;color=Highlight&gt;{0}&lt;/color&gt; lần sẽ triệu hồi Phantom Rover: Spectro để tung ra 1 đợt tấn công. Mỗi đợt gây DMG Spectro bằng &lt;color=Highlight&gt;{1}&lt;/color&gt; ATK.
+- Nếu Rover không thuộc thuộc tính Havoc: Gây DMG Resonance Skill lên mục tiêu &lt;color=Highlight&gt;{2}&lt;/color&gt; lần sẽ triệu hồi Phantom Rover: Havoc để tung ra 1 đợt tấn công. Mỗi đợt gây DMG Havoc bằng &lt;color=Highlight&gt;{3}&lt;/color&gt; ATK.
+- Nếu Rover không thuộc thuộc tính Aero: Gây DMG Đòn Heavy Attack lên mục tiêu &lt;color=Highlight&gt;{4}&lt;/color&gt; lần sẽ triệu hồi Phantom Rover: Aero để tung ra 1 đợt tấn công. Mỗi đợt gây DMG Aero bằng &lt;color=Highlight&gt;{5}&lt;/color&gt; ATK.</t>
         </is>
       </c>
     </row>
@@ -5193,8 +5193,8 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated if the team's active Resonator is Rover&lt;/color&gt;
-Khi sử dụng Resonance Liberation, triệu hồi các Phantom Rover thuộc các Thuộc Tính khác để thi triển Resonance Liberation của chúng, mỗi lần gây Sát Thương bằng {0} Tấn Công. Hiệu ứng này kích hoạt mỗi {1} giây một lần.</t>
+          <t>&lt;color=Highlight&gt;Kích hoạt nếu Resonator đang hoạt động trong đội là Rover&lt;/color&gt;
+Khi sử dụng Resonance Liberation, triệu hồi các Phantom Rover thuộc các Thuộc Tính khác để thi triển Resonance Liberation của chúng, mỗi lần gây Sát Thương bằng {0} ATK. Hiệu ứng này kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -5261,9 +5261,9 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated if there is only Rover in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt nếu đội chỉ có Rover&lt;/color&gt;
 - Khi bắt đầu Synergy Burst, gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Spectro Frazzle và &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S= tầng P= tầng} Aero Erosion. Sau đó, ngay lập tức kích hoạt Sát Thương từ toàn bộ Spectro Frazzle và Aero Erosion đã tích lũy &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S= lần P= lần}.
- - Trong Synergy Burst, mỗi khi Rover gây Sát Thương, gây thêm Havoc DMG bằng {3} Tấn Công một lần, kích hoạt mỗi {4} giây một lần.</t>
+ - Trong Synergy Burst, mỗi khi Rover gây Sát Thương, gây thêm Sát Thương Havoc bằng {3} ATK một lần, kích hoạt mỗi {4} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -5330,9 +5330,9 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated if there is only Rover in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt nếu đội chỉ có Rover&lt;/color&gt;
 Khi trong Synergy Burst:
-Increase Crit. Rate thêm {0}. Mỗi khi Rover gây Sát Thương, gây thêm Spectro DMG bằng {1} Tấn Công và Aero DMG bằng {2} Tấn Công một lần, kích hoạt mỗi {3} giây một lần.</t>
+Tăng Crit. Rate thêm {0}. Mỗi khi Rover gây Sát Thương, gây thêm Sát Thương Spectro bằng {1} ATK và Sát Thương Aero bằng {2} ATK một lần, kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -5399,9 +5399,9 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
 - Khôi phục ngay lập tức {0} HP tối đa khi kích hoạt Cơn Bùng Nổ Đồng Điệu.
-- Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, Synergy Giả đang hoạt động nhận thêm {1} Hiệu Quả Healing và khôi phục {3} HP tối đa mỗi {2} giây.</t>
+- Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, Resonator đang hoạt động nhận thêm {1} Hiệu Quả Hồi Phục và khôi phục {3} HP tối đa mỗi {2} giây.</t>
         </is>
       </c>
     </row>
@@ -5468,9 +5468,9 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-- Khi kích hoạt Synergy Burst, hồi phục thêm {0} HP tối đa. Khi trong Synergy Burst, nhận thêm {1} Hiệu Quả Chữa Trị và hồi phục thêm {3} HP tối đa mỗi {2} giây cho Synergy Giả đang hoạt động.
-- Khi trong Synergy Burst, Cooldown chiêu của Kỹ Năng Synergy giảm {4}.</t>
+          <t>&lt;color=Highlight&gt;Kích hoạt khi đội có 3 Thành Viên Liên Kết&lt;/color&gt;
+- Khi kích hoạt Synergy Burst, hồi phục thêm {0} HP tối đa. Khi trong Synergy Burst, nhận thêm {1} Hiệu Quả Chữa Trị và hồi phục thêm {3} HP tối đa mỗi {2} giây cho Resonator đang hoạt động.
+- Khi trong Synergy Burst, Thời gian hồi chiêu của Resonance Skill giảm {4}.</t>
         </is>
       </c>
     </row>
@@ -5539,11 +5539,11 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-- Resonators nhận thêm Wage mỗi {0} giây.
-- Một tầng Allowance bổ sung được đặt lên tất cả mục tiêu trong phạm vi mỗi {1} giây.
-- DMG gây bởi Wage và Reimbursement được Khuếch đại thêm {2}.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+- Resonator nhận thêm Lương mỗi {0} giây.
+- Mỗi {1} giây, một lớp Trợ Cấp được đặt lên tất cả mục tiêu trong phạm vi.
+- DMG gây ra bởi Lương và Hoàn Trả được Khuếch Đại thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -5610,9 +5610,9 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Kích hoạt khi có &lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>Kích hoạt khi có &lt;color=Highlight&gt;3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi ở trạng thái Đồng Bộ Bùng Nổ:
-Gây sát thương bằng Kiếm Lại sẽ áp dụng &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp Hiệu Ứng Thời Gian} Overtime lên mục tiêu, tối đa {1} lớp. Khi Synergy Giả rời khỏi trạng thái Đồng Bộ Bùng Nổ, tất cả lớp Hiệu Ứng Thời Gian trên mục tiêu gần đó sẽ bị xóa, mỗi lần xóa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần} sẽ kích hoạt thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần} Kiếm Lại lên mục tiêu.</t>
+Gây sát thương bằng Kiếm Lại sẽ áp dụng &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp Hiệu Ứng Thời Gian} Overtime lên mục tiêu, tối đa {1} lớp. Khi Resonator rời khỏi trạng thái Đồng Bộ Bùng Nổ, tất cả lớp Hiệu Ứng Thời Gian trên mục tiêu gần đó sẽ bị xóa, mỗi lần xóa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần} sẽ kích hoạt thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần} Kiếm Lại lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -5680,10 +5680,10 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-- Resonators đang hoạt động nhận Power Boost, tăng ATK/Max HP/DEF/Crit. Rate/Crit. DMG tương đương {0} tổng ATK/Max HP/DEF/Crit. Rate/Crit. DMG của tất cả Resonators không có mặt trên chiến trường.
-- Khi Resonators gây sát thương, họ sẽ gây thêm Physical DMG tương đương {1} ATK, kích hoạt mỗi {2} giây một lần.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+- Resonator đang hoạt động nhận Hiệu Ứng Tăng Sức, tăng ATK/HP tối đa/Phòng Ngự/Crit. Rate/Crit. DMG bằng {0} tổng ATK/HP tối đa/Phòng Ngự/Crit. Rate/Crit. DMG của tất cả Resonator không có mặt trên chiến trường.
+- Khi Resonator gây DMG, họ sẽ gây thêm DMG Vật Lý bằng {1} ATK, kích hoạt mỗi {2} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -5752,10 +5752,10 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu:
-- Tăng Cường Sức Mạnh giờ đây tăng chỉ số thêm {1} tổng Tấn Công/HP tối đa/Phòng Ngự/Crit. Rate/Crit. DMG của tất cả Synergy Giả không có mặt trên chiến trường thay vì {0}.
-- Khi một Synergy Giả gây sát thương, họ sẽ gây thêm Sát Thương Physical bằng {2} Tấn Công, kích hoạt mỗi {3} giây một lần.
+- Tăng Cường Sức Mạnh giờ đây tăng chỉ số thêm {1} tổng ATK/HP tối đa/Phòng Ngự/Crit. Rate/Crit. DMG của tất cả Resonator không có mặt trên chiến trường thay vì {0}.
+- Khi một Resonator gây DMG, họ sẽ gây thêm Sát Thương Vật Lý bằng {2} ATK, kích hoạt mỗi {3} giây một lần.
 - Tăng Cường Sức Mạnh vẫn duy trì thêm {4} giây sau khi Cơn Bùng Nổ Đồng Điệu kết thúc.</t>
         </is>
       </c>
@@ -5823,9 +5823,9 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt khi đội có 3 Thành Viên Liên Kết&lt;/color&gt;
 - Giảm {0} Phòng Ngự của tất cả mục tiêu.
-- Khi kích hoạt Synergy Burst, triệu hồi nhiều Otherworld Thunders tấn công mục tiêu, mỗi đòn gây Sát Thương Physical bằng {1} Tấn Công, được tính là Sát Thương Kỹ Năng Synergy.</t>
+- Khi kích hoạt Synergy Burst, triệu hồi nhiều Otherworld Thunders tấn công mục tiêu, mỗi đòn gây Sát Thương Vật Lý bằng {1} ATK, được tính là Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -5891,8 +5891,8 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi thoát khỏi Cơn Bùng Nổ Đồng Điệu, triệu hồi một Thunder Tận Thế khổng lồ gây Sát Thương Physical bằng {0} Tấn Công lên mục tiêu, được tính là Sát Thương Kỹ Năng Synergy.</t>
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
+Khi thoát khỏi Cơn Bùng Nổ Đồng Điệu, triệu hồi một Sấm Sét Tận Thế khổng lồ gây Sát Thương Vật Lý bằng {0} ATK lên mục tiêu, được tính là Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -5959,9 +5959,9 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Kích hoạt khi có &lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>Kích hoạt khi có &lt;color=Highlight&gt;3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi ở trạng thái Đồng Bộ Bùng Nổ:
-Summon Dòng Chảy Sụp Đổ liên tục hút mục tiêu gần đó, gây sát thương Physical bằng {1} Tấn Công {0} times. Khi hiệu ứng hút kết thúc, kích hoạt {2} Sụp Đổ, gây sát thương Physical bằng {3} Tấn Công. Sau đó triệu hồi {4} Cổng Data tấn công mục tiêu liên tục. Mỗi Cổng Data phóng {5} Quả Bom Data vào mục tiêu, mỗi quả gây sát thương bằng {6} Tấn Công.</t>
+Triệu hồi Dòng Chảy Sụp Đổ liên tục hút mục tiêu gần đó, gây DMG Vật Lý bằng {1} ATK {0} lần. Khi hiệu ứng hút kết thúc, kích hoạt {2} Sụp Đổ, gây DMG Vật Lý bằng {3} ATK. Sau đó triệu hồi {4} Cổng Dữ Liệu tấn công mục tiêu liên tục. Mỗi Cổng Dữ Liệu phóng {5} Quả Bom Dữ Liệu vào mục tiêu, mỗi quả gây DMG bằng {6} ATK.</t>
         </is>
       </c>
     </row>
@@ -6028,9 +6028,9 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi trong trạng thái Đồng Điệu Tăng Cường:
-Mỗi lần Quả Bom Data trúng mục tiêu, Phòng Ngự của mục tiêu sẽ bị giảm {0} trong {2} giây, tối đa chồng chất {1} lần.</t>
+Mỗi lần Quả Bom Dữ Liệu trúng mục tiêu, Phòng Ngự của mục tiêu sẽ bị giảm {0} trong {2} giây, tối đa chồng chất {1} lần.</t>
         </is>
       </c>
     </row>
@@ -6098,10 +6098,10 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-Sử dụng Resonance Skill, Resonance Liberation, Dodge Counter và Dodge thành công sẽ nhận thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=0} Rebel's Flag, kích hoạt mỗi {1} giây.
-Khi Fool's Cannon gây DMG, triệu hồi Fool's Wave thực hiện {2} đòn tấn công, mỗi đòn gây Physical DMG bằng {3} ATK. Cooldown của Resonance Skill giảm {4}. Phục hồi {5} Resonance Energy.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+Kích hoạt Resonance Skill, Giải Cứu Cộng Hưởng, Dodge Counter hoặc né thành công sẽ nhận thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; lớp Cờ Nổi Loạn, kích hoạt mỗi {1} giây một lần.
+Khi Pháo Dại gây DMG, triệu hồi Sóng Dại phóng {2} đòn tấn công, mỗi đòn gây DMG Vật Lý bằng {3} ATK. Thời gian hồi chiêu Resonance Skill giảm {4}. Phục hồi {5} Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -6168,9 +6168,9 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Kích hoạt khi có &lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>Kích hoạt khi có &lt;color=Highlight&gt;3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi ở trạng thái Đồng Bộ Bùng Nổ:
-Sát thương gây ra bởi Pháo Đài Ngu Ngốc và Sóng Ngu Ngốc được Khuếch Đại thêm {0}. Sử dụng Kỹ Năng Synergy, Giải Phóng Synergy, Dodge Counter và Dodge thành công sẽ nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} Cờ Nổi Loạn, kích hoạt mỗi {2} giây một lần.</t>
+DMG gây ra bởi Pháo Đài Ngu Ngốc và Sóng Ngu Ngốc được Khuếch Đại thêm {0}. Sử dụng Resonance Skill, Resonance Liberation, Dodge Counter Tránh và Né Tránh thành công sẽ nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp} Cờ Nổi Loạn, kích hoạt mỗi {2} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack được khuếch đại thêm {0}.</t>
+          <t>DMG Basic Attack được khuếch đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -6302,9 +6302,9 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng Basic Attack và Heavy Attack sẽ nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Ẩn Mình, kích hoạt mỗi {1} giây một lần.
-Dodge thành công sẽ nhận được &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=2} Ẩn Mình, kích hoạt mỗi {3} giây một lần.
-Đạt &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=4} Ẩn Mình sẽ tiêu hao toàn bộ để thi triển Bóp Chặt, gây Sát Thương Physical bằng {6} Attack &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=5} khi Basic Attack hoặc Heavy Attack tiếp theo trúng mục tiêu hoặc khi thực hiện Dodge Counter.</t>
+          <t>ATK mục tiêu bằng Đòn Cơ Bản và Đòn Nặng sẽ nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Ẩn Mình, kích hoạt mỗi {1} giây một lần.
+Né thành công sẽ nhận được &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=2} Ẩn Mình, kích hoạt mỗi {3} giây một lần.
+Đạt &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=4} Ẩn Mình sẽ tiêu hao toàn bộ để thi triển Bóp Chặt, gây Sát Thương Vật Lý bằng {6} ATK &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=5} khi Đòn Cơ Bản hoặc Đòn Nặng tiếp theo trúng mục tiêu hoặc khi thực hiện Dodge Counter.</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Basic Attack, Heavy Attack hoặc Dodge thành công sẽ nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=cấp P=cấp SapTag=0} Tàng Hình.</t>
+          <t>Đánh trúng mục tiêu bằng Đòn Cơ Bản, Đòn Nặng hoặc né tránh thành công sẽ nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=cấp P=cấp SapTag=0} Tàng Hình.</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Hệ số sát thương của Clench tăng lên {0} Tấn Công. Kích hoạt Clench sẽ tạo khiên tương đương {1} HP tối đa và miễn nhiễm gián đoạn trong {2} giây.</t>
+          <t>Hệ số DMG của Clench tăng lên {0} ATK. Kích hoạt Clench sẽ tạo khiên tương đương {1} HP tối đa và miễn nhiễm gián đoạn trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Gây sát thương sẽ nhận 1 tầng Võ Nghệ sau mỗi {3} giây, mỗi tầng tăng Tấn Công lên {0} trong {2} giây, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; tầng.</t>
+          <t>Gây sát thương sẽ nhận 1 tầng Võ Nghệ sau mỗi {3} giây, mỗi tầng tăng ATK lên {0} trong {2} giây, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -6568,9 +6568,9 @@
       <c r="M92" t="inlineStr">
         <is>
           <t>Sử dụng các chiêu thức võ học khác nhau tấn công mục tiêu! Mỗi {0} giây, hiệu ứng Thế Thủ Uyên Thâm sẽ thay đổi lần lượt như sau:
-- Resonance Lôi Hỏa: Khi gây sát thương bằng Basic Attack/Heavy Attack/Resonance Skill/Resonance Liberation, thêm Fusion DMG bằng {1} Attack và Electro DMG bằng {2} Attack, kích hoạt mỗi {3} giây một lần.
-- Hội Tụ Light và Bóng Tối: Khi gây sát thương bằng Basic Attack/Heavy Attack/Resonance Skill/Resonance Liberation, thêm Spectro DMG bằng {4} Attack và Havoc DMG bằng {5} Attack, kích hoạt mỗi {6} giây một lần.
-- Attack Phong Băng: Khi gây sát thương bằng Basic Attack/Heavy Attack/Resonance Skill/Resonance Liberation, thêm Aero DMG bằng {7} Attack và Glacio DMG bằng {8} Attack, kích hoạt mỗi {9} giây một lần.</t>
+- Cộng Hưởng Lôi Hỏa: Khi gây DMG bằng Đòn Cơ Bản/Đòn Nặng/Resonance Skill/Resonance Liberation, thêm DMG Fusion bằng {1} ATK và DMG Electro bằng {2} ATK, kích hoạt mỗi {3} giây một lần.
+- Hội Tụ Ánh Sáng và Bóng Tối: Khi gây DMG bằng Đòn Cơ Bản/Đòn Nặng/Resonance Skill/Resonance Liberation, thêm DMG Spectro bằng {4} ATK và DMG Havoc bằng {5} ATK, kích hoạt mỗi {6} giây một lần.
+- ATK Phong Băng: Khi gây DMG bằng Đòn Cơ Bản/Đòn Nặng/Resonance Skill/Resonance Liberation, thêm DMG Aero bằng {7} ATK và DMG Glacio bằng {8} ATK, kích hoạt mỗi {9} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Mỗi điểm Võ Thuật giờ đây sẽ tăng {0} Tấn Công.</t>
+          <t>Mỗi điểm Võ Thuật giờ đây sẽ tăng {0} ATK.</t>
         </is>
       </c>
     </row>
@@ -6702,9 +6702,9 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-Sau khi gây hiệu ứng Negative Status &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0} lên mục tiêu, triệu hồi 1 Kiếm Thần Thánh, gây Aero DMG bằng {1} ATK lên các mục tiêu lân cận.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+Sau khi gây hiệu ứng Trạng Thái Tiêu Cực &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; lần lên mục tiêu, triệu hồi 1 Kiếm Thần Thánh, gây DMG Aero bằng {1} ATK lên các mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -6771,9 +6771,9 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Kích hoạt khi có &lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>Kích hoạt khi có &lt;color=Highlight&gt;3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi ở trạng thái Đồng Bộ Bùng Nổ:
-Triệu hồi Kiếm Thần Thánh sẽ tăng {0} Sát Thương cho tất cả Synergy Giả trong đội trong {1} giây, tối đa {2} lớp.</t>
+Triệu hồi Kiếm Thần Thánh sẽ tăng {0} Sát Thương cho tất cả Resonator trong đội trong {1} giây, tối đa {2} lớp.</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Tất cả Resonators nhận Hiệu Ứng Đồng Quy: Gây Sát Thương bằng Basic Attack, Tấn Công Nặng, Resonance Skill và Resonance Liberation sẽ áp đặt &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=0} Erosion Aero và &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Spectro Frazzle, kích hoạt mỗi {2} giây một lần.</t>
+          <t>Tất cả Resonator nhận Hiệu Ứng Đồng Quy: Gây Sát Thương bằng ATK Cơ Bản, ATK Nặng, Resonance Skill và Resonance Liberation sẽ áp đặt &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=0} Xói Mòn Aero và &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=1} Rối Loạn Spectro, kích hoạt mỗi {2} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Sau khi gây hiệu ứng Erosion Gió hoặc Nhiễu Loạn Quang &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0}, triệu hồi Kiếm Bão &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} tấn công mục tiêu xung quanh. Mỗi Kiếm Bão gây Sát Thương Gió bằng {2} Tấn Công và gây &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S= tầng P=tầng SapTag=3} Erosion Gió cùng &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=4} Nhiễu Loạn Quang.</t>
+          <t>Sau khi gây hiệu ứng Aero Erosion hoặc Nhiễu Loạn Quang &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=0}, triệu hồi Kiếm Bão &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} tấn công mục tiêu xung quanh. Mỗi Kiếm Bão gây Sát Thương Gió bằng {2} ATK và gây &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S= tầng P=tầng SapTag=3} Aero Erosion cùng &lt;SapTag=4&gt;{4}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=4} Nhiễu Loạn Quang.</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Xóa khoảng thời gian gây hiệu ứng trạng thái tiêu cực của Collinearity. Khi gây Aero Erosion hoặc Spectro Frazzle lên mục tiêu, toàn bộ Resonators trong đội nhận thêm {0} Sát Thương trong {1} giây, tối đa cộng dồn {2} lần.</t>
+          <t>Xóa khoảng thời gian gây hiệu ứng trạng thái tiêu cực của Collinearity. Khi gây Aero Erosion hoặc Spectro Frazzle lên mục tiêu, toàn bộ Resonator trong đội nhận thêm {0} Sát Thương trong {1} giây, tối đa cộng dồn {2} lần.</t>
         </is>
       </c>
     </row>
@@ -7035,9 +7035,9 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-Sử dụng Resonance Liberation sẽ triệu hồi một Quả Lựu Đạn Tên Lửa gây Fusion DMG bằng {0} ATK lên các mục tiêu lân cận.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+Kích hoạt Giải Cứu Cộng Hưởng sẽ triệu hồi một Quả Lựu Đạn Tên Lửa, gây DMG Fusion bằng {0} ATK lên các mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -7104,9 +7104,9 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Kích hoạt khi có &lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>Kích hoạt khi có &lt;color=Highlight&gt;3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi ở trạng thái Đồng Bộ Bùng Nổ:
-Cooldown chiêu Giải Phóng Synergy giảm {0}. Synergy Giả ngay lập tức hồi lại toàn bộ Năng Lượng Synergy khi sử dụng Giải Phóng Synergy.</t>
+Thời gian hồi chiêu Resonance Liberation giảm {0}. Resonator ngay lập tức hồi lại toàn bộ Resonance Energy khi sử dụng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation bỏ qua {0} Phòng Ngự của mục tiêu.</t>
+          <t>DMG Resonance Liberation bỏ qua {0} Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ xóa Cooldown chiêu của Resonance Liberation tiếp theo và phục hồi toàn bộ Resonance Energy, kích hoạt mỗi {0} giây một lần.</t>
+          <t>Kích hoạt Resonance Liberation sẽ xóa thời gian hồi chiêu của Resonance Liberation tiếp theo và phục hồi toàn bộ Resonance Energy, kích hoạt mỗi {0} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Tấn Công {0} trong {1} giây, tối đa cộng dồn {2} lần.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng ATK {0} trong {1} giây, tối đa cộng dồn {2} lần.</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Tấn Công%</t>
+          <t>ATK%</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>PHÒNG NGỤ</t>
+          <t>DEF</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Spectro DMG Bonus</t>
+          <t>Thêm Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Havoc DMG Bonus</t>
+          <t>Tăng Sát Thương Havoc</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Fusion DMG Bonus</t>
+          <t>Thêm Sát Thương Hợp Thể</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Glacio DMG Bonus</t>
+          <t>Thêm Sát Thương Băng giá</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Aero DMG Bonus</t>
+          <t>Tăng Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Electro DMG Bonus</t>
+          <t>Thêm Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Tăng DMG Chung</t>
+          <t>Tăng Sát Thương Tổng Hợp</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Tăng Sát thương Basic Attack</t>
+          <t>Tăng DMG Basic Attack</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Cộng Dồn Sát Thương Heavy Attack</t>
+          <t>Cộng Dồn Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Intro Skill DMG Bonus</t>
+          <t>Tăng Sát Thương Kỹ Năng Khởi Động</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Giảm DMG Chung</t>
+          <t>Giảm Sát Thương Tổng Hợp</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Khuếch đại DMG</t>
+          <t>Khuếch Đại Sát Thương</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>STA Tối Đa+</t>
+          <t>STA tối đa+</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;1&lt;/color&gt; bẫy nổ sẽ xuất hiện tại vị trí của Resonator đang hoạt động sau mỗi &lt;color=#b72924ff&gt;10s&lt;/color&gt;. Nó sẽ phát nổ sau &lt;color=#b72924ff&gt;3s&lt;/color&gt; và gây sát thương bằng &lt;color=#b72924ff&gt;20% of their Max HP&lt;/color&gt; của mục tiêu bên trong.</t>
+          <t>&lt;color=#b72924ff&gt;1&lt;/color&gt; bẫy nổ sẽ xuất hiện tại vị trí của Resonator đang hoạt động sau mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt;. Nó sẽ phát nổ sau &lt;color=#b72924ff&gt;3 giây&lt;/color&gt; và gây DMG bằng &lt;color=#b72924ff&gt;20% HP tối đa&lt;/color&gt; của mục tiêu bên trong.</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ tiêu hao &lt;color=#b72924ff&gt;15% of the Resonator's current HP&lt;/color&gt; và giảm &lt;color=#5cc96aff&gt;cooldown by 50%&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần cho mỗi Resonator.</t>
+          <t>Kích hoạt Resonance Skill sẽ tiêu hao &lt;color=#b72924ff&gt;15% HP hiện tại của Resonator&lt;/color&gt; và giảm &lt;color=#5cc96aff&gt;50% thời gian hồi chiêu Resonance Skill&lt;/color&gt;. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần cho mỗi Resonator.</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Resonance Skill &lt;color=#b72924ff&gt;thời gian Cooldown tăng 50%&lt;/color&gt;.</t>
+          <t>Resonance Skill &lt;color=#b72924ff&gt;thời gian hồi chiêu tăng 50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9057,8 +9057,8 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;ATK is increased by 10%&lt;/color&gt;. Hiệu ứng có thể chồng chất.
-&lt;color=#5cc96aff&gt;Defeating an enemy&lt;/color&gt; sẽ ban cho Resonators gần đó trong đội &lt;color=#5cc96aff&gt;80% DMG Bonus&lt;/color&gt; trong &lt;color=#5cc96aff&gt;5&lt;/color&gt; giây.</t>
+          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;ATK của Queen of the Night tăng 10%&lt;/color&gt;. Hiệu ứng có thể chồng chất.
+&lt;color=#5cc96aff&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ ban cho các Resonator gần đó trong đội &lt;color=#5cc96aff&gt;thêm 80% Sát Thương&lt;/color&gt; trong &lt;color=#5cc96aff&gt;5&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -9124,8 +9124,8 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;DEF is increased by 10%&lt;/color&gt;. Hiệu ứng có thể chồng chất.
-&lt;color=#5cc96aff&gt;Defeating an enemy&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50% of the Resonator's Max HP&lt;/color&gt; cho Resonator.</t>
+          <t>Kẻ địch nhận hiệu ứng sau: &lt;color=#b72924ff&gt;Phòng Ngự của Queen of the Night tăng 10%&lt;/color&gt;. Hiệu ứng có thể chồng chất.
+&lt;color=#5cc96aff&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ hồi phục &lt;color=#5cc96aff&gt;50% HP tối đa&lt;/color&gt; cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;When Fleurdelys hits a Resonator&lt;/color&gt;, cô sẽ nhận một Lớp Shield tương đương &lt;color=#b72924ff&gt;5% of her Max HP&lt;/color&gt;, kích hoạt mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt; một lần. &lt;color=#b72924ff&gt;Her Vibration Strength cannot be reduced by taking DMG when she is shielded&lt;/color&gt;.</t>
+          <t>Khi &lt;color=#b72924ff&gt;Fleurdelys đánh trúng một Resonator&lt;/color&gt;, cô sẽ nhận một Lớp Khiên tương đương &lt;color=#b72924ff&gt;5% HP tối đa&lt;/color&gt;, kích hoạt mỗi &lt;color=#b72924ff&gt;10 giây&lt;/color&gt; một lần. &lt;color=#b72924ff&gt;Sức Mạnh Rung Động của cô không thể bị giảm khi đang được bảo vệ bởi Lớp Khiên&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;When a Resonator hits an enemy&lt;/color&gt;, &lt;color=#b72924ff&gt;a lightning strike is summoned&lt;/color&gt; tại vị trí đó để phản công Resonator, gây sát thương bằng &lt;color=#b72924ff&gt;10% of the Resonator's Max HP&lt;/color&gt; của Resonator. Hiệu ứng này chỉ kích hoạt &lt;color=#b72924ff&gt;10s&lt;/color&gt; một lần.</t>
+          <t>Khi &lt;color=#b72924ff&gt;Resonator tấn công kẻ địch&lt;/color&gt;, &lt;color=#b72924ff&gt;một tia sét sẽ giáng xuống&lt;/color&gt; tại vị trí đó để phản công Resonator, gây DMG bằng &lt;color=#b72924ff&gt;10% HP tối đa&lt;/color&gt; của Resonator. Hiệu ứng này chỉ kích hoạt &lt;color=#b72924ff&gt;mỗi 10 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Khi bước vào trận chiến, Resonators trong đội nhận được Shield tương đương &lt;color=#5cc96aff&gt;20% of their Max HP&lt;/color&gt;. &lt;color=#b72924ff&gt;When Resonators aren't shielded&lt;/color&gt;, họ sẽ chịu Sát Thương bằng &lt;color=#b72924ff&gt;2% of their Max HP&lt;/color&gt; mỗi giây.</t>
+          <t>Khi bước vào trận chiến, các Resonator trong đội nhận được Khiên tương đương &lt;color=#5cc96aff&gt;20% HP tối đa&lt;/color&gt;. &lt;color=#b72924ff&gt;Khi không còn khiên&lt;/color&gt;, họ sẽ chịu Sát Thương bằng &lt;color=#b72924ff&gt;2% HP tối đa&lt;/color&gt; mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Khi bước vào trận chiến, Resonators trong đội nhận được Shield tương đương &lt;color=#5cc96aff&gt;20% of their Max HP&lt;/color&gt;. &lt;color=#b72924ff&gt;When enemies are shielded&lt;/color&gt;, chúng sẽ chịu &lt;color=#b72924ff&gt;30% less DMG&lt;/color&gt;.</t>
+          <t>Khi bước vào trận chiến, các Resonator trong đội nhận được Khiên tương đương &lt;color=#5cc96aff&gt;20% HP tối đa&lt;/color&gt;. &lt;color=#b72924ff&gt;Khi kẻ địch có khiên&lt;/color&gt;, chúng sẽ chịu &lt;color=#b72924ff&gt;giảm 30% Sát Thương&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Khi bước vào trận chiến, Fleurdelys nhận được Shield tương đương &lt;color=#b72924ff&gt;50% of her Max HP&lt;/color&gt;. &lt;color=#5cc96aff&gt;Casting Resonance Liberation&lt;/color&gt; sẽ trao cho tất cả Resonators trong đội &lt;color=#5cc96aff&gt;10% DMG Bonus&lt;/color&gt; khi tấn công kẻ địch &lt;color=#5cc96aff&gt;shielded&lt;/color&gt;. Hiệu ứng này kéo dài &lt;color=#5cc96aff&gt;10s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#5cc96aff&gt;3 lần&lt;/color&gt;.</t>
+          <t>Khi bước vào trận chiến, Fleurdelys nhận được Khiên tương đương &lt;color=#b72924ff&gt;50% HP tối đa&lt;/color&gt;. &lt;color=#5cc96aff&gt;Kích hoạt Resonance Liberation&lt;/color&gt; sẽ trao cho tất cả Resonator trong đội &lt;color=#5cc96aff&gt;Thêm 10% Sát Thương&lt;/color&gt; khi tấn công kẻ địch &lt;color=#5cc96aff&gt;có khiên&lt;/color&gt;. Hiệu ứng này kéo dài &lt;color=#5cc96aff&gt;10 giây&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#5cc96aff&gt;3 lần&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Khi bước vào trận chiến, Fleurdelys nhận được Shield tương đương &lt;color=#b72924ff&gt;50% of her Max HP&lt;/color&gt;. &lt;color=#5cc96aff&gt;Casting Resonance Liberation&lt;/color&gt; sẽ trao cho tất cả Resonators trong đội Shield tương đương &lt;color=#5cc96aff&gt;10% of their Max HP&lt;/color&gt; của họ.</t>
+          <t>Khi bước vào trận chiến, Fleurdelys nhận được Khiên tương đương &lt;color=#b72924ff&gt;50% HP tối đa&lt;/color&gt;. &lt;color=#5cc96aff&gt;Kích hoạt Resonance Liberation&lt;/color&gt; sẽ trao cho tất cả Resonator trong đội Khiên tương đương &lt;color=#5cc96aff&gt;10% HP tối đa&lt;/color&gt; của họ.</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Khi Lá Chắn của Fleurdelys &lt;color=#b72924ff&gt;totally depleted&lt;/color&gt;, nó sẽ gây Sát Thương bằng &lt;color=#b72924ff&gt;200% of her ATK&lt;/color&gt; lên Resonators xung quanh.</t>
+          <t>Khi Lá Chắn của Fleurdelys &lt;color=#b72924ff&gt;bị phá hủy hoàn toàn&lt;/color&gt;, nó sẽ gây Sát Thương bằng &lt;color=#b72924ff&gt;200% ATK của cô&lt;/color&gt; lên các Resonator xung quanh.</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Havoc Dreadmane&lt;/color&gt; giờ đây &lt;color=#b72924ff&gt;restores 4% of Feilian Beringal's Max HP&lt;/color&gt; khi gây sát thương. &lt;color=#5cc96aff&gt;When an enemy is defeated&lt;/color&gt;, Resonators trong đội sẽ &lt;color=#5cc96aff&gt;3% of their Max HP&lt;/color&gt; khi gây sát thương. Hiệu ứng này kéo dài trong &lt;color=#5cc96aff&gt;10s&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;Havoc Dreadmane&lt;/color&gt; giờ đây &lt;color=#b72924ff&gt;hồi phục 4% HP tối đa của Feilian Beringal&lt;/color&gt; khi gây sát thương. &lt;color=#5cc96aff&gt;Khi đánh bại kẻ địch&lt;/color&gt;, các Resonator trong đội sẽ &lt;color=#5cc96aff&gt;hồi phục 3% HP tối đa&lt;/color&gt; khi gây sát thương. Hiệu ứng này kéo dài trong &lt;color=#5cc96aff&gt;10 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9711,8 +9711,8 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Spearback&lt;/color&gt; mang lại hiệu ứng sau: Feilian Beringal &lt;color=#b72924ff&gt;takes 50% less DMG&lt;/color&gt;.
-&lt;color=#5cc96aff&gt;Defeating an enemy&lt;/color&gt; sẽ tăng &lt;color=#5cc96aff&gt;DEF&lt;/color&gt; cho Resonators trong đội lên &lt;color=#5cc96aff&gt;10%&lt;/color&gt;. Hiệu ứng này có thể chồng chất.</t>
+          <t>&lt;color=#b72924ff&gt;Spearback&lt;/color&gt; mang lại hiệu ứng sau: Feilian Beringal &lt;color=#b72924ff&gt;chịu ít hơn 50% DMG&lt;/color&gt;.
+&lt;color=#5cc96aff&gt;Tiêu diệt kẻ địch&lt;/color&gt; sẽ tăng &lt;color=#5cc96aff&gt;Phòng Ngự&lt;/color&gt; cho các Resonator trong đội lên &lt;color=#5cc96aff&gt;10%&lt;/color&gt;. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -9778,8 +9778,8 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Hoochief Menace&lt;/color&gt; giờ đây &lt;color=#b72924ff&gt;restores 1.2% of Feilian Beringal's Max HP&lt;/color&gt;.
-&lt;color=#5cc96aff&gt;When an enemy is defeated&lt;/color&gt;, Resonators trong đội sẽ &lt;color=#5cc96aff&gt;1% of their Max HP&lt;/color&gt;. Hiệu ứng này có thể chồng chất.</t>
+          <t>&lt;color=#b72924ff&gt;Hoochief Menace&lt;/color&gt; giờ đây &lt;color=#b72924ff&gt;hồi phục 1.2% HP tối đa của Feilian Beringal&lt;/color&gt;.
+&lt;color=#5cc96aff&gt;Khi đánh bại kẻ địch&lt;/color&gt;, các Resonator trong đội sẽ &lt;color=#5cc96aff&gt;hồi phục 1% HP tối đa mỗi giây&lt;/color&gt;. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Một số kẻ địch được tăng cường: Tất cả kẻ địch khác gần đó có &lt;color=#b72924ff&gt;ATK increased by 20%&lt;/color&gt;.</t>
+          <t>Một số kẻ địch được tăng cường: Tất cả kẻ địch khác gần đó có &lt;color=#b72924ff&gt;ATK tăng 20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Một số kẻ địch được tăng cường: Tất cả kẻ địch khác gần đó có &lt;color=#b72924ff&gt;DEF increased by 20%&lt;/color&gt;.</t>
+          <t>Một số kẻ địch được tăng cường: Tất cả kẻ địch khác gần đó có &lt;color=#b72924ff&gt;Phòng Ngự tăng 20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Resonators &lt;color=#b72924ff&gt;take 30% more DMG&lt;/color&gt;. &lt;color=#5cc96aff&gt;Dodge Counter&lt;/color&gt; còn gây thêm sát thương bằng &lt;color=#5cc96aff&gt;3% of their Max HP&lt;/color&gt; lên kẻ địch.</t>
+          <t>Resonator &lt;color=#b72924ff&gt;chịu thêm 30% DMG&lt;/color&gt;. &lt;color=#5cc96aff&gt;Dodge Counter Tránh&lt;/color&gt; còn gây thêm DMG bằng &lt;color=#5cc96aff&gt;3% HP tối đa&lt;/color&gt; lên kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Khi bước vào trận chiến, tất cả kẻ địch ngoại trừ Feilian Beringal nhận được Shield tương đương &lt;color=#b72924ff&gt;30% of their Max HP&lt;/color&gt;. Khi có khiên, chúng sẽ nhận &lt;color=#b72924ff&gt;50% DMG Bonus&lt;/color&gt;.</t>
+          <t>Khi bước vào trận chiến, tất cả kẻ địch ngoại trừ Feilian Beringal nhận được Khiên tương đương &lt;color=#b72924ff&gt;30% HP tối đa&lt;/color&gt;. Khi có khiên, chúng sẽ nhận &lt;color=#b72924ff&gt;Thêm 50% Sát Thương&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Khi bước vào trận chiến, tất cả kẻ địch ngoại trừ Feilian Beringal nhận được Shield tương đương &lt;color=#b72924ff&gt;50% of their Max HP&lt;/color&gt;.</t>
+          <t>Khi bước vào trận chiến, tất cả kẻ địch ngoại trừ Feilian Beringal nhận được Khiên tương đương &lt;color=#b72924ff&gt;50% HP tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Resonance Skill &lt;color=#b72924ff&gt;Casting Resonance Skill&lt;/color&gt; gây &lt;color=#b72924ff&gt;2 tầng&lt;/color&gt; &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên Resonator. &lt;color=#5cc96aff&gt;Casting Resonance Liberation&lt;/color&gt; sẽ loại bỏ toàn bộ tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt;.</t>
+          <t>Kỹ năng Cộng Hưởng &lt;color=#b72924ff&gt;triệu hồi&lt;/color&gt; gây &lt;color=#b72924ff&gt;2 tầng&lt;/color&gt; &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên Resonator. &lt;color=#5cc96aff&gt;Kỹ năng Resonance Liberation&lt;/color&gt; sẽ loại bỏ toàn bộ tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Casting Heavy Attack&lt;/color&gt; sẽ gây &lt;color=#b72924ff&gt;2 tầng&lt;/color&gt; &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên Resonator. &lt;color=#5cc96aff&gt;Casting Resonance Liberation&lt;/color&gt; sẽ xóa toàn bộ tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;Dùng Heavy Attack&lt;/color&gt; sẽ gây &lt;color=#b72924ff&gt;2 tầng&lt;/color&gt; &lt;color=#b72924ff&gt;Glacio Chafe&lt;/color&gt; lên Resonator. &lt;color=#5cc96aff&gt;Dùng Resonance Liberation&lt;/color&gt; sẽ xóa toàn bộ tầng &lt;color=#5cc96aff&gt;Glacio Chafe&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Khi Resonator chủ động &lt;color=#b72924ff&gt;on the ground&lt;/color&gt; và trong phạm vi nhất định của kẻ địch, họ sẽ chịu Sát Thương bằng &lt;color=#b72924ff&gt;1.2% of their Max HP&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0.5s&lt;/color&gt;.</t>
+          <t>Khi Resonator chủ động &lt;color=#b72924ff&gt;đứng trên mặt đất&lt;/color&gt; và trong phạm vi nhất định của kẻ địch, họ sẽ chịu Sát Thương bằng &lt;color=#b72924ff&gt;1,2% HP tối đa&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;0,5 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Staying on the ground&lt;/color&gt; gây &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Aero Erosion&lt;/color&gt; lên Resonator đang hoạt động sau mỗi &lt;color=#b72924ff&gt;1.5s&lt;/color&gt;. Tất cả các tầng &lt;color=#5cc96aff&gt;Aero Erosion&lt;/color&gt; sẽ bị xóa khi ở &lt;color=#5cc96aff&gt;trên không&lt;/color&gt;.</t>
+          <t>Ở &lt;color=#b72924ff&gt;trạng thái trên mặt đất&lt;/color&gt;, Resonator hiện tại sẽ nhận &lt;color=#b72924ff&gt;1 tầng Xói Mòn Aero&lt;/color&gt; sau mỗi &lt;color=#b72924ff&gt;1,5 giây&lt;/color&gt;. Toàn bộ &lt;color=#5cc96aff&gt;tầng Xói Mòn Aero&lt;/color&gt; sẽ bị xóa khi ở &lt;color=#5cc96aff&gt;trạng thái lơ lửng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Staying in trên không&lt;/color&gt; gây &lt;color=#b72924ff&gt;1&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Aero Erosion&lt;/color&gt; lên Resonator đang hoạt động sau mỗi &lt;color=#b72924ff&gt;1.5s&lt;/color&gt;.</t>
+          <t>Ở &lt;color=#b72924ff&gt;trạng thái lơ lửng&lt;/color&gt;, Resonator hiện tại sẽ nhận &lt;color=#b72924ff&gt;1 tầng Xói Mòn Aero&lt;/color&gt; sau mỗi &lt;color=#b72924ff&gt;1,5 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Cooldown chiêu của Resonance Liberation &lt;color=#b72924ff&gt;cooldown is increased by 300%&lt;/color&gt;. Gây sát thương sẽ giảm Cooldown chiêu Resonance Liberation của Resonator đi &lt;color=#5cc96aff&gt;1s&lt;/color&gt;, kích hoạt mỗi &lt;color=#b72924ff&gt;0.2s&lt;/color&gt; một lần.</t>
+          <t>Thời gian hồi chiêu của Resonance Liberation &lt;color=#b72924ff&gt;tăng 300%&lt;/color&gt;. Gây sát thương sẽ giảm thời gian hồi chiêu Resonance Liberation của Resonator đi &lt;color=#5cc96aff&gt;1 giây&lt;/color&gt;, kích hoạt mỗi &lt;color=#b72924ff&gt;0,2 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Resonance Liberation &lt;color=#b72924ff&gt;thời gian Cooldown tăng 100%&lt;/color&gt;.</t>
+          <t>Resonance Liberation &lt;color=#b72924ff&gt;tăng thời gian hồi chiêu lên 100%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>&lt;color=#5cc96aff&gt;Attribute RES is reduced by 30%&lt;/color&gt;. Gây &lt;color=#b72924ff&gt;Resonance Skill DMG&lt;/color&gt; lên kẻ địch đang mang &lt;color=#b72924ff&gt;Negative Status&lt;/color&gt; sẽ áp đặt &lt;color=#b72924ff&gt;5&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Spectro Frazzle&lt;/color&gt; lên Resonator.</t>
+          <t>&lt;color=#5cc96aff&gt;Kháng Thuộc Tính của kẻ địch giảm 30%&lt;/color&gt;. Gây &lt;color=#b72924ff&gt;Sát Thương Resonance Skill&lt;/color&gt; lên kẻ địch đang mang &lt;color=#b72924ff&gt;Trạng Thái Tiêu Cực&lt;/color&gt; sẽ áp đặt &lt;color=#b72924ff&gt;5&lt;/color&gt; tầng &lt;color=#b72924ff&gt;Spectro Frazzle&lt;/color&gt; lên Resonator.</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Attribute RES is increased by 30%&lt;/color&gt;. Gây sát thương lên kẻ địch đang mang &lt;color=#5cc96aff&gt;Negative Status&lt;/color&gt; sẽ xóa toàn bộ &lt;color=#5cc96aff&gt;Negative Statuses&lt;/color&gt; trên bản thân Resonators.</t>
+          <t>&lt;color=#b72924ff&gt;Kháng Thuộc Tính của kẻ địch tăng 30%&lt;/color&gt;. Gây sát thương lên kẻ địch đang mang &lt;color=#5cc96aff&gt;Trạng Thái Tiêu Cực&lt;/color&gt; sẽ xóa toàn bộ &lt;color=#5cc96aff&gt;Trạng Thái Tiêu Cực&lt;/color&gt; trên bản thân Resonator.</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Max Vibration Strength is increased by 100%&lt;/color&gt;. Mỗi lần tấn công kẻ địch bằng &lt;color=#5cc96aff&gt;Coordinated Attack&lt;/color&gt; sẽ làm giảm thêm &lt;color=#5cc96aff&gt;7%&lt;/color&gt; Lực Rung Động của chúng.</t>
+          <t>&lt;color=#b72924ff&gt;Lực Rung Động Tối Đa của kẻ địch tăng 100%&lt;/color&gt;. Mỗi lần tấn công kẻ địch bằng &lt;color=#5cc96aff&gt;Đòn Phối Hợp&lt;/color&gt; sẽ làm giảm thêm &lt;color=#5cc96aff&gt;7%&lt;/color&gt; Lực Rung Động của chúng.</t>
         </is>
       </c>
     </row>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Max Vibration Strength is increased by 100%&lt;/color&gt;. Mỗi lần tấn công kẻ địch bằng &lt;color=#5cc96aff&gt;Dodge Counter&lt;/color&gt; sẽ làm giảm thêm &lt;color=#5cc96aff&gt;10%&lt;/color&gt; Lực Rung Động của chúng.</t>
+          <t>&lt;color=#b72924ff&gt;Lực Rung Động Tối Đa của kẻ địch tăng 100%&lt;/color&gt;. Mỗi lần tấn công kẻ địch bằng &lt;color=#5cc96aff&gt;Dodge Counter Tránh&lt;/color&gt; sẽ làm giảm thêm &lt;color=#5cc96aff&gt;10%&lt;/color&gt; Lực Rung Động của chúng.</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tất cả kẻ địch (trừ Fallacy of Không Return) nhận &lt;color=#b72924ff&gt;5% DMG Bonus&lt;/color&gt; và bị &lt;color=#5cc96aff&gt;DEF reduced by 5%&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;5s&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;20 lần&lt;/color&gt;.</t>
+          <t>Tất cả kẻ địch (trừ Fallacy of No Return) nhận &lt;color=#b72924ff&gt;+5% Sát Thương&lt;/color&gt; và bị &lt;color=#5cc96aff&gt;giảm 5% DEF&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;5 giây&lt;/color&gt;, tối đa &lt;color=#b72924ff&gt;20 lần&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;max STA is reduced by 20%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;STA tối đa của Resonator giảm 20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;max STA is reduced by 40%&lt;/color&gt;.</t>
+          <t>&lt;color=#b72924ff&gt;STA tối đa của Resonator giảm 40%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Max HP is increased by 15%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;HP tối đa tăng 15%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Max HP is increased by 30%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 30% HP tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Max Vibration Strength is increased by 15%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 15% Độ Mạnh Rung Động tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Max Vibration Strength is increased by 30%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 30% Độ Mạnh Rung Động tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11350,16 +11350,16 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>[Stats Resonators]
-Trong Dreaming Deep, chỉ số của Chuỗi Resonance, Vũ Khí và Kỹ Năng của Resonators sẽ giống như ở Thế Giới Thường.
-[Cấp Độ Resonators]
-Mỗi cấp độ đội đạt được sẽ tăng cấp độ Resonators lên 1.
-[Weapon Level]
+          <t>[Chỉ Số Resonator]
+Trong Dreaming Deep, chỉ số của Resonance Chain, Vũ Khí và Kỹ Năng của Resonator sẽ giống như ở Thế Giới Thường.
+[Cấp Độ Resonator]
+Mỗi cấp độ đội đạt được sẽ tăng cấp độ Resonator lên 1.
+[Cấp Độ Vũ Khí]
 Mỗi cấp độ đội đạt được sẽ tăng cấp độ Vũ Khí lên 1.
 [Cấp Độ Kỹ Năng]
 Cấp Đội 1 = Cấp Kỹ Năng 1
 Cấp Đội 40 = Cấp Kỹ Năng 3
-Cấp Đội 60 = Skill Level 6
+Cấp Đội 60 = Cấp Kỹ Năng 6
 Cấp Đội 80 = Cấp Kỹ Năng 9
 Cấp Đội 90 = Cấp Kỹ Năng 10</t>
         </is>
@@ -11432,13 +11432,13 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>1) Hoàn thành Battle Event, Random Event hoặc Sự Kiện Cốt Truyện trong Film sẽ tiêu hao Cuộn Film.
-2) Nếu bị đánh bại trong trận chiến, bạn có thể tiêu hao Cuộn Film để quay về trạng thái trước trận đấu.
-3) Số lượng Cuộn Film bạn sở hữu quyết định hiệu ứng bạn nhận được:
-Trên 70 Cuộn Film: Crit. Rate tăng 20%. Sử dụng Resonance Skill hồi phục 20% HP tối đa, hiệu lực mỗi 30 giây một lần.
-30 đến 70 Cuộn Film: Sử dụng Resonance Skill hồi phục 20% HP tối đa, hiệu lực mỗi 30 giây một lần.
--30 đến -70 Cuộn Film: Tấn Công của kẻ địch tăng 20%.
-Dưới -70 Cuộn Film: Tấn Công của kẻ địch tăng 40% và HP tăng 30%.</t>
+          <t>1) Hoàn thành Sự Kiện Chiến Đấu, Sự Kiện Ngẫu Nhiên hoặc Sự Kiện Cốt Truyện trong Phim sẽ tiêu hao Cuộn Phim.
+2) Nếu bị đánh bại trong trận chiến, bạn có thể tiêu hao Cuộn Phim để quay về trạng thái trước trận đấu.
+3) Số lượng Cuộn Phim bạn sở hữu quyết định hiệu ứng bạn nhận được:
+Trên 70 Cuộn Phim: Crit. Rate tăng 20%. Sử dụng Resonance Skill hồi phục 20% HP tối đa, hiệu lực mỗi 30 giây một lần.
+30 đến 70 Cuộn Phim: Sử dụng Resonance Skill hồi phục 20% HP tối đa, hiệu lực mỗi 30 giây một lần.
+-30 đến -70 Cuộn Phim: ATK của kẻ địch tăng 20%.
+Dưới -70 Cuộn Phim: ATK của kẻ địch tăng 40% và HP tăng 30%.</t>
         </is>
       </c>
     </row>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Cooldown chiêu &lt;color=#b72924ff&gt;Resonator switch cooldown&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;3s&lt;/color&gt; (Skill Khởi Động không bị ảnh hưởng).</t>
+          <t>Thời gian hồi chiêu &lt;color=#b72924ff&gt;chuyển đổi Resonator&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;3 giây&lt;/color&gt; (Kỹ năng Khởi Động không bị ảnh hưởng).</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Cooldown chiêu &lt;color=#b72924ff&gt;Resonator switch cooldown&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;5s&lt;/color&gt; (Intro Skill không bị ảnh hưởng).</t>
+          <t>Thời gian hồi chiêu &lt;color=#b72924ff&gt;chuyển đổi Resonator&lt;/color&gt; tăng lên &lt;color=#b72924ff&gt;5 giây&lt;/color&gt; (Kỹ Năng Khởi Động không bị ảnh hưởng).</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;Max HP is increased by 20%&lt;/color&gt;. &lt;color=#5cc96aff&gt;Dodge Counter&lt;/color&gt; gây thêm sát thương bằng &lt;color=#5cc96aff&gt;3%&lt;/color&gt; HP tối đa của kẻ địch.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;tăng 20% HP tối đa&lt;/color&gt;. &lt;color=#5cc96aff&gt;Dodge Counter Tránh&lt;/color&gt; gây thêm DMG bằng &lt;color=#5cc96aff&gt;3%&lt;/color&gt; HP tối đa của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK is increased by 15%&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=#b72924ff&gt;ATK tăng 15%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Khi kẻ địch ở trạng thái &lt;color=#b72924ff&gt;Immobilized&lt;/color&gt;, chúng gây Sát Thương bằng &lt;color=#b72924ff&gt;200% of their ATK&lt;/color&gt; lên Resonators gần đó.</t>
+          <t>Khi kẻ địch ở trạng thái &lt;color=#b72924ff&gt;Bất Động&lt;/color&gt;, chúng gây Sát Thương bằng &lt;color=#b72924ff&gt;200% ATK&lt;/color&gt; lên các Resonator gần đó.</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Cooldown chiêu của Resonance Liberation &lt;color=#b72924ff&gt;cooldown is increased by 300%&lt;/color&gt;. Khi Resonator đang kích hoạt tiêu diệt kẻ địch, &lt;color=#5cc96aff&gt;their Resonance Liberation cooldown is immediately reset&lt;/color&gt;.</t>
+          <t>Thời gian hồi chiêu của Resonance Liberation &lt;color=#b72924ff&gt;tăng 300%&lt;/color&gt;. Khi Resonator đang kích hoạt tiêu diệt kẻ địch, &lt;color=#5cc96aff&gt;thời gian hồi chiêu Resonance Liberation của họ sẽ được đặt lại ngay lập tức&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Cooldown chiêu Resonance Liberation của Resonators giảm 50%.</t>
+          <t>Thời gian hồi chiêu Resonance Liberation của Resonator giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Tốc độ phục hồi Thể Lực của Resonators tăng 100%.</t>
+          <t>Tốc độ phục hồi STA của Resonator tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Tốc độ Basic Attack của Resonators tăng 60%.</t>
+          <t>Tốc độ Basic Attack của Resonator tăng 60%.</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>HP tối đa của Resonators tăng 100%.</t>
+          <t>HP tối đa của Resonator tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Khi ở trên không, Resonators phục hồi 1% HP tối đa mỗi giây.</t>
+          <t>Khi ở trên không, Resonator phục hồi 1% HP tối đa mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Concerto Regen của Resonators tăng 100%.</t>
+          <t>Hồi Phục Concerto của Resonator tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Khi HP của Fleurdelys xuống thấp, cô sẽ nhận được một Lá Chắn tương đương &lt;color=#b72924ff&gt;50% of her Max HP&lt;/color&gt;. Các khu vực khác nhau trên chiến trường &lt;color=#5cc96aff&gt;provide various buffs for Resonators&lt;/color&gt;.</t>
+          <t>Khi HP của Fleurdelys xuống thấp, cô sẽ nhận được một Lá Chắn tương đương &lt;color=#b72924ff&gt;50% HP tối đa&lt;/color&gt;. Các khu vực khác nhau trên chiến trường &lt;color=#5cc96aff&gt;cung cấp nhiều hiệu ứng tăng cường khác nhau cho Resonator&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Queen of the Night triệu hồi &lt;color=#b72924ff&gt;Burst Bubble and Healing Bubble&lt;/color&gt;, gây sát thương hoặc hồi phục cho cả Resonators lẫn kẻ địch.</t>
+          <t>Queen of the Night triệu hồi &lt;color=#b72924ff&gt;Bong Bóng Nổ và Bong Bóng Hồi Phục&lt;/color&gt;, gây sát thương hoặc hồi phục cho cả Resonator lẫn kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -12432,26 +12432,26 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Về Khám Phá Map
-[Events]
+          <t>Về Khám Phá Bản Đồ
+[Sự Kiện]
 Trên bản đồ có nhiều loại sự kiện khác nhau, mỗi loại mang lại hiệu ứng như sau:
-Events Cốt Truyện: Events bắt buộc để tiến triển, bao gồm cốt truyện chính và thử thách cuối.
-Battle Event: Tham gia chiến đấu và nhận Dream Fragments dựa trên độ khó của trận đánh.
-Random Event: Trigger các kết quả khác nhau.
-Events Tuyển Mộ: Dùng Dream Fragments để tuyển Synergy Giả.
-Events Nghỉ Ngơi: Khôi phục Film Cuộn.
-[Film Cuộn]
-Film Cuộn bị tiêu hao trong Battle Event, Random Event và Events Cốt Truyện.
-Nếu bị đánh bại trong trận chiến, dùng Film Cuộn để đưa Synergy Giả về trạng thái trước khi giao tranh.
-[Bond]
-Một số Synergy Giả có thể hình thành Bond, và một Synergy Giả có thể có nhiều Bond.
-Bond mang lại hiệu ứng tăng cường chiến đấu áp dụng cho tất cả Synergy Giả trừ khi có quy định khác.
-Cấp Độ Bond dựa trên Xếp Hạng Sao của tất cả Synergy Giả cùng chia sẻ Bond đó.
-Increase Cấp Độ Bond để mở khóa Kỹ Năng Đồng Điệu Đặc Biệt.
+Sự Kiện Cốt Truyện: Sự kiện bắt buộc để tiến triển, bao gồm cốt truyện chính và thử thách cuối.
+Sự Kiện Chiến Đấu: Tham gia chiến đấu và nhận Mảnh Giấc Mơ dựa trên độ khó của trận đánh.
+Sự Kiện Ngẫu Nhiên: Kích hoạt các kết quả khác nhau.
+Sự Kiện Tuyển Mộ: Dùng Mảnh Giấc Mơ để tuyển Resonator.
+Sự Kiện Nghỉ Ngơi: Khôi phục Phim Cuộn.
+[Phim Cuộn]
+Phim Cuộn bị tiêu hao trong Sự Kiện Chiến Đấu, Sự Kiện Ngẫu Nhiên và Sự Kiện Cốt Truyện.
+Nếu bị đánh bại trong trận chiến, dùng Phim Cuộn để đưa Resonator về trạng thái trước khi giao tranh.
+[Mối Liên Kết]
+Một số Resonator có thể hình thành Mối Liên Kết, và một Resonator có thể có nhiều Mối Liên Kết.
+Mối Liên Kết mang lại hiệu ứng tăng cường chiến đấu áp dụng cho tất cả Resonator trừ khi có quy định khác.
+Cấp Độ Mối Liên Kết dựa trên Xếp Hạng Sao của tất cả Resonator cùng chia sẻ Mối Liên Kết đó.
+Tăng Cấp Độ Mối Liên Kết để mở khóa Kỹ Năng Đồng Điệu Đặc Biệt.
 [Kỹ Năng Đồng Điệu]
-Khi có ba Synergy Giả cùng Bond trong đội, Kỹ Năng Đồng Điệu của họ sẽ được kích hoạt, mang lại các hiệu ứng sau:
+Khi có ba Resonator cùng Mối Liên Kết trong đội, Kỹ Năng Đồng Điệu của họ sẽ được kích hoạt, mang lại các hiệu ứng sau:
 1. Mục tiêu bị bất động ngay lập tức.
-2. Cooldown chiêu của Kỹ Năng Synergy và Giải Phóng Synergy được đặt lại. Năng Lượng Synergy được phục hồi và 100 Concerto Energy được khôi phục.</t>
+2. Thời gian hồi chiêu của Resonance Skill và Resonance Liberation được đặt lại. Resonance Energy được phục hồi và 100 Concerto Energy được khôi phục.</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Khi Resonators Hệ Aero liên tục tấn công mục tiêu (khoảng cách giữa các lần tấn công dưới 2 giây), sát thương gây ra sẽ tăng thêm 8% mỗi 0,5 giây, kéo dài trong 1,5 giây và có thể chồng chất tối đa 15 lần.</t>
+          <t>Khi Resonator Hệ Aero liên tục tấn công mục tiêu (khoảng cách giữa các lần tấn công dưới 2 giây), sát thương gây ra sẽ tăng thêm 8% mỗi 0,5 giây, kéo dài trong 1,5 giây và có thể chồng chất tối đa 15 lần.</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Khi Resonators Hệ Aero liên tục tấn công mục tiêu, sát thương gây ra sẽ tăng lên.</t>
+          <t>Khi Resonator Hệ Aero liên tục tấn công mục tiêu, sát thương gây ra sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Sau khi Resonators Glacio kích hoạt Resonance Liberation, Tấn Công của họ tăng 100% trong 15 giây.</t>
+          <t>Sau khi Resonator Glacio kích hoạt Resonance Liberation, ATK của họ tăng 100% trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Sau khi Resonators Glacio kích hoạt Resonance Liberation, Tấn Công của họ được tăng cường.</t>
+          <t>Sau khi Resonator Glacio kích hoạt Resonance Liberation, ATK của họ được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Khi Resonators Spectro gây sát thương lên mục tiêu bị Spectro Frazzle, Crit. DMG của đòn tấn công này tăng thêm 150%.</t>
+          <t>Khi Resonator Spectro gây DMG lên mục tiêu bị Rối Loạn Spectro, Crit. DMG của đòn tấn công này tăng thêm 150%.</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Khi Resonators Spectro gây sát thương lên mục tiêu bị hiệu ứng Spectro Frazzle, Crit. DMG của đòn tấn công này sẽ tăng lên.</t>
+          <t>Khi Resonator Spectro gây DMG lên mục tiêu bị hiệu ứng Rối Loạn Spectro, Crit. DMG của đòn tấn công này sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators Havoc gây sát thương, mục tiêu trúng đòn sẽ nhận một tầng [Phân Rã], giảm Havoc RES đi 5% trong 20 giây, tối đa 20 tầng. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Mỗi khi Resonator Havoc gây sát thương, mục tiêu trúng đòn sẽ nhận một tầng [Phân Rã], giảm Kháng Havoc đi 5% trong 20 giây, tối đa 20 tầng. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators Havoc gây sát thương, Havoc RES của mục tiêu sẽ bị giảm.</t>
+          <t>Mỗi khi Resonator Havoc gây sát thương, Kháng Havoc của mục tiêu sẽ bị giảm.</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13036,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators Fusion gây sát thương, họ sẽ áp đặt một tầng [Effect Fusion], tăng Crit. DMG lên 7% trong 10 giây, tối đa 30 tầng. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Mỗi khi Resonator Fusion gây DMG, họ sẽ áp đặt một tầng [Hiệu Ứng Fusion], tăng Crit. DMG lên 7% trong 10 giây, tối đa 30 tầng. Hiệu ứng này chỉ kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators Fusion gây sát thương, họ sẽ áp đặt một tầng [Effect Fusion], tăng Crit. DMG.</t>
+          <t>Mỗi khi Resonator Fusion gây DMG, họ sẽ áp đặt một tầng [Hiệu Ứng Fusion], tăng Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Sau khi Resonators Hệ Electro sử dụng Resonance Skill, Electro DMG của họ tăng 50% trong 12 giây, có thể chồng chất tối đa 4 lần. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Sau khi Resonator Hệ Electro sử dụng Resonance Skill, DMG Electro của họ tăng 50% trong 12 giây, có thể chồng chất tối đa 4 lần. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Sau khi Resonators Hệ Electro sử dụng Resonance Skill, Electro DMG của họ được tăng cường.</t>
+          <t>Sau khi Resonator Hệ Electro sử dụng Resonance Skill, DMG Electro của họ được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators Hệ Aero hoặc Spectro tấn công mục tiêu, hiệu ứng Spectro Frazzle và Aero Erosion trên mục tiêu sẽ ngay lập tức gây sát thương thêm một lần. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần.</t>
+          <t>Mỗi khi Resonator Hệ Aero hoặc Spectro tấn công mục tiêu, hiệu ứng Spectro Frazzle và Aero Erosion trên mục tiêu sẽ ngay lập tức gây sát thương thêm một lần. Hiệu ứng này chỉ có thể kích hoạt mỗi 2 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators Hệ Aero hoặc Spectro tấn công mục tiêu, hiệu ứng Spectro Frazzle và Aero Erosion trên mục tiêu sẽ ngay lập tức gây sát thương thêm một lần.</t>
+          <t>Mỗi khi Resonator Hệ Aero hoặc Spectro tấn công mục tiêu, hiệu ứng Spectro Frazzle và Aero Erosion trên mục tiêu sẽ ngay lập tức gây sát thương thêm một lần.</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Sát Thương Resonance Skill của Resonators Glacio và Spectro được Khuếch Đại thêm 60%.</t>
+          <t>Sát Thương Resonance Skill của Resonator Glacio và Spectro được Khuếch Đại thêm 60%.</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Sát Thương Resonance Skill của Resonators Glacio và Spectro được Khuếch Đại.</t>
+          <t>Sát Thương Resonance Skill của Resonator Glacio và Spectro được Khuếch Đại.</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Sát Thương Resonance Liberation của Resonators Fusion và Havoc được Khuếch Đại thêm 60%.</t>
+          <t>Sát Thương Resonance Liberation của Resonator Fusion và Havoc được Khuếch Đại thêm 60%.</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Sát Thương Resonance Liberation của Resonators Fusion và Havoc được Khuếch Đại.</t>
+          <t>Sát Thương Resonance Liberation của Resonator Fusion và Havoc được Khuếch Đại.</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Crit. DMG của Đòn Phối Hợp từ Resonators Electro, Fusion và Glacio tăng thêm 263%.</t>
+          <t>Crit. DMG của Đòn Phối Hợp từ các Resonator Electro, Fusion và Glacio tăng thêm 263%.</t>
         </is>
       </c>
     </row>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Crit. DMG của Đòn Phối Hợp từ Resonators Electro, Fusion và Glacio được tăng cường.</t>
+          <t>Crit. DMG của Đòn Phối Hợp từ các Resonator Electro, Fusion và Glacio được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Sau khi Resonators Hệ Electro hoặc Aero sử dụng Resonance Liberation, hiệu quả giảm Concerto Vibrancy của mục tiêu tăng 200% trong 12 giây. Tấn công mục tiêu bị bất động gây thêm sát thương Physical bằng 700% Tấn Công, kích hoạt mỗi 3 giây một lần.</t>
+          <t>Sau khi Resonator Hệ Electro hoặc Aero sử dụng Resonance Liberation, hiệu quả giảm Sức Mạnh Rung Động của mục tiêu tăng 200% trong 12 giây. ATK mục tiêu bị bất động gây thêm DMG Vật Lý bằng 700% ATK, kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Sau khi Resonators Hệ Electro hoặc Aero sử dụng Resonance Liberation, hiệu quả giảm Concerto Vibrancy của mục tiêu được tăng cường. Tấn công mục tiêu bị bất động gây thêm sát thương Physical.</t>
+          <t>Sau khi Resonator Hệ Electro hoặc Aero sử dụng Resonance Liberation, hiệu quả giảm Sức Mạnh Rung Động của mục tiêu được tăng cường. Tấn công mục tiêu bị bất động gây thêm DMG Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators dùng Rectifier hồi phục, họ nhận được một tầng [Nốt Mạnh]. Hiệu ứng này có thể kích hoạt mỗi giây. Khi đạt 10 tầng, tiêu hao toàn bộ để gây Sát Thương Physical bằng 500% Attack và thêm Sát Thương Physical bằng 100% HP cùng với Basic Attack tiếp theo.</t>
+          <t>Mỗi khi Resonator dùng Pháp khí hồi phục, họ nhận được một tầng [Nốt Mạnh]. Hiệu ứng này có thể kích hoạt mỗi giây. Khi đạt 10 tầng, tiêu hao toàn bộ để gây Sát Thương Vật Lý bằng 500% ATK và thêm Sát Thương Vật Lý bằng 100% HP cùng với Đòn Basic Attack tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators dùng Rectifier hồi phục, họ nhận được một tầng [Nốt Mạnh]. Khi đạt đủ số tầng nhất định, tiêu hao toàn bộ để gây thêm sát thương cùng Basic Attack.</t>
+          <t>Mỗi khi Resonator dùng Pháp khí hồi phục, họ nhận được một tầng [Nốt Mạnh]. Khi đạt đủ số tầng nhất định, tiêu hao toàn bộ để gây thêm DMG cùng Đòn Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Sau khi Resonators sử dụng Găng Tay kích hoạt Resonance Liberation, tất cả Resonators trong đội nhận Shield tương đương 50% HP tối đa trong 8 giây. Hiệu ứng này chỉ có thể kích hoạt mỗi 5 giây một lần.</t>
+          <t>Sau khi Resonator sử dụng Găng Tay kích hoạt Resonance Liberation, tất cả Resonator trong đội nhận Khiên tương đương 50% HP tối đa trong 8 giây. Hiệu ứng này chỉ có thể kích hoạt mỗi 5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14141,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Sau khi Resonators sử dụng Găng Tay kích hoạt Resonance Liberation, tất cả Resonators trong đội nhận Shield.</t>
+          <t>Sau khi Resonator sử dụng Găng Tay kích hoạt Resonance Liberation, tất cả Resonator trong đội nhận Khiên.</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Súng ngắn tấn công mục tiêu, họ gây thêm Sát Thương Physical bằng 400% Tấn Công. Hiệu ứng này có thể kích hoạt mỗi 5 giây một lần.</t>
+          <t>Khi Resonator sử dụng Súng ngắn tấn công mục tiêu, họ gây thêm Sát Thương Vật Lý bằng 400% ATK. Hiệu ứng này có thể kích hoạt mỗi 5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Súng ngắn tấn công mục tiêu, họ gây thêm sát thương.</t>
+          <t>Khi Resonator sử dụng Súng ngắn tấn công mục tiêu, họ gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -14336,7 +14336,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Kiếm gây Sát Thương Basic Attack, họ gây thêm Sát Thương Basic Attack bằng 80% Attack. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Khi Resonator sử dụng Kiếm gây Sát Thương Đòn Cơ Bản, họ gây thêm Sát Thương Đòn Cơ Bản bằng 80% ATK. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Kiếm gây Sát Thương Basic Attack, họ gây thêm sát thương.</t>
+          <t>Khi Resonator sử dụng Kiếm gây Sát Thương Đòn Cơ Bản, họ gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -14467,8 +14467,8 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators dùng Broadblade gây Sát Thương Resonance Skill, họ nhận được một tầng Impetus, tối đa 20 tầng. Hiệu ứng này có thể kích hoạt mỗi 0.1 giây.
-Khi Resonators dùng Broadblade trúng mục tiêu bằng Resonance Liberation, họ sẽ tiêu hao toàn bộ tầng Impetus để gây sát thương, mỗi tầng tiêu hao gây Sát Thương Physical bằng 70% Tấn Công.</t>
+          <t>Mỗi khi Resonator dùng Đại kiếm gây Sát Thương Resonance Skill, họ nhận được một tầng Impetus, tối đa 20 tầng. Hiệu ứng này có thể kích hoạt mỗi 0.1 giây.
+Khi Resonator dùng Đại kiếm trúng mục tiêu bằng Resonance Liberation, họ sẽ tiêu hao toàn bộ tầng Impetus để gây DMG, mỗi tầng tiêu hao gây Sát Thương Vật Lý bằng 70% ATK.</t>
         </is>
       </c>
     </row>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Mỗi khi Resonators sử dụng Broadblade gây Sát Thương Resonance Skill, họ nhận được [Đà Tấn Công]. Khi dùng Resonance Liberation trúng mục tiêu, tất cả [Đà Tấn Công] sẽ được tiêu thụ để gây thêm sát thương.</t>
+          <t>Mỗi khi Resonator sử dụng Đại kiếm gây Sát Thương Resonance Skill, họ nhận được [Đà Tấn Công]. Khi dùng Resonance Liberation trúng mục tiêu, tất cả [Đà Tấn Công] sẽ được tiêu thụ để gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Crit. DMG của Resonators sử dụng Găng Tay và Súng Ngắn khi tấn công mục tiêu bị bất động tăng 400%.</t>
+          <t>Crit. DMG của Resonator sử dụng Găng Tay và Súng Ngắn khi tấn công mục tiêu bị bất động tăng 400%.</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Crit. DMG của Resonators sử dụng Găng Tay và Súng Ngắn khi tấn công mục tiêu bị bất động được tăng lên.</t>
+          <t>Crit. DMG của Resonator sử dụng Găng Tay và Súng Ngắn khi tấn công mục tiêu bị bất động được tăng lên.</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Crit. Rate của Resonators sử dụng Bộ Chỉnh Lưu và Súng Ngắn tăng 30%. Mỗi khi gây sát thương, tất cả Resonators trong đội hồi phục thêm 2 Resonance Energy. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Crit. Rate của Resonator sử dụng Bộ Chỉnh Lưu và Súng Ngắn tăng 30%. Mỗi khi gây sát thương, tất cả Resonator trong đội hồi phục thêm 2 Resonance Energy. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Crit. Rate của Resonators sử dụng Bộ Chỉnh Lưu và Súng Ngắn tăng lên. Mỗi khi gây sát thương, tất cả Resonators trong đội hồi phục thêm Resonance Energy.</t>
+          <t>Crit. Rate của Resonator sử dụng Bộ Chỉnh Lưu và Súng Ngắn tăng lên. Mỗi khi gây sát thương, tất cả Resonator trong đội hồi phục thêm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Kiếm hoặc Rìu Lớn gây Sát Thương Resonance Liberation, họ áp đặt [Vết Cắt Sâu] lên mục tiêu trong 10 giây. Mỗi lần tấn công trúng, mục tiêu bị ảnh hưởng sẽ nhận thêm Sát Thương Physical bằng 300% Tấn Công. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Khi Resonator sử dụng Kiếm hoặc Rìu Lớn gây Sát Thương Resonance Liberation, họ áp đặt [Vết Cắt Sâu] lên mục tiêu trong 10 giây. Mỗi lần tấn công trúng, mục tiêu bị ảnh hưởng sẽ nhận thêm Sát Thương Vật Lý bằng 300% ATK. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -14923,7 +14923,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Sau khi Resonators sử dụng Kiếm hoặc Đại Kiếm gây Sát Thương Resonance Liberation, mục tiêu sẽ bị ảnh hưởng bởi [Vết Thương Sâu]. Mỗi lần tấn công trúng, mục tiêu sẽ chịu thêm Sát Thương Physical.</t>
+          <t>Sau khi Resonator sử dụng Kiếm hoặc Đại Kiếm gây Sát Thương Resonance Liberation, mục tiêu sẽ bị ảnh hưởng bởi [Vết Thương Sâu]. Mỗi lần tấn công trúng, mục tiêu sẽ chịu thêm Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -14989,8 +14989,8 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Với mỗi Resonators trong đội sử dụng Nắm Đấm hoặc Broadblade, tất cả Resonators dùng Nắm Đấm và Broadblade sẽ được tăng Crit. Rate thêm 10% và Crit. DMG thêm 30%.
-Khi Resonators dùng Nắm Đấm hoặc Broadblade gây sát thương, có 10% cơ hội hồi phục 7% HP tối đa. Hiệu ứng này có thể kích hoạt mỗi 15 giây một lần.</t>
+          <t>Với mỗi Resonator trong đội sử dụng Nắm Đấm hoặc Kiếm Rộng, tất cả Resonator dùng Nắm Đấm và Kiếm Rộng sẽ được tăng Crit. Rate thêm 10% và Crit. DMG thêm 30%.
+Khi Resonator dùng Nắm Đấm hoặc Kiếm Rộng gây DMG, có 10% cơ hội hồi phục 7% HP tối đa. Hiệu ứng này có thể kích hoạt mỗi 15 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15056,8 +15056,8 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Với mỗi Resonators sử dụng Găng Tay hoặc Broadblade trong đội, tất cả Resonators sử dụng Găng Tay và Broadblade trong đội sẽ được tăng Crit. Rate và Crit. DMG.
-Resonators sử dụng Găng Tay hoặc Broadblade có thể hồi phục HP khi gây sát thương.</t>
+          <t>Với mỗi Resonator sử dụng Găng Tay hoặc Kiếm Rộng trong đội, tất cả Resonator sử dụng Găng Tay và Kiếm Rộng trong đội sẽ được tăng Crit. Rate và Crit. DMG.
+Resonator sử dụng Găng Tay hoặc Kiếm Rộng có thể hồi phục HP khi gây DMG.</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Sau khi Resonators sử dụng Kiếm hoặc Bộ Chỉnh Lưu thi triển Resonance Liberation, tất cả Resonators trong đội sẽ hồi phục 20% HP tối đa và Tấn Công tăng 40% trong 10 giây.</t>
+          <t>Sau khi Resonator sử dụng Kiếm hoặc Bộ Chỉnh Lưu thi triển Resonance Liberation, tất cả Resonator trong đội sẽ hồi phục 20% HP tối đa và ATK tăng 40% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Sau khi Resonators sử dụng Kiếm hoặc Bộ Chỉnh Lưu thi triển Resonance Liberation, tất cả Resonators trong đội sẽ hồi phục HP và Tấn Công được tăng cường.</t>
+          <t>Sau khi Resonator sử dụng Kiếm hoặc Bộ Chỉnh Lưu thi triển Resonance Liberation, tất cả Resonator trong đội sẽ hồi phục HP và ATK được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Sát thương tấn công phối hợp được khuếch đại thêm {0}.</t>
+          <t>DMG tấn công phối hợp được khuếch đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Khi Đòn Phối Hợp gây sát thương, gọi thêm một đợt Attack Quỹ Đạo, gây sát thương Physical bằng {0} sức Attack khi trúng đích. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
+          <t>Khi Đòn Phối Hợp gây DMG, gọi thêm một đợt ATK Quỹ Đạo, gây DMG Vật Lý bằng {0} sức ATK khi trúng đích. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Khi Đòn Phối Hợp gây sát thương, Cooldown chiêu Resonance Skill của tất cả Resonators trong đội sẽ giảm {0} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
+          <t>Khi Đòn Phối Hợp gây sát thương, Thời gian hồi chiêu Resonance Skill của tất cả Resonator trong đội sẽ giảm {0} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Khi Đòn Phối Hợp gây sát thương, Cooldown chiêu Resonance Liberation của tất cả Resonators trong đội sẽ giảm {0} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
+          <t>Khi Đòn Phối Hợp gây sát thương, Thời gian hồi chiêu Resonance Liberation của tất cả Resonator trong đội sẽ giảm {0} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15514,9 +15514,9 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Khi đội có ít nhất &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Resonators P=Resonators SapTag=0} sở hữu Liên Kết "Chuyện Cổ Tích Kết Thúc":
-- Dodge thành công sẽ triệu hồi Dây Leo Ảo để tung mục tiêu gần đó lên không trung, gây Spectro DMG bằng {1} Tấn Công và hồi {2} HP tối đa của Resonators đang hoạt động. Hiệu ứng này có thể kích hoạt mỗi {3} giây một lần.
-- Sử dụng Resonance Skill sẽ kích hoạt Đòn Đánh Chiến Binh sau một khoảng thời gian ngắn, gây tổng Fusion DMG bằng {4} Tấn Công. Hiệu ứng này có thể kích hoạt mỗi {5} giây một lần.</t>
+          <t>Khi đội có ít nhất &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Resonator P=Resonator SapTag=0} sở hữu Liên Kết "Chuyện Cổ Tích Kết Thúc":
+- Né thành công sẽ triệu hồi Dây Leo Ảo để tung mục tiêu gần đó lên không trung, gây Sát Thương Spectro bằng {1} ATK và hồi {2} HP tối đa của Resonator đang hoạt động. Hiệu ứng này có thể kích hoạt mỗi {3} giây một lần.
+- Sử dụng Resonance Skill sẽ kích hoạt Đòn Đánh Chiến Binh sau một khoảng thời gian ngắn, gây tổng Sát Thương Fusion bằng {4} ATK. Hiệu ứng này có thể kích hoạt mỗi {5} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15583,9 +15583,9 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Khi đội có ít nhất &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Resonators P=Resonators SapTag=0} sở hữu Liên Kết "Chuyện Cổ Tích Kết Thúc":
-- Gây Sát Thương bằng Basic Attack sẽ triệu hồi Youhu thực hiện Brawl Bouncy, gây tổng Glacio DMG bằng {1} Attack. Hiệu ứng này có thể kích hoạt mỗi {2} giây một lần.
-- Gây Sát Thương bằng Heavy Attack sẽ triệu hồi Roccia thực hiện Xoáy Quái Dị và kéo các mục tiêu gần đó vào, gây tổng Havoc DMG bằng {3} Attack. Hiệu ứng này có thể kích hoạt mỗi {4} giây một lần.</t>
+          <t>Khi đội có ít nhất &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Resonator P=Resonator SapTag=0} sở hữu Liên Kết "Chuyện Cổ Tích Kết Thúc":
+- Gây Sát Thương bằng Đòn Basic Attack sẽ triệu hồi Youhu thực hiện Brawl Nảy, gây tổng Sát Thương Glacio bằng {1} ATK. Hiệu ứng này có thể kích hoạt mỗi {2} giây một lần.
+- Gây Sát Thương bằng Đòn ATK Mạnh sẽ triệu hồi Roccia thực hiện Xoáy Quái Dị và kéo các mục tiêu gần đó vào, gây tổng Sát Thương Havoc bằng {3} ATK. Hiệu ứng này có thể kích hoạt mỗi {4} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi các hiệu ứng kích hoạt từ Bond Fairy Tale's Finale (như Bouncy Brawl và Whimsical Whirl) được Khuếch Đại thêm {0}.</t>
+          <t>DMG gây ra bởi các hiệu ứng kích hoạt từ Bond Fairy Tale's Finale (như Bouncy Brawl và Whimsical Whirl) được Khuếch Đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Kích hoạt Đòn Mid-air Attack sẽ kích hoạt Không Kích, tấn công mục tiêu nhiều lần, mỗi lần gây Sát Thương Physical bằng {0} Attack. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Kích hoạt Đòn ATK Giữa Không sẽ kích hoạt Không Kích, tấn công mục tiêu nhiều lần, mỗi lần gây Sát Thương Vật Lý bằng {0} ATK. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
         </is>
       </c>
     </row>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Resonators ở trên không tăng cường khả năng kháng gián đoạn. Sát thương từ Đòn Hạ Gục Từ Trên Cao cũng tăng lên, tương đương {0} Tấn Công. Ngoài ra, đòn này còn giảm {1} Tấn Công của mục tiêu trong {2} giây.</t>
+          <t>Resonator ở trên không tăng cường khả năng kháng gián đoạn. Sát thương từ Đòn Hạ Gục Từ Trên Cao cũng tăng lên, tương đương {0} ATK. Ngoài ra, đòn này còn giảm {1} ATK của mục tiêu trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Resonators có khiên sẽ được ban cho Ý Chí Wall Thành: Mọi đòn tấn công gây thêm sát thương bằng {0} điểm khiên hiện tại. Hiệu ứng này kích hoạt tối đa một lần mỗi giây.</t>
+          <t>Resonator có khiên sẽ được ban cho Ý Chí Tường Thành: Mọi đòn tấn công gây thêm DMG bằng {0} điểm khiên hiện tại. Hiệu ứng này kích hoạt tối đa một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -15975,7 +15975,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Sát thương cộng thêm từ Ý Chí Bức Wall được Khuếch Đại thêm {0} và bỏ qua {1} Phòng Ngự của mục tiêu.</t>
+          <t>DMG cộng thêm từ Ý Chí Bức Tường được Khuếch Đại thêm {0} và bỏ qua {1} Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ kích hoạt hồi máu liên tục trong {0} giây tiếp theo, phục hồi tổng cộng {1} HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi {2} giây một lần.</t>
+          <t>Né tránh thành công sẽ kích hoạt hồi máu liên tục trong {0} giây tiếp theo, phục hồi tổng cộng {1} HP tối đa. Hiệu ứng này chỉ kích hoạt mỗi {2} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Khi hồi phục, tung Chiêu Wave lên 1 mục tiêu trong phạm vi, gây Sát Thương Physical bằng {0} Tấn Công của Resonator kích hoạt, kích hoạt mỗi {1} giây. Wave nhận thêm Sát Thương Bonus bằng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} Hiệu Quả Healing của Resonator kích hoạt.</t>
+          <t>Khi hồi phục, tung Chiêu Wave lên 1 mục tiêu trong phạm vi, gây Sát Thương Vật Lý bằng {0} ATK của Resonator kích hoạt, kích hoạt mỗi {1} giây. Wave nhận thêm Sát Thương Bonus bằng &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} Hiệu Quả Hồi Phục của Resonator kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Khi Sóng đánh trúng mục tiêu, nó gây thêm Sát Thương bằng {0} Tấn Công của Resonator đang kích hoạt.</t>
+          <t>Khi Sóng đánh trúng mục tiêu, nó gây thêm Sát Thương bằng {0} ATK của Resonator đang kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Trong chiến đấu, nhận Lương mỗi {0} giây. Lương sẽ bị tiêu hao khi Resonance Skill trúng mục tiêu, gây Sát Thương Physical bằng {1}% Tấn Công.</t>
+          <t>Trong chiến đấu, nhận Lương mỗi {0} giây. Lương sẽ bị tiêu hao khi Resonance Skill trúng mục tiêu, gây Sát Thương Vật Lý bằng {1}% ATK.</t>
         </is>
       </c>
     </row>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Trong chiến đấu, Đánh Dấu sẽ được áp dụng lên tất cả mục tiêu trong phạm vi mỗi {0} giây, tối đa 1 lớp. Gây sát thương lên mục tiêu mang Đánh Dấu sẽ tiêu hao 1 lớp Đánh Dấu để kích hoạt Hoàn Trả, gây Sát Thương Physical bằng {1}% Tấn Công.</t>
+          <t>Trong chiến đấu, Đánh Dấu sẽ được áp dụng lên tất cả mục tiêu trong phạm vi mỗi {0} giây, tối đa 1 lớp. Gây DMG lên mục tiêu mang Đánh Dấu sẽ tiêu hao 1 lớp Đánh Dấu để kích hoạt Hoàn Trả, gây Sát Thương Vật Lý bằng {1}% ATK.</t>
         </is>
       </c>
     </row>
@@ -16365,7 +16365,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi Wage được Khuếch Đại thêm {0}.</t>
+          <t>DMG gây ra bởi Wage được Khuếch Đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Mỗi lần kích hoạt Hoàn Trả sẽ giảm Thời Gian Cooldown của Resonance Skill và Resonance Liberation đi {0}. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
+          <t>Mỗi lần kích hoạt Hoàn Trả sẽ giảm Thời gian hồi Chiêu của Resonance Skill và Resonance Liberation đi {0}. Hiệu ứng này chỉ có thể kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -16498,10 +16498,10 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Attack của tất cả Resonators trong đội tăng {0}. Khi Resonators với Mô Hình Liên Kết Công Dân gây Sát Thương Basic Attack/Heavy Attack/Resonance Skill, có {1} xác suất kích hoạt một trong các hiệu ứng sau:
-- Summon {2} Đèn Bão để tấn công mục tiêu, mỗi chiếc gây Aero DMG bằng {3} Attack, kích hoạt mỗi {4} giây.
-- Summon {5} Nguồn Năng Lượng để tấn công mục tiêu, mỗi chiếc gây Electro DMG bằng {6} Attack, kích hoạt mỗi {7} giây.
-- Summon và phóng {8} Wheel Công Dân xoay tròn rồi quay lại sau {9} giây. Mỗi bánh xe thực hiện {10} cú đánh khi xoay và thêm &lt;SapTag=11&gt;{11}&lt;/SapTag&gt; {Cus:Sap,S=cú đánh P=cú đánh SapTag=11} khi bay về. Mỗi cú đánh gây Spectro DMG bằng {12} Attack. Hiệu ứng này kích hoạt mỗi {13} giây.</t>
+          <t>ATK của tất cả Resonator trong đội tăng {0}. Khi Resonator với Mô Hình Liên Kết Công Dân gây Sát Thương Basic Attack/Heavy Attack/Resonance Skill, có {1} xác suất kích hoạt một trong các hiệu ứng sau:
+- Triệu hồi {2} Đèn Bão để tấn công mục tiêu, mỗi chiếc gây Sát Thương Aero bằng {3} ATK, kích hoạt mỗi {4} giây.
+- Triệu hồi {5} Nguồn Năng Lượng để tấn công mục tiêu, mỗi chiếc gây Sát Thương Electro bằng {6} ATK, kích hoạt mỗi {7} giây.
+- Triệu hồi và phóng {8} Bánh Xe Công Dân xoay tròn rồi quay lại sau {9} giây. Mỗi bánh xe thực hiện {10} cú đánh khi xoay và thêm &lt;SapTag=11&gt;{11}&lt;/SapTag&gt; {Cus:Sap,S=cú đánh P=cú đánh SapTag=11} khi bay về. Mỗi cú đánh gây Sát Thương Spectro bằng {12} ATK. Hiệu ứng này kích hoạt mỗi {13} giây.</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       <c r="M244" t="inlineStr">
         <is>
           <t>Khi Resonator sở hữu Mô Hình Liên Kết Công Dân thi triển Resonance Liberation, kích hoạt hiệu ứng sau:
-Summon &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; Lốc Xoáy {Cus:Sap,S=Tornado P=Tornados SapTag=0} tấn công mục tiêu {1} lần, mỗi đòn gây Sát Thương Gió bằng {2} Sức Tấn Công. Sau đó, nó sẽ tấn công thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, mỗi đòn gây sát thương bằng {4} Sức Tấn Công. Cuối cùng, triệu hồi {5} Quả Cầu Tuyết Công Dân, mỗi quả gây Sát Thương Băng bằng {6} Sức Tấn Công. Khi quả cầu cuối cùng trúng đích, nó sẽ gây Sát Thương Băng bằng {7} Sức Tấn Công và hồi {8} HP tối đa cho Resonator đang hoạt động.</t>
+Triệu hồi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; Lốc Xoáy {Cus:Sap,S=Tornado P=Tornados SapTag=0} tấn công mục tiêu {1} lần, mỗi đòn gây Sát Thương Gió bằng {2} Sức ATK. Sau đó, nó sẽ tấn công thêm &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}, mỗi đòn gây DMG bằng {4} Sức ATK. Cuối cùng, triệu hồi {5} Quả Cầu Tuyết Công Dân, mỗi quả gây Sát Thương Băng bằng {6} Sức ATK. Khi quả cầu cuối cùng trúng đích, nó sẽ gây Sát Thương Băng bằng {7} Sức ATK và hồi {8} HP tối đa cho Resonator đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Sát thương Resonance Liberation được Khuếch Đại bởi {0}. Khi sử dụng Resonance Liberation, kích hoạt Good Citizen, tăng Tấn Công, Phòng Ngự, HP tối đa, Crit. Rate và Crit. DMG cho tất cả Resonators trong đội lên {1} trong {3} giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>DMG Resonance Liberation được Khuếch Đại bởi {0}. Khi sử dụng Resonance Liberation, kích hoạt Good Citizen, tăng ATK, Phòng Ngự, HP tối đa, Crit. Rate và Crit. DMG cho tất cả Resonator trong đội lên {1} trong {3} giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi tất cả Resonators trong đội tăng thêm {1} cho mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Resonators P=Resonators SapTag=0} có Bond Model Citizen trong đội.</t>
+          <t>DMG gây ra bởi tất cả Resonator trong đội tăng thêm {1} cho mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Resonator P=Resonator SapTag=0} có Bond Model Citizen trong đội.</t>
         </is>
       </c>
     </row>
@@ -16763,7 +16763,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Resonators sở hữu Liên Kết "Khách Lạ Tại Vùng Siêu Tần" sẽ nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Đông Cứng Thời Gian mỗi khi sử dụng Resonance Skill trong chiến đấu. Mỗi điểm tăng {1} Sát Thương Resonance Skill trong {4} giây, tối đa {3} điểm. Hiệu ứng này kích hoạt tối đa một lần mỗi {2} giây.</t>
+          <t>Resonator sở hữu Liên Kết "Khách Lạ Tại Vùng Siêu Tần" sẽ nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Đông Cứng Thời Gian mỗi khi sử dụng Resonance Skill trong chiến đấu. Mỗi điểm tăng {1} Sát Thương Resonance Skill trong {4} giây, tối đa {3} điểm. Hiệu ứng này kích hoạt tối đa một lần mỗi {2} giây.</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Khi Resonators sở hữu Mô Hình Liên Kết Du Khách Vùng Siêu Tần thi triển Resonance Liberation, Crit. DMG của kỹ năng Resonance tiếp theo do tất cả Resonators trong đội thi triển sẽ tăng thêm {0} trong {2} giây, có thể cộng dồn tối đa {1} lần.</t>
+          <t>Khi Resonator sở hữu Mô Hình Liên Kết Du Khách Vùng Siêu Tần thi triển Resonance Liberation, Crit. DMG của kỹ năng Cộng Hưởng tiếp theo do tất cả Resonator trong đội thi triển sẽ tăng thêm {0} trong {2} giây, có thể cộng dồn tối đa {1} lần.</t>
         </is>
       </c>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Resonators sở hữu Liên Kết "Khách Lạ Tại Vùng Siêu Tần" sẽ được tăng {0} Tấn Công.</t>
+          <t>Resonator sở hữu Liên Kết "Khách Lạ Tại Vùng Siêu Tần" sẽ được tăng {0} ATK.</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ triệu hồi một Cổng Data phóng {0} Quả Bom Data vào mục tiêu, mỗi quả gây sát thương bằng {1} Tấn Công. Hiệu ứng này chỉ kích hoạt mỗi {2} giây một lần.</t>
+          <t>Né tránh thành công sẽ triệu hồi một Cổng Dữ Liệu phóng {0} Quả Bom Dữ Liệu vào mục tiêu, mỗi quả gây DMG bằng {1} ATK. Hiệu ứng này chỉ kích hoạt mỗi {2} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Dodge Counter triệu hồi thêm một Cổng Data khi trúng đích, phóng {0} Quả Bom Data vào mục tiêu, mỗi quả gây sát thương bằng {1} Tấn Công. Hiệu ứng này chỉ kích hoạt một lần mỗi {2} giây.</t>
+          <t>Dodge Counter triệu hồi thêm một Cổng Dữ Liệu khi trúng đích, phóng {0} Quả Bom Dữ Liệu vào mục tiêu, mỗi quả gây DMG bằng {1} ATK. Hiệu ứng này chỉ kích hoạt một lần mỗi {2} giây.</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi Data Bomb được Khuếch Đại thêm {0}.</t>
+          <t>DMG gây ra bởi Data Bomb được Khuếch Đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Với mỗi Resonator có mối liên kết Rebel of the Mercury Palace trong đội, Resonator hiện tại sẽ được tăng {0} Phòng Ngự và HP tối đa.</t>
+          <t>Với mỗi Resonator có mối liên kết Kẻ Nổi Loạn Cung Thủy Ngân trong đội, Resonator hiện tại sẽ được tăng {0} Phòng Ngự và HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill, Resonance Liberation, Dodge Counter và Dodge thành công sẽ nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Cờ Khởi Nghĩa, kích hoạt mỗi {1} giây. Khi đạt {2} điểm Cờ Khởi Nghĩa, tất cả điểm sẽ bị xóa để kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=phát P=phát SapTag=3} Đại Bác Ngu Ngốc, gây Sát Thương Physical bằng {4} Tấn Công.</t>
+          <t>Kích hoạt Resonance Skill, Resonance Liberation, Dodge Counter Tránh và Né Tránh thành công sẽ nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Cờ Khởi Nghĩa, kích hoạt mỗi {1} giây. Khi đạt {2} điểm Cờ Khởi Nghĩa, tất cả điểm sẽ bị xóa để kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=phát P=phát SapTag=3} Đại Bác Ngu Ngốc, gây Sát Thương Vật Lý bằng {4} ATK.</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Khi Fool's Cannon gây Sát Thương, Crit. DMG của tất cả Resonators trong đội sẽ tăng {0} trong {1} giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Khi Fool's Cannon gây Sát Thương, Crit. DMG của tất cả Resonator trong đội sẽ tăng {0} trong {1} giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Normal Attack và Heavy Attack sẽ cấp &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Cờ Khởi Nghĩa khi trúng đích, kích hoạt mỗi {1} giây một lần.</t>
+          <t>Đòn Normal Attack và Đòn Heavy Attack sẽ cấp &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} Cờ Khởi Nghĩa khi trúng đích, kích hoạt mỗi {1} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Khi trúng Bong Bóng Kiềm Chế, &lt;color=#b72924ff&gt;DEF is reduced by 100%&lt;/color&gt;.</t>
+          <t>Khi trúng Bong Bóng Kiềm Chế, &lt;color=#b72924ff&gt;Phòng Ngự của Resonator giảm 100%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Bong bóng Burst gây &lt;color=#b72924ff&gt;100% more DMG&lt;/color&gt;.</t>
+          <t>Bong bóng Kích Hoạt gây &lt;color=#b72924ff&gt;thêm 100% Sát Thương&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Resonators trúng Bong Bóng Nổ sẽ bị &lt;color=#b72924ff&gt;have their ATK reduced by 80%&lt;/color&gt; trong &lt;color=#b72924ff&gt;15s&lt;/color&gt;.</t>
+          <t>Resonator trúng Bong Bóng Nổ sẽ bị &lt;color=#b72924ff&gt;giảm 80% ATK&lt;/color&gt; trong &lt;color=#b72924ff&gt;15 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Resonators hoặc kẻ địch trúng Bong Bóng Healing sẽ &lt;color=#5cc96aff&gt;have their ATK increased by 15%&lt;/color&gt; trong &lt;color=#5cc96aff&gt;15s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#5cc96aff&gt;5 lần&lt;/color&gt;.</t>
+          <t>Resonator hoặc kẻ địch trúng Bong Bóng Hồi Phục sẽ &lt;color=#5cc96aff&gt;tăng 15% ATK&lt;/color&gt; trong &lt;color=#5cc96aff&gt;15 giây&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#5cc96aff&gt;5 lần&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Resonators hoặc kẻ địch trúng Bong Bóng Healing sẽ &lt;color=#5cc96aff&gt;have their DEF increased by 15%&lt;/color&gt; trong &lt;color=#5cc96aff&gt;15s&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#5cc96aff&gt;5 lần&lt;/color&gt;.</t>
+          <t>Resonator hoặc kẻ địch trúng Bong Bóng Hồi Phục sẽ &lt;color=#5cc96aff&gt;tăng 15% Phòng Ngự&lt;/color&gt; trong &lt;color=#5cc96aff&gt;15 giây&lt;/color&gt;, có thể chồng chất lên đến &lt;color=#5cc96aff&gt;5 lần&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Kẻ địch trở nên &lt;color=#b72924ff&gt;more aggressive&lt;/color&gt;.</t>
+          <t>Kẻ địch trở nên &lt;color=#b72924ff&gt;hung hãn hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Feilian Beringal triệu hồi &lt;color=#b72924ff&gt;1&lt;/color&gt; &lt;color=#b72924ff&gt;Shock Stump&lt;/color&gt; trên chiến trường lần đầu &lt;color=#b72924ff&gt;its HP drops below 95%/75%/55%/30%&lt;/color&gt;. Gốc Cây Sốc Điện gây sát thương cho Resonators xung quanh bằng &lt;color=#b72924ff&gt;20% of their Max HP&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;15s&lt;/color&gt;.</t>
+          <t>Feilian Beringal triệu hồi &lt;color=#b72924ff&gt;1&lt;/color&gt; &lt;color=#b72924ff&gt;Gốc Cây Sốc Điện&lt;/color&gt; trên chiến trường lần đầu &lt;color=#b72924ff&gt;HP của nó giảm xuống dưới 95%/75%/55%/30%&lt;/color&gt;. Gốc Cây Sốc Điện gây DMG cho Resonator xung quanh bằng &lt;color=#b72924ff&gt;20% HP tối đa&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;15 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Feilian Beringal triệu hồi &lt;color=#b72924ff&gt;1&lt;/color&gt; &lt;color=#b72924ff&gt;Healing Stump&lt;/color&gt; trên chiến trường lần đầu &lt;color=#b72924ff&gt;its HP drops below 95%/75%/55%/30%&lt;/color&gt;. Gốc Cây Healing phục hồi HP cho kẻ địch xung quanh &lt;color=#b72924ff&gt;5% of their Max HP&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;15s&lt;/color&gt;.</t>
+          <t>Feilian Beringal triệu hồi &lt;color=#b72924ff&gt;1&lt;/color&gt; &lt;color=#b72924ff&gt;Gốc Cây Hồi Phục&lt;/color&gt; trên chiến trường lần đầu &lt;color=#b72924ff&gt;HP của nó giảm xuống dưới 95%/75%/55%/30%&lt;/color&gt;. Gốc Cây Hồi Phục phục hồi HP cho kẻ địch xung quanh &lt;color=#b72924ff&gt;5% HP tối đa&lt;/color&gt; mỗi &lt;color=#b72924ff&gt;15 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17937,8 +17937,8 @@
       <c r="M265" t="inlineStr">
         <is>
           <t>Kỹ năng mới cho Queen of the Night!
-&lt;color=Highlight&gt;[Burst Bubble]&lt;/color&gt;: Bong bóng nổ sẽ bám theo Resonators và phát nổ sau một khoảng thời gian ngắn, gây sát thương cho bản thân (&lt;color=Highlight&gt;2% of her Max HP&lt;/color&gt;) hoặc Resonators và kẻ địch khác (&lt;color=Highlight&gt;10% of their Max HP&lt;/color&gt;).
-&lt;color=Highlight&gt;[Healing Bubble]&lt;/color&gt;: Bong bóng hồi phục sẽ bám theo Queen of the Night và phục hồi HP cho bản thân (&lt;color=Highlight&gt;2% of her Max HP&lt;/color&gt;) hoặc Resonators và kẻ địch khác (&lt;color=Highlight&gt;10% of their Max HP&lt;/color&gt;).
+&lt;color=Highlight&gt;[Burst Bubble]&lt;/color&gt;: Bong bóng nổ sẽ bám theo Resonator và phát nổ sau một khoảng thời gian ngắn, gây sát thương cho bản thân (&lt;color=Highlight&gt;2% HP tối đa&lt;/color&gt;) hoặc Resonator và kẻ địch khác (&lt;color=Highlight&gt;10% HP tối đa&lt;/color&gt;).
+&lt;color=Highlight&gt;[Healing Bubble]&lt;/color&gt;: Bong bóng hồi phục sẽ bám theo Queen of the Night và phục hồi HP cho bản thân (&lt;color=Highlight&gt;2% HP tối đa&lt;/color&gt;) hoặc Resonator và kẻ địch khác (&lt;color=Highlight&gt;10% HP tối đa&lt;/color&gt;).
 Ác ý đang dần gặm nhấm tâm trí Queen of the Night, thúc đẩy cô tràn ngập Biển Mây bằng những đợt thủy triều hỗn loạn. Nhưng với tư cách là một sinh thể được Sentinel khai sáng và giao phó nhiệm vụ thanh lọc những tần số độc hại, có lẽ vẫn còn chút tỉnh táo trong cô để giúp cậu chấm dứt thảm họa này.</t>
         </is>
       </c>
@@ -18008,8 +18008,8 @@
       <c r="M266" t="inlineStr">
         <is>
           <t>Đấu trường Fleurdelys đã được tái cấu trúc!
-&lt;color=Highlight&gt;[Shielded Crown]&lt;/color&gt;: Khi HP của Fleurdelys lần đầu giảm xuống dưới &lt;color=Highlight&gt;20%&lt;/color&gt;, cô sẽ nhận được &lt;color=Highlight&gt;Shield equal to 50% of her Max HP&lt;/color&gt;.
-&lt;color=Highlight&gt;[Realm]&lt;/color&gt;: Đấu trường của Fleurdelys luôn biến đổi. Resonators nhận được hiệu ứng tương ứng khi đứng ở các vùng khác nhau. Khi ở &lt;color=Highlight&gt;Realm of Spear&lt;/color&gt; tại trung tâm đấu trường, Resonators &lt;color=Highlight&gt;deal 30% more DMG to shielded enemies&lt;/color&gt;. Khi ở &lt;color=Highlight&gt;Realm of Shield&lt;/color&gt; bao trùm toàn đấu trường, Resonators &lt;color=Highlight&gt;gain a Shield equal to 10% of their Max HP every 5s&lt;/color&gt;, không cộng dồn. Khi ở &lt;color=Highlight&gt;Realm of Resonance&lt;/color&gt; di chuyển, tất cả Resonators trong đội &lt;color=Highlight&gt;restore 10 points of their Resonance Energy each second&lt;/color&gt;.
+&lt;color=Highlight&gt;[Vương Miện Khiên]&lt;/color&gt;: Khi HP của Fleurdelys lần đầu giảm xuống dưới &lt;color=Highlight&gt;20%&lt;/color&gt;, cô sẽ nhận được &lt;color=Highlight&gt;Khiên tương đương 50% HP tối đa&lt;/color&gt;.
+&lt;color=Highlight&gt;[Cõi]&lt;/color&gt;: Đấu trường của Fleurdelys luôn biến đổi. Resonator nhận được hiệu ứng tương ứng khi đứng ở các vùng khác nhau. Khi ở &lt;color=Highlight&gt;Cõi Thương&lt;/color&gt; tại trung tâm đấu trường, Resonator &lt;color=Highlight&gt;gây thêm 30% DMG lên kẻ địch có khiên&lt;/color&gt;. Khi ở &lt;color=Highlight&gt;Cõi Khiên&lt;/color&gt; bao trùm toàn đấu trường, Resonator &lt;color=Highlight&gt;nhận được Khiên tương đương 10% HP tối đa mỗi 5 giây&lt;/color&gt;, không cộng dồn. Khi ở &lt;color=Highlight&gt;Cõi Cộng Hưởng&lt;/color&gt; di chuyển, tất cả Resonator trong đội &lt;color=Highlight&gt;hồi phục 10 điểm Resonance Energy mỗi giây&lt;/color&gt;.
 Hai thế lực đối lập, Sentinel và Threnodian, đã khắc sâu những tần số riêng biệt vào bản chất của Avinoleum. Nơi đây, những bất thường khó lường xuất hiện rồi biến mất không báo trước. Hãy cảnh giác trong môi trường luôn thay đổi và chuẩn bị tinh thần đối mặt với những cơn bão gươm đao vang vọng không ngừng.</t>
         </is>
       </c>
@@ -18081,10 +18081,10 @@
       <c r="M267" t="inlineStr">
         <is>
           <t>Hỗ trợ từ bầy đàn cho Feilian Beringal!
-&lt;color=Highlight&gt;Wolf Blood&lt;/color&gt;: Feilian Beringal triệu hồi một &lt;color=Highlight&gt;Havoc Dreadmane&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;95%&lt;/color&gt;, giúp Feilian Beringal hồi phục &lt;color=Highlight&gt;1% of its Max HP&lt;/color&gt; mỗi khi gây sát thương.
-&lt;color=Highlight&gt;Bear Will&lt;/color&gt;: Feilian Beringal triệu hồi một &lt;color=Highlight&gt;Spearback&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;75%&lt;/color&gt;. Spearback hy sinh Concerto Vibrancy của chính mình để hồi phục &lt;color=Highlight&gt;5% of Feilian Beringal's Max Vibration Strength&lt;/color&gt; của Feilian Beringal mỗi giây.
-&lt;color=Highlight&gt;Ape Spirit&lt;/color&gt;: Feilian Beringal triệu hồi một &lt;color=Highlight&gt;Hoochief Menace&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;55%&lt;/color&gt;. Hoochief Menace hy sinh HP của mình để hồi phục &lt;color=Highlight&gt;0.2% of Feilian Beringal's Max HP&lt;/color&gt; của Feilian Beringal mỗi giây.
-&lt;color=Highlight&gt;Group Aid&lt;/color&gt;: Feilian Beringal triệu hồi lại &lt;color=Highlight&gt;Havoc Dreadmane and Spearback&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;30%&lt;/color&gt;. Chúng cung cấp các hiệu ứng tăng cường tương ứng cho Feilian Beringal.
+&lt;color=Highlight&gt;HP Sói&lt;/color&gt;: Feilian Beringal triệu hồi một &lt;color=Highlight&gt;Havoc Dreadmane&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;95%&lt;/color&gt;, giúp Feilian Beringal hồi phục &lt;color=Highlight&gt;1% HP tối đa&lt;/color&gt; mỗi khi gây sát thương.
+&lt;color=Highlight&gt;Ý Chí Gấu&lt;/color&gt;: Feilian Beringal triệu hồi một &lt;color=Highlight&gt;Spearback&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;75%&lt;/color&gt;. Spearback hy sinh Sức Mạnh Rung Động của chính mình để hồi phục &lt;color=Highlight&gt;5% Sức Mạnh Rung Động tối đa&lt;/color&gt; của Feilian Beringal mỗi giây.
+&lt;color=Highlight&gt;Tinh Linh Khỉ&lt;/color&gt;: Feilian Beringal triệu hồi một &lt;color=Highlight&gt;Hoochief Menace&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;55%&lt;/color&gt;. Hoochief Menace hy sinh HP của mình để hồi phục &lt;color=Highlight&gt;0.2% HP tối đa&lt;/color&gt; của Feilian Beringal mỗi giây.
+&lt;color=Highlight&gt;Hỗ Trợ Đoàn Thể&lt;/color&gt;: Feilian Beringal triệu hồi lại &lt;color=Highlight&gt;Havoc Dreadmane và Spearback&lt;/color&gt; trợ chiến lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;30%&lt;/color&gt;. Chúng cung cấp các hiệu ứng tăng cường tương ứng cho Feilian Beringal.
 Với sự hỗ trợ của các Tacet Discord khác, Feilian Beringal đã giải phóng cơn thịnh nộ tần số dữ dội, đẩy bầy đàn tiến về Ragunna trong cuộc bành trướng không ngừng. Để chấm dứt cuộc tấn công này, ngươi phải cắt đứt mối liên kết của con thú với đồng minh!</t>
         </is>
       </c>
@@ -18156,13 +18156,13 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return giờ đây sử dụng dữ liệu để triệu hồi Tacet Discord!
-&lt;color=Highlight&gt;Lampylumen Myriad&lt;/color&gt;: Fallacy of Không Return triệu hồi Lampylumen Myriad lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;95%&lt;/color&gt; và nhận được 
-&lt;color=Highlight&gt;Shield equal to 80% of its own Max HP&lt;/color&gt; của bản thân. Tiêu diệt Lampylumen Myriad sẽ &lt;color=Highlight&gt;removes the Shield&lt;/color&gt; của Fallacy of Không Return và &lt;color=Highlight&gt;restores all Resonance Energy&lt;/color&gt; cho Resonators. Glacio RES của Lampylumen Myriad bị giảm.
-&lt;color=Highlight&gt;Inferno Rider&lt;/color&gt;: Fallacy of Không Return triệu hồi Inferno Rider lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;65%&lt;/color&gt; và nhận được 
-&lt;color=Highlight&gt;Shield equal to 80% of its own Max HP&lt;/color&gt; của bản thân. Tiêu diệt Inferno Rider sẽ &lt;color=Highlight&gt;removes the Shield&lt;/color&gt; của Fallacy of Không Return và &lt;color=Highlight&gt;restores all Resonance Energy&lt;/color&gt; cho Resonators. Fusion RES của Inferno Rider bị giảm.
-&lt;color=Highlight&gt;Impermanence Heron&lt;/color&gt;: Fallacy of Không Return triệu hồi Impermanence Heron lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;35%&lt;/color&gt; và nhận được &lt;color=Highlight&gt;Shield equal to 80% of its own Max HP&lt;/color&gt; của bản thân. Tiêu diệt Impermanence Heron sẽ &lt;color=Highlight&gt;removes the Shield&lt;/color&gt; của Fallacy of Không Return và &lt;color=Highlight&gt;restores all Resonance Energy&lt;/color&gt; cho Resonators. Havoc RES của Impermanence Heron bị giảm.
-Các mã lỗi trong Ma Trận Sao đã làm suy yếu hệ thống phòng thủ của Tethys trong vụ rò rỉ dữ liệu. Dựa trên Fallacy of Không Return như một khung sườn, chúng đã tạo ra các Tacet Discord cấp Overlord để tự vệ. Để chấm dứt cuộc khủng hoảng này, những Tacet Discord được rèn từ dữ liệu này phải bị tiêu diệt.</t>
+          <t>Fallacy of No Return giờ đây sử dụng dữ liệu để triệu hồi Tacet Discord!
+&lt;color=Highlight&gt;Lampylumen Myriad&lt;/color&gt;: Fallacy of No Return triệu hồi Lampylumen Myriad lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;95%&lt;/color&gt; và nhận được 
+&lt;color=Highlight&gt;Khiên tương đương 80% HP tối đa&lt;/color&gt; của bản thân. Tiêu diệt Lampylumen Myriad sẽ &lt;color=Highlight&gt;phá hủy Khiên&lt;/color&gt; của Fallacy of No Return và &lt;color=Highlight&gt;khôi phục toàn bộ Resonance Energy&lt;/color&gt; cho Resonator. Kháng Glacio của Lampylumen Myriad bị giảm.
+&lt;color=Highlight&gt;Inferno Rider&lt;/color&gt;: Fallacy of No Return triệu hồi Inferno Rider lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;65%&lt;/color&gt; và nhận được 
+&lt;color=Highlight&gt;Khiên tương đương 80% HP tối đa&lt;/color&gt; của bản thân. Tiêu diệt Inferno Rider sẽ &lt;color=Highlight&gt;phá hủy Khiên&lt;/color&gt; của Fallacy of No Return và &lt;color=Highlight&gt;khôi phục toàn bộ Resonance Energy&lt;/color&gt; cho Resonator. Kháng Fusion của Inferno Rider bị giảm.
+&lt;color=Highlight&gt;Impermanence Heron&lt;/color&gt;: Fallacy of No Return triệu hồi Impermanence Heron lần đầu khi HP giảm xuống dưới &lt;color=Highlight&gt;35%&lt;/color&gt; và nhận được &lt;color=Highlight&gt;Khiên tương đương 80% HP tối đa&lt;/color&gt; của bản thân. Tiêu diệt Impermanence Heron sẽ &lt;color=Highlight&gt;phá hủy Khiên&lt;/color&gt; của Fallacy of No Return và &lt;color=Highlight&gt;khôi phục toàn bộ Resonance Energy&lt;/color&gt; cho Resonator. Kháng Havoc của Impermanence Heron bị giảm.
+Các mã lỗi trong Ma Trận Sao đã làm suy yếu hệ thống phòng thủ của Tethys trong vụ rò rỉ dữ liệu. Dựa trên Fallacy of No Return như một khung sườn, chúng đã tạo ra các Tacet Discord cấp Overlord để tự vệ. Để chấm dứt cuộc khủng hoảng này, những Tacet Discord được rèn từ dữ liệu này phải bị tiêu diệt.</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Tất cả kẻ địch có &lt;color=#b72924ff&gt;Max HP increased by 200%&lt;/color&gt; và &lt;color=#b72924ff&gt;ATK increased by 50%&lt;/color&gt;.</t>
+          <t>Tất cả kẻ địch có &lt;color=#b72924ff&gt;HP tối đa tăng 200%&lt;/color&gt; và &lt;color=#b72924ff&gt;ATK tăng 50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Tất cả kẻ địch có &lt;color=#b72924ff&gt;Max HP increased by 350%&lt;/color&gt; và &lt;color=#b72924ff&gt;ATK increased by 100%&lt;/color&gt;.</t>
+          <t>Tất cả kẻ địch có &lt;color=#b72924ff&gt;HP tối đa tăng 350%&lt;/color&gt; và &lt;color=#b72924ff&gt;ATK tăng 100%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18357,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Tất cả kẻ địch có &lt;color=#b72924ff&gt;Max HP increased by 500%&lt;/color&gt; và &lt;color=#b72924ff&gt;ATK increased by 150%&lt;/color&gt;.</t>
+          <t>Tất cả kẻ địch có &lt;color=#b72924ff&gt;HP tối đa tăng 500%&lt;/color&gt; và &lt;color=#b72924ff&gt;ATK tăng 150%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>&lt;color=#b72924ff&gt;Falling Blade is summoned five times&lt;/color&gt; tại vị trí của Resonator đang hoạt động mỗi &lt;color=#b72924ff&gt;8s&lt;/color&gt;, mỗi lần gây sát thương bằng &lt;color=#b72924ff&gt;5% of their Max HP&lt;/color&gt; của họ.</t>
+          <t>&lt;color=#b72924ff&gt;Falling Blade được triệu hồi năm lần&lt;/color&gt; tại vị trí của Resonator đang hoạt động mỗi &lt;color=#b72924ff&gt;8 giây&lt;/color&gt;, mỗi lần gây DMG bằng &lt;color=#b72924ff&gt;5% HP tối đa&lt;/color&gt; của họ.</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;When Resonators are in Realm of Resonance&lt;/color&gt;, tất cả Resonators trong đội sẽ chịu sát thương bằng &lt;color=#b72924ff&gt;2% of their Max HP&lt;/color&gt; mỗi giây.</t>
+          <t>Khi &lt;color=#b72924ff&gt;Resonator ở trong Cõi Giao Hưởng&lt;/color&gt;, tất cả Resonator trong đội sẽ chịu DMG bằng &lt;color=#b72924ff&gt;2% HP tối đa&lt;/color&gt; mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#b72924ff&gt;When Resonators enter Realm of Resonance&lt;/color&gt;, Fleurdelys ngay lập tức nhận một Lớp Shield tương đương &lt;color=#b72924ff&gt;10% of her Max HP&lt;/color&gt;.</t>
+          <t>Khi &lt;color=#b72924ff&gt;Resonator bước vào Cõi Giao Hưởng&lt;/color&gt;, Fleurdelys ngay lập tức nhận một Lớp Khiên tương đương &lt;color=#b72924ff&gt;10% HP tối đa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18617,7 +18617,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Resonators trong đội &lt;color=#b72924ff&gt;take 100% more DMG&lt;/color&gt;. Khi Cấp Độ Giao Hưởng đạt hoặc vượt &lt;color=#5cc96aff&gt;SS&lt;/color&gt;, &lt;color=#5cc96aff&gt;HP will not drop below 1%&lt;/color&gt;.</t>
+          <t>Resonator trong đội &lt;color=#b72924ff&gt;chịu nhiều hơn 100% DMG&lt;/color&gt;. Khi Cấp Độ Giao Hưởng đạt hoặc vượt &lt;color=#5cc96aff&gt;SS&lt;/color&gt;, &lt;color=#5cc96aff&gt;HP của Resonator sẽ không bao giờ xuống dưới 1%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18682,7 +18682,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy Sự Trao đổi làm khả năng cốt lõi. Một số Resonator có thể thay đổi giấc mơ thông qua Trao đổi. Sau khi ở lại chiến trường đủ số ngày nhất định, chúng sẽ tự loại bỏ và để lại nhiều hiệu ứng tăng cường khác nhau.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy Sự Trao Đổi làm khả năng cốt lõi. Một số Cộng Hưởng Giả có thể thay đổi giấc mơ thông qua Trao Đổi. Sau khi ở lại chiến trường đủ số ngày nhất định, chúng sẽ tự loại bỏ và để lại nhiều hiệu ứng tăng cường khác nhau.</t>
         </is>
       </c>
     </row>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy Sự Kết Hợp làm khả năng cốt lõi. Một số Resonator có thể gây ra biến động trong giấc mơ thông qua Sự Kết Hợp. Khi đạt đủ điều kiện, các Resonator liền kề sẽ hòa nhập thành một Resonator hoàn toàn mới và mang lại nhiều hiệu ứng tăng cường khác nhau.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy Sự Kết Hợp làm khả năng cốt lõi. Một số Cộng Hưởng Giả có thể gây ra biến động trong giấc mơ thông qua Sự Kết Hợp. Khi đạt đủ điều kiện, các Cộng Hưởng Giả liền kề sẽ hòa nhập thành một Cộng Hưởng Giả hoàn toàn mới và mang lại nhiều hiệu ứng tăng cường khác nhau.</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Thời Gian Dài Nhất</t>
+          <t>Thời Gian Duy Trì Lâu Nhất</t>
         </is>
       </c>
     </row>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Thời Gian Exploration</t>
+          <t>Thời Gian Thám Hiểm</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Kẻ địch bị đánh bại</t>
+          <t>Đã tiêu diệt kẻ địch</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19072,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tip của Namipon: Phá vỡ Nước Suối Lấp Lánh của Namipon để hồi phục Độ Stability.</t>
+          <t>Mẹo của Namipon: Phá vỡ Nước Suối Lấp Lánh của Namipon để hồi phục Độ Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tip của Namipon: Nâng cấp Namipon Badge để tăng Độ Stability Tối Đa.</t>
+          <t>Mẹo của Namipon: Nâng cấp Huy Hiệu Namipon để tăng Độ Ổn Định Tối Đa.</t>
         </is>
       </c>
     </row>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#d5aa29&gt;{0}&lt;/color&gt; × {1} để nâng cấp Namipon Badge lên Lv. &lt;color=#d5aa29&gt;{2}&lt;/color&gt;?
+          <t>Dùng &lt;color=#d5aa29&gt;{0}&lt;/color&gt; × {1} để nâng cấp Huy Hiệu Namipon lên Lv. &lt;color=#d5aa29&gt;{2}&lt;/color&gt;?
 Độ Bền Tối Đa: &lt;color=#d5aa29&gt;{3}&lt;/color&gt; &gt;&gt; &lt;color=#d5aa29&gt;{4}&lt;/color&gt;</t>
         </is>
       </c>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Enemies &amp; Dư Âm New</t>
+          <t>Kẻ Thù &amp; Dư Âm Mới</t>
         </is>
       </c>
     </row>
@@ -19399,7 +19399,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Enemies &amp; Dư Âm New</t>
+          <t>Kẻ Thù &amp; Dư Âm Mới</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Kẻ địch: Reactor Husk</t>
+          <t>Kẻ địch: Xác Reactor</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Summon Hyvatia tấn công kẻ địch, gây Spectro DMG và tăng Sát Thương Toàn Thuộc Tính cho Intro Skill của Resonator tiếp theo.</t>
+          <t>Triệu hồi Hyvatia tấn công kẻ địch, gây DMG Spectro và tăng Sát Thương Toàn Thuộc Tính cho Kỹ Năng Intro của Resonator tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -19725,8 +19725,8 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Biến thành Reactor Husk để tấn công kẻ địch, gây Fusion DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận Tăng Tốc Energy Regen.</t>
+          <t>Biến hình thành Reactor Husk để tấn công kẻ địch, gây Sát Thương Fusion.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận Tăng Tốc Hồi Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG</t>
+          <t>Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Kết tăng Tấn Công cho Resonator kế tiếp và trao thêm hiệu ứng tăng Tấn Công dựa trên Tăng Cường Phá Nhịp của họ.</t>
+          <t>Kích hoạt Kỹ Năng Kết tăng ATK cho Resonator kế tiếp và trao thêm hiệu ứng tăng ATK dựa trên Tăng Cường Phá Nhịp của họ.</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Hồi phục đồng minh sẽ tăng Tấn Công cho Resonators trong đội dựa trên tỷ lệ Dị Tần Tích Lũy hiện tại.</t>
+          <t>Hồi phục đồng minh sẽ tăng ATK cho Resonator trong đội dựa trên tỷ lệ Dị Tần Tích Lũy hiện tại.</t>
         </is>
       </c>
     </row>
@@ -19986,7 +19986,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Tăng Spectro DMG</t>
+          <t>Sát Thương Spectro+</t>
         </is>
       </c>
     </row>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Basic Attack sẽ tăng Spectro DMG, có thể tích lũy. Khi đạt tối đa, sử dụng Resonance Liberation sẽ tăng Sát Thương Basic Attack.</t>
+          <t>Gây Sát Thương Basic Attack sẽ tăng Sát Thương Spectro, có thể tích lũy. Khi đạt tối đa, sử dụng Resonance Liberation sẽ tăng Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20182,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>KU-Raji từ Bờ Đen gửi lời nhắn tới cậu: Đài quan sát Spacetrek đã bị Void Storm phá hủy. Dù nó đóng vai trò then chốt trong việc lập bản đồ địa hình, hệ sinh thái và khí hậu của Lahai-Roi, việc tái thiết vẫn đang đình trệ…
+          <t>KU-Raji từ Bờ Đen gửi lời nhắn tới cậu: Đài quan sát Spacetrek đã bị Bão Hư Không phá hủy. Dù nó đóng vai trò then chốt trong việc lập bản đồ địa hình, hệ sinh thái và khí hậu của Lahai-Roi, việc tái thiết vẫn đang đình trệ…
 Giờ là lúc khôi phục vùng đất biên cương này. Hãy xây dựng lại mạng lưới tuyến đường của Lahai-Roi và hỗ trợ tái thiết Đài quan sát Spacetrek!</t>
         </is>
       </c>
@@ -20255,14 +20255,14 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Một cơ chế chiến đấu mới đã được thêm khi Resonators giao tranh với kẻ địch: Cơ chế Lệch Nhịp.
+          <t>Một cơ chế chiến đấu mới đã được thêm khi Resonator giao tranh với kẻ địch: Cơ chế Lệch Nhịp.
 Lệch Nhịp và Sai Nhịp
-Các đòn tấn công của Resonators sẽ tích lũy Mức Độ Lệch Nhịp của kẻ địch. Khi Mức Độ Lệch Nhịp của kẻ địch đạt đến giới hạn, chúng sẽ rơi vào trạng thái Sai Nhịp.
-Trong trạng thái Sai Nhịp, Resonators có thể tung ra một đòn Phá Nhịp mạnh mẽ, gây thêm sát thương. Thực hiện thành công Phá Nhịp sẽ đặt lại Mức Độ Lệch Nhịp của kẻ địch.
+Các đòn tấn công của Resonator sẽ tích lũy Mức Độ Lệch Nhịp của kẻ địch. Khi Mức Độ Lệch Nhịp của kẻ địch đạt đến giới hạn, chúng sẽ rơi vào trạng thái Sai Nhịp.
+Trong trạng thái Sai Nhịp, Resonator có thể tung ra một đòn Phá Nhịp mạnh mẽ, gây thêm sát thương. Thực hiện thành công Phá Nhịp sẽ đặt lại Mức Độ Lệch Nhịp của kẻ địch.
 Trong khoảng thời gian sau khi bị Phá Nhịp, Mức Độ Lệch Nhịp của kẻ địch không thể tích lũy lại.
 Phá Nhịp
-Đối với kẻ địch mạnh, khi Mức Độ Lệch Nhịp đầy, Resonators phải sử dụng kỹ năng Phá Nhịp để gây sát thương Phá Nhịp lên kẻ địch trong trạng thái Sai Nhịp.
-Kỹ năng Phá Nhịp gây sát thương lên kẻ địch, giảm Concerto Vibrancy của chúng, làm gián đoạn chuỗi tấn công và đặt lại Mức Độ Lệch Nhịp.</t>
+Đối với kẻ địch mạnh, khi Mức Độ Lệch Nhịp đầy, Resonator phải sử dụng kỹ năng Phá Nhịp để gây sát thương Phá Nhịp lên kẻ địch trong trạng thái Sai Nhịp.
+Kỹ năng Phá Nhịp gây sát thương lên kẻ địch, giảm Sức Mạnh Rung Động của chúng, làm gián đoạn chuỗi tấn công và đặt lại Mức Độ Lệch Nhịp.</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20327,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Chỉ hiển thị kẻ địch Cấp Đại Họa, Cấp Chúa Tể và Echo thôi.</t>
+          <t>Chỉ hiển thị kẻ địch Cấp Đại Họa, Cấp Chúa Tể và Tiếng Vọng thôi.</t>
         </is>
       </c>
     </row>
@@ -20392,7 +20392,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Phục hồi tần số để nhận</t>
+          <t>Khôi phục Tần số để nhận</t>
         </is>
       </c>
     </row>
@@ -20660,7 +20660,7 @@
       <c r="M306" t="inlineStr">
         <is>
           <t>Chỉ số Chiến Lực của ngươi càng cao so với kẻ địch, trận chiến càng dễ dàng.
-Độ hiếm của Hình Dán, Resonators, thẻ Namipon và bộ trang bị Namipon kích hoạt đều ảnh hưởng đến Chiến Lực của ngươi.</t>
+Độ hiếm của Hình Dán, Resonator, thẻ Namipon và bộ trang bị Namipon kích hoạt đều ảnh hưởng đến Chiến Lực của ngươi.</t>
         </is>
       </c>
     </row>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Con đường nối Hầm Gió Rít với Startorch Academy. Hư hại khiến đoạn dốc đứng gần như không thể vượt qua.</t>
+          <t>Con đường nối Hầm Gió Rít với Học viện Startorch. Hư hại khiến đoạn dốc đứng gần như không thể vượt qua.</t>
         </is>
       </c>
     </row>
@@ -20855,7 +20855,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Đánh dấu mục tiêu</t>
+          <t>Đánh Dấu Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -20922,8 +20922,8 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Intensity Dư Âm hiện tại: {0}
-Intensity Dư Âm tăng sau mỗi lần tiêu diệt kẻ địch, làm mạnh thêm sức tấn công của chúng.
+          <t>Cường độ Dư Âm hiện tại: {0}
+Cường độ Dư Âm tăng sau mỗi lần tiêu diệt kẻ địch, làm mạnh thêm sức tấn công của chúng.
 Mức độ kẻ địch hiện đã tăng thêm: {1}</t>
         </is>
       </c>
@@ -20989,7 +20989,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus gần Starward Riseway</t>
+          <t>Kích hoạt Mạch Cộng hưởng gần Starward Riseway</t>
         </is>
       </c>
     </row>
@@ -21054,7 +21054,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Tìm đến khu vực ẩn "Bjartr Woods" và kích hoạt Nexus Resonance</t>
+          <t>Tìm đến khu vực ẩn "Bjartr Woods" và kích hoạt Nexus Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Hẻm núi Fangspire để bắt đầu nhiệm vụ</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Hẻm núi Fangspire để bắt đầu nhiệm vụ</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Bjartr Woods để bắt đầu nhiệm vụ</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Bjartr Woods để bắt đầu nhiệm vụ</t>
         </is>
       </c>
     </row>
@@ -21249,7 +21249,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Stagnant Run để bắt đầu nhiệm vụ</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Stagnant Run để bắt đầu nhiệm vụ</t>
         </is>
       </c>
     </row>
@@ -21444,7 +21444,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt; kích hoạt Riot Blades.</t>
+          <t>&lt;color=Highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; kích hoạt Riot Blades.</t>
         </is>
       </c>
     </row>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Riot Blades hồi phục Resonance Energy.</t>
+          <t>Lưỡi Kiếm Bạo Loạn hồi phục Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Mid-air&lt;/color&gt; tăng 100%.</t>
+          <t>&lt;color=Highlight&gt;Crit. DMG Giữa Không&lt;/color&gt; tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Mid-air DMG&lt;/color&gt; tạo ra Nhân Data.</t>
+          <t>&lt;color=Highlight&gt;Sát Thương Giữa Không&lt;/color&gt; tạo ra Nhân Dữ Liệu.</t>
         </is>
       </c>
     </row>
@@ -21704,7 +21704,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ tăng Sát Thương Thuộc Tính Toàn Bộ.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; sẽ tăng Sát Thương Thuộc Tính Toàn Bộ.</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt; sẽ tạo ra Impulse Tide.</t>
+          <t>Gây &lt;color=Highlight&gt;Sát Thương Heavy Attack&lt;/color&gt; sẽ tạo ra Impulse Tide.</t>
         </is>
       </c>
     </row>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Cooldown chiêu của Impulse Tide đã giảm.</t>
+          <t>Thời gian hồi chiêu của Sóng Xung Kích đã giảm.</t>
         </is>
       </c>
     </row>
@@ -21899,7 +21899,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Tất cả sát thương Status Tiêu Cực được khuếch đại thêm 100%.</t>
+          <t>Tất cả DMG Trạng Thái Tiêu Cực được khuếch đại thêm 100%.</t>
         </is>
       </c>
     </row>
@@ -21964,7 +21964,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Tiêu diệt mục tiêu bị ảnh hưởng bởi &lt;color=Highlight&gt;Negative Statuses&lt;/color&gt; sẽ để lại Ceaseless Chant.</t>
+          <t>Tiêu diệt mục tiêu bị ảnh hưởng bởi &lt;color=Highlight&gt;Trạng Thái Tiêu Cực&lt;/color&gt; sẽ để lại Ceaseless Chant.</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Sát thương của Bài Thánh Ca Ceaseless tăng thêm 100%.</t>
+          <t>DMG của Bài Thánh Ca Vô Tận tăng thêm 100%.</t>
         </is>
       </c>
     </row>
@@ -22094,7 +22094,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; tăng Tấn Công.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -22159,7 +22159,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; phóng ra Móng Piercing Claw.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; phóng ra Móng Vuốt Xuyên Thấu.</t>
         </is>
       </c>
     </row>
@@ -22224,7 +22224,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Cooldown chiêu của &lt;color=Highlight&gt;Echo Skill&lt;/color&gt; giảm 85%.</t>
+          <t>Thời gian hồi chiêu của &lt;color=Highlight&gt;Kỹ Năng Echo&lt;/color&gt; giảm 85%.</t>
         </is>
       </c>
     </row>
@@ -22289,7 +22289,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Lồng Budget gây thêm sát thương khi hết hiệu lực.</t>
+          <t>Lồng Ngân Sách gây thêm sát thương khi hết hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -22354,7 +22354,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -22419,7 +22419,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -22493,11 +22493,11 @@
       <c r="M334" t="inlineStr">
         <is>
           <t>Giới thiệu
-Xung quanh một Quả Cầu Sonoro, bạn tình cờ gặp một nhà nghiên cứu đang gặp rắc rối, dường như anh ta đang gấp rút hoàn thành nhiệm vụ quan trọng...
+Xung quanh một Sonoro Sphere, bạn tình cờ gặp một nhà nghiên cứu đang gặp rắc rối, dường như anh ta đang gấp rút hoàn thành nhiệm vụ quan trọng...
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và mở khóa Resonance Nexus của Học Viện Startorch trong Nhiệm Vụ Chính "Lửa Cháy Dưới Băng Giá".
+Đạt Cấp Liên Minh 14 và mở khóa Mạng Lưới Cộng Hưởng của Học Viện Startorch trong Nhiệm Vụ Chính "Lửa Cháy Dưới Băng Giá".
 Quy tắc sự kiện
-1. Trong sự kiện, bạn sẽ bước vào một Quả Cầu Sonoro đặc biệt để chiến đấu với làn sóng kẻ địch trong thời gian giới hạn, với sự hỗ trợ của các hiệu ứng tăng cường độc đáo.
+1. Trong sự kiện, bạn sẽ bước vào một Sonoro Sphere đặc biệt để chiến đấu với làn sóng kẻ địch trong thời gian giới hạn, với sự hỗ trợ của các hiệu ứng tăng cường độc đáo.
 2. Bạn thu thập Xu bằng cách gây sát thương lên kẻ địch và mất Xu khi bị tấn công.
 3. Vượt qua các làn sóng kẻ địch sẽ mở khóa thêm nhiều hiệu ứng tăng cường đặc biệt để hỗ trợ bạn.
 4. Hoàn thành một làn sóng sẽ nhận được thêm thời gian. Số Xu bạn thu thập được khi hết giờ sẽ là thành tích của giai đoạn này.</t>
@@ -22567,8 +22567,8 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Khi một đơn vị đồng minh ở trong phạm vi 15m của kẻ địch Class Elite trong khu vực thi, Tấn Công của kẻ địch đó sẽ tăng 30% trong 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Khi một đơn vị đồng minh ở trong phạm vi 15m của kẻ địch Hạng Elite trong khu vực thi, ATK của kẻ địch đó sẽ tăng 30% trong 5 giây.
 Trước những vùng đất bí ẩn rộng lớn ở Lahai-Roi, Spacetrek Collective đã phát triển Spacetrek Explorer đa năng để phục vụ vận tải, lưu trữ và phòng thủ. Chân bánh xe và lốp chuyên dụng giúp nó di chuyển trên các bề mặt thẳng đứng, phù hợp cho cả địa hình đô thị lẫn địa hình gồ ghề. Các khoang chứa trên tàu được thiết kế để hỗ trợ các chuyến thám hiểm khoa học dài hạn.</t>
         </is>
       </c>
@@ -22636,8 +22636,8 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Khi một đơn vị đồng minh ở trong phạm vi 15m của kẻ địch Class Elite trong khu vực thi, Tấn Công của kẻ địch đó sẽ tăng 30% trong 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Khi một đơn vị đồng minh ở trong phạm vi 15m của kẻ địch Hạng Elite trong khu vực thi, ATK của kẻ địch đó sẽ tăng 30% trong 5 giây.
 Sau khi quét dữ liệu các loài động vật trước đây ở Lahai-Roi, Exostrider đã sử dụng chính các bộ phận của mình để phát triển và nhân bản những con tuần lộc cơ khí. Những Mining Reindeer này là bạn đồng hành của Roya và hỗ trợ Roya trong việc khai thác quặng.</t>
         </is>
       </c>
@@ -22705,8 +22705,8 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Khi có đơn vị đồng minh trong phạm vi 15m quanh kẻ địch Class Elite trong khu vực thi, sức tấn công của kẻ địch đó sẽ tăng 30% trong 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Khi có đơn vị đồng minh trong phạm vi 15m quanh kẻ địch Hạng Elite trong khu vực thi, sức tấn công của kẻ địch đó sẽ tăng 30% trong 5 giây.
 Sau khi quét dữ liệu của các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã dùng chính bộ phận của mình để nhân giống và phát triển loài bò xạ cơ khí. Nhờ lớp giáp cứng cáp giúp Ironhoof chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
       </c>
@@ -22775,10 +22775,10 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Khi một đơn vị đồng minh ở trong phạm vi 15m của kẻ địch Class Elite trong khu vực thi, Tấn Công của kẻ địch đó sẽ tăng 30% trong 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Khi một đơn vị đồng minh ở trong phạm vi 15m của kẻ địch Hạng Elite trong khu vực thi, ATK của kẻ địch đó sẽ tăng 30% trong 5 giây.
 Một TD canh giữ cao lớn. Dáng vẻ của nó giống như những tảng đá nguyên khối từ núi non.
-Dù trông như một pháo đài bất khả xâm phạm, bản chất của Guardian Đá Vững Chãi không phải là bảo vệ, mà là nghiền nát mọi chướng ngại cản bước tiến của nó.</t>
+Dù trông như một pháo đài bất khả xâm phạm, bản chất của Người Bảo Vệ Đá Vững Chãi không phải là bảo vệ, mà là nghiền nát mọi chướng ngại cản bước tiến của nó.</t>
         </is>
       </c>
     </row>
@@ -22845,8 +22845,8 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Khi có đơn vị đồng minh trong phạm vi 15m quanh kẻ địch Class Elite trong khu vực thi, sức tấn công của kẻ địch đó sẽ tăng 30% trong 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Khi có đơn vị đồng minh trong phạm vi 15m quanh kẻ địch Hạng Elite trong khu vực thi, sức tấn công của kẻ địch đó sẽ tăng 30% trong 5 giây.
 Cỗ máy săn mồi này chỉ có một mục đích duy nhất: xé nát mọi thứ trên đường đi. Nó rình rập khắp vùng hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào. Với tiếng gầm rít không ngừng của lưỡi cưa gắn đuôi, nó truy sát mục tiêu với hiệu quả tàn nhẫn.</t>
         </is>
       </c>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và chịu thêm 30% Sát Thương Echo.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và chịu thêm 30% Sát Thương Echo.
 Một Tacet Discord mạnh mẽ lang thang trên Central Plains. Với sự trợ giúp của bão sấm, nó tiếp tục nuốt chửng những âm thanh bảo vệ của con người. Được coi là tiên phong của Crownless.</t>
         </is>
       </c>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Resonance Regen</t>
+          <t>Hồi Phục Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -23109,7 +23109,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Resonance Regen: Zeal</t>
+          <t>Hồi Phục Cộng Hưởng: Nhiệt Huyết</t>
         </is>
       </c>
     </row>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Tấn Công tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;. Tăng Tune Break Boost thêm &lt;color=Highlight&gt;20&lt;/color&gt;.</t>
+          <t>ATK tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;. Tăng Tune Break Boost thêm &lt;color=Highlight&gt;20&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23239,7 +23239,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Concerto Energy phục hồi &lt;color=Highlight&gt;10&lt;/color&gt; điểm mỗi giây khi không chiến đấu.</t>
+          <t>Năng lượng Concerto phục hồi &lt;color=Highlight&gt;10&lt;/color&gt; điểm mỗi giây khi không chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -23304,7 +23304,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Tấn Công tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;.</t>
+          <t>ATK tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23499,7 +23499,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Dodge Phản Công và Phản Đòn gây thêm Sát Thương Physical tương đương với một lượng HP tối đa nhất định của mục tiêu.</t>
+          <t>Né Tránh Phản Công và Phản Đòn gây thêm Sát Thương Vật Lý tương đương với một lượng HP tối đa nhất định của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23629,7 +23629,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ tăng cấp GPA Tạm Thời.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ tăng cấp GPA Tạm Thời.</t>
         </is>
       </c>
     </row>
@@ -23759,7 +23759,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Phá Tune giảm Cooldown chiêu Resonance Liberation và cung cấp một lượng lớn Resonance Energy.</t>
+          <t>Kích hoạt Kỹ Năng Phá Điệu giảm Thời gian hồi chiêu Resonance Liberation và cung cấp một lượng lớn Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -23889,7 +23889,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Đòn tấn công có xác suất gây Status Tiêu Cực khi trúng đích. Sát Thương sẽ được Khuếch Đại theo từng lớp Status Tiêu Cực.</t>
+          <t>Đòn tấn công có xác suất gây Trạng Thái Tiêu Cực khi trúng đích. Sát Thương sẽ được Khuếch Đại theo từng lớp Trạng Thái Tiêu Cực.</t>
         </is>
       </c>
     </row>
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tấn Công tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;. Tăng Tune Break Boost thêm &lt;color=Highlight&gt;20&lt;/color&gt;.</t>
+          <t>ATK tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;. Tăng Tune Break Boost thêm &lt;color=Highlight&gt;20&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24019,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Concerto Energy phục hồi &lt;color=Highlight&gt;10&lt;/color&gt; điểm mỗi giây khi không chiến đấu.</t>
+          <t>Năng lượng Concerto phục hồi &lt;color=Highlight&gt;10&lt;/color&gt; điểm mỗi giây khi không chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Tấn Công tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;.</t>
+          <t>ATK tăng &lt;color=Highlight&gt;7,5%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24280,8 +24280,8 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Dodge Counter gây Physical DMG bằng &lt;color=Highlight&gt;1%&lt;/color&gt; HP tối đa của mục tiêu. Đánh trúng mục tiêu bằng Counterattack gây Physical DMG bằng &lt;color=Highlight&gt;5%&lt;/color&gt; HP tối đa của mục tiêu.
-Cả hai hiệu ứng có thể được kích hoạt &lt;color=Highlight&gt;once&lt;/color&gt; mỗi &lt;color=Highlight&gt;3s&lt;/color&gt;. DMG gây lên mục tiêu có khiên tăng gấp đôi.</t>
+          <t>Dodge Counter trúng mục tiêu sẽ gây Sát Thương Vật Lý bằng &lt;color=Highlight&gt;1%&lt;/color&gt; HP tối đa của mục tiêu. Phản Đòn trúng mục tiêu sẽ gây Sát Thương Vật Lý bằng &lt;color=Highlight&gt;5%&lt;/color&gt; HP tối đa của mục tiêu.
+Cả hai hiệu ứng đều có thể kích hoạt &lt;color=Highlight&gt;mỗi 3 giây một lần&lt;/color&gt;. DMG gây lên mục tiêu có Khiên sẽ tăng gấp đôi.</t>
         </is>
       </c>
     </row>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ tăng &lt;color=Highlight&gt;5&lt;/color&gt; cấp GPA Tạm Thời, kích hoạt &lt;color=Highlight&gt;once&lt;/color&gt; &lt;color=Highlight&gt;20s&lt;/color&gt; một lần.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ tăng &lt;color=Highlight&gt;5&lt;/color&gt; cấp GPA Tạm Thời, kích hoạt &lt;color=Highlight&gt;mỗi&lt;/color&gt; &lt;color=Highlight&gt;20 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -24541,7 +24541,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Phá Tune giảm Cooldown chiêu Resonance Liberation xuống &lt;color=Highlight&gt;50%&lt;/color&gt; và cung cấp &lt;color=Highlight&gt;50%&lt;/color&gt; Resonance Energy. Hiệu ứng này chỉ kích hoạt &lt;color=Highlight&gt;once&lt;/color&gt; &lt;color=Highlight&gt;20s&lt;/color&gt; một lần.</t>
+          <t>Kích hoạt Kỹ Năng Phá Điệu giảm Thời gian hồi chiêu Resonance Liberation xuống &lt;color=Highlight&gt;50%&lt;/color&gt; và cung cấp &lt;color=Highlight&gt;50%&lt;/color&gt; Resonance Energy. Hiệu ứng này chỉ kích hoạt &lt;color=Highlight&gt;mỗi&lt;/color&gt; &lt;color=Highlight&gt;20 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -24671,7 +24671,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Các đòn tấn công của cậu có xác suất gây &lt;color=Highlight&gt;1&lt;/color&gt; tầng hiệu ứng Fusion Burst, Aero Erosion, Spectro Frazzle, Electro Flare hoặc Havoc Bane khi trúng mục tiêu. Hiệu ứng này chỉ kích hoạt &lt;color=Highlight&gt;once&lt;/color&gt; mỗi &lt;color=Highlight&gt;0.5s&lt;/color&gt;. Mỗi tầng Status Tiêu Cực trên mục tiêu sẽ tăng &lt;color=Highlight&gt;1%&lt;/color&gt; DMG Amplification cho cậu trong &lt;color=Highlight&gt;4s&lt;/color&gt;, tối đa &lt;color=Highlight&gt;30&lt;/color&gt; tầng.</t>
+          <t>Các đòn tấn công của cậu có xác suất gây &lt;color=Highlight&gt;1&lt;/color&gt; tầng hiệu ứng Fusion Burst, Aero Erosion, Spectro Frazzle, Electro Flare hoặc Havoc Bane khi trúng mục tiêu. Hiệu ứng này chỉ kích hoạt &lt;color=Highlight&gt;một lần&lt;/color&gt; mỗi &lt;color=Highlight&gt;0.5 giây&lt;/color&gt;. Mỗi tầng Trạng Thái Tiêu Cực trên mục tiêu sẽ tăng &lt;color=Highlight&gt;1%&lt;/color&gt; Khuếch Đại Sát Thương cho cậu trong &lt;color=Highlight&gt;4 giây&lt;/color&gt;, tối đa &lt;color=Highlight&gt;30&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -24801,7 +24801,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Phá Tune gây Sát Thương bằng &lt;color=Highlight&gt;5%&lt;/color&gt; HP tối đa của mục tiêu, kích hoạt &lt;color=Highlight&gt;once&lt;/color&gt; &lt;color=Highlight&gt;20s&lt;/color&gt; một lần.</t>
+          <t>Kích hoạt Kỹ Năng Phá Điệu gây Sát Thương bằng &lt;color=Highlight&gt;5%&lt;/color&gt; HP tối đa của mục tiêu, kích hoạt &lt;color=Highlight&gt;mỗi&lt;/color&gt; &lt;color=Highlight&gt;20 giây&lt;/color&gt; một lần.</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Dodge Counter giảm &lt;color=Highlight&gt;5%&lt;/color&gt; Vibration Strength của mục tiêu khi trúng đích. Counterattack thêm sẽ giảm tiếp &lt;color=Highlight&gt;12.5%&lt;/color&gt; Vibration Strength khi trúng. Cả hai hiệu ứng chỉ kích hoạt &lt;color=Highlight&gt;once&lt;/color&gt; mỗi &lt;color=Highlight&gt;3s&lt;/color&gt;.</t>
+          <t>Dodge Counter giảm &lt;color=Highlight&gt;5%&lt;/color&gt; Sức Rung của mục tiêu khi trúng đích. Phản công thêm sẽ giảm tiếp &lt;color=Highlight&gt;12.5%&lt;/color&gt; Sức Rung khi trúng. Cả hai hiệu ứng chỉ kích hoạt &lt;color=Highlight&gt;một lần&lt;/color&gt; mỗi &lt;color=Highlight&gt;3 giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24996,7 +24996,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Cooldown kỹ năng Cộng hưởng giảm &lt;color=Highlight&gt;50%&lt;/color&gt;.</t>
+          <t>Thời gian hồi kỹ năng Cộng hưởng giảm &lt;color=Highlight&gt;50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25061,7 +25061,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Tune Break Boost được tăng thêm &lt;color=Highlight&gt;100&lt;/color&gt;. Sử dụng Skill Tune Break sẽ tiêu hao &lt;color=Highlight&gt;20&lt;/color&gt; cấp GPA Tạm thời.</t>
+          <t>Tăng cường Đột phá Điệu nhạc được tăng thêm &lt;color=Highlight&gt;100&lt;/color&gt;. Sử dụng Kỹ năng Đột phá Điệu nhạc sẽ tiêu hao &lt;color=Highlight&gt;20&lt;/color&gt; cấp GPA Tạm thời.</t>
         </is>
       </c>
     </row>
@@ -25126,7 +25126,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội nhận được &lt;color=Highlight&gt;100%&lt;/color&gt; Healing thêm. Khi Cấp Độ GPA Tạm Thời không dưới &lt;color=Highlight&gt;50&lt;/color&gt;, Resonators sẽ trụ lại với &lt;color=Highlight&gt;1&lt;/color&gt; HP khi nhận đòn chí mạng. Hiệu ứng này chỉ kích hoạt &lt;color=Highlight&gt;once&lt;/color&gt; mỗi kỳ thi.</t>
+          <t>Tất cả Resonator trong đội nhận được &lt;color=Highlight&gt;100%&lt;/color&gt; Hồi Phục thêm. Khi Cấp Độ GPA Tạm Thời không dưới &lt;color=Highlight&gt;50&lt;/color&gt;, Resonator sẽ trụ lại với &lt;color=Highlight&gt;1&lt;/color&gt; HP khi nhận đòn chí mạng. Hiệu ứng này chỉ kích hoạt &lt;color=Highlight&gt;một lần&lt;/color&gt; mỗi kỳ thi.</t>
         </is>
       </c>
     </row>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Total Tăng Crit. DMG tăng &lt;color=Highlight&gt;30%&lt;/color&gt;. Tăng Sát Thương Kỹ Năng Echo bằng &lt;color=Highlight&gt;150%&lt;/color&gt; lượng Tăng Crit. DMG.</t>
+          <t>Tổng Tăng Crit. DMG tăng &lt;color=Highlight&gt;30%&lt;/color&gt;. Tăng Sát Thương Kỹ Năng Echo bằng &lt;color=Highlight&gt;150%&lt;/color&gt; lượng Tăng Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -25386,7 +25386,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Total Tăng Sát Thương Tất Cả Thuộc Tính tăng &lt;color=Highlight&gt;30%&lt;/color&gt;.</t>
+          <t>Tổng Tăng Sát Thương Tất Cả Thuộc Tính tăng &lt;color=Highlight&gt;30%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25470,20 +25470,20 @@
           <t>Về sự kiện
 Tại buổi Triển lãm &amp; Trình diễn Câu lạc bộ năm nay, Van Tassie từ Hiệp hội Trị liệu Tâm lý Ngưỡng Tâm lý Thay thế tự hào giới thiệu dự án mới nhất của mình: "Mô phỏng Tối ưu Hóa N.L.N" (F.U.E.L.). Ông tuyên bố trò chơi này sẽ cách mạng hóa trải nghiệm ẩm thực của Học viện bằng cách thu thập những dữ liệu thiết yếu. Như thường lệ, tên của cậu đã có trong danh sách thử nghiệm. Thế nhưng, ngay từ đầu, thiết kế cốt lõi của dự án này đã có gì đó... hơi lệch lạc.
 Điều kiện tham gia
-Đạt Cấp Liên minh 14 và kích hoạt Points Cộng hưởng tại Startorch Academy trong Nhiệm vụ Main "Điều Gì Nung Nấu Dưới Lãnh Nguyên" để mở khóa.
+Đạt Cấp Liên minh 14 và kích hoạt Điểm Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên" để mở khóa.
 (Lưu ý: Hoàn thành "Vàng Đọng Trong Bóng Tối" để có trải nghiệm chơi tốt hơn.)
 Quy tắc
 1. Cách chơi
-Truy cập sự kiện từ máy Mind Dive Arcade hoặc trang Event. Điều khiển Resonator của cậu di chuyển trái phải để bắt thức ăn rơi xuống và kiếm Gourmet Points.
-2. Năng lượng &amp; Skills
-Bắt thức ăn để tích lũy Năng lượng. Khi thanh Năng lượng đầy, cậu có thể kích hoạt Skills Resonance mạnh mẽ.
+Truy cập sự kiện từ máy Mind Dive Arcade hoặc trang Sự kiện. Điều khiển Resonator của cậu di chuyển trái phải để bắt thức ăn rơi xuống và kiếm Điểm Ẩm Thực.
+2. Năng lượng &amp; Kỹ năng
+Bắt thức ăn để tích lũy Năng lượng. Khi thanh Năng lượng đầy, cậu có thể kích hoạt Kỹ năng Cộng Hưởng mạnh mẽ.
 Cẩn thận—bắt phải một số loại thức ăn tiêu cực sẽ làm cậu mất Năng lượng và di chuyển chậm lại.
 3. Hoàn thành giai đoạn
-Đạt số Gourmet Points mục tiêu để nhận 1 Sao và hoàn thành giai đoạn. Nếu thoát giữa chừng, giai đoạn này sẽ được xác nhận dựa trên số Gourmet Points đã kiếm được.
-4. Unlock giai đoạn
+Đạt số Điểm Ẩm Thực mục tiêu để nhận 1 Sao và hoàn thành giai đoạn. Nếu thoát giữa chừng, giai đoạn này sẽ được xác nhận dựa trên số Điểm Ẩm Thực đã kiếm được.
+4. Mở khóa giai đoạn
 Giai đoạn 1 sẽ mở khi sự kiện bắt đầu. Mỗi ngày tiếp theo sẽ mở khóa một giai đoạn mới, mỗi giai đoạn có một Resonator mới với kỹ năng độc đáo.
-5. Rewards
-Nếu còn phần thưởng chưa nhận khi sự kiện kết thúc, cậu có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua Mail.</t>
+5. Phần thưởng
+Nếu còn phần thưởng chưa nhận khi sự kiện kết thúc, cậu có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua Thư.</t>
         </is>
       </c>
     </row>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Startorch Academy và Bộ tộc Roya đã hợp tác thiết lập căn cứ tại Dimmr Plains, khởi động chuyến thám hiểm khoa học chung vào vùng đất cô lập từ lâu này. Mục tiêu bao gồm thu thập dữ liệu môi trường, phục hồi mẫu thực vật cổ đại và linh kiện Exostrider, cũng như khắc phục thiệt hại môi trường do Void Storm gây ra. Thành quả của chiến dịch này sẽ thúc đẩy đáng kể nghiên cứu sinh thái và phục hồi môi trường sống tại Lahai-Roi.
+          <t>Học viện Startorch và Bộ tộc Roya đã hợp tác thiết lập căn cứ tại Đồng bằng Dimmr, khởi động chuyến thám hiểm khoa học chung vào vùng đất cô lập từ lâu này. Mục tiêu bao gồm thu thập dữ liệu môi trường, phục hồi mẫu thực vật cổ đại và linh kiện Exostrider, cũng như khắc phục thiệt hại môi trường do Bão Hư Không gây ra. Thành quả của chiến dịch này sẽ thúc đẩy đáng kể nghiên cứu sinh thái và phục hồi môi trường sống tại Lahai-Roi.
 Cậu nhận được tin nhắn từ I.R.I.S., mời tham gia chuyến thám hiểm đầu tiên...</t>
         </is>
       </c>
@@ -25685,8 +25685,8 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Summon Sigillum tấn công kẻ địch, gây Fusion DMG.
-Khi Aemeath trang bị ở vị trí chính, cộng thêm Tăng Sát Thương Giải Phóng Echo.</t>
+          <t>Triệu hồi Sigillum tấn công kẻ địch, gây Sát Thương Fusion.
+Khi Aemeath trang bị ở vị trí chính, cộng thêm Tăng Sát Thương Giải Phóng Tiếng Vang.</t>
         </is>
       </c>
     </row>
@@ -25752,8 +25752,8 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Summon Nameless Explorer tấn công kẻ địch, gây Aero DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ gây thêm Aero DMG và Sát Thương Kỹ Năng Echo.</t>
+          <t>Triệu hồi Nhà Thám Hiểm Vô Danh tấn công kẻ địch, gây Sát Thương Aero.
+Resonator trang bị Echo này ở vị trí chính sẽ gây thêm Sát Thương Aero và Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Tăng Fusion DMG</t>
+          <t>Sát Thương Hợp Thể +</t>
         </is>
       </c>
     </row>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Gây Nổ Nhiệt Hạch hoặc Tune Rupture - Shifting lên kẻ địch sẽ tăng Crit. Rate và Sát Thương Nhiệt Hạch của Resonator.</t>
+          <t>Gây Fusion Burst hoặc Đứt Giai Điệu - Dịch Chuyển lên kẻ địch sẽ tăng Crit. Rate và Sát Thương Nhiệt Hạch của Resonator.</t>
         </is>
       </c>
     </row>
@@ -25948,7 +25948,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Tăng Fusion DMG</t>
+          <t>Sát Thương Hợp Thể +</t>
         </is>
       </c>
     </row>
@@ -26013,7 +26013,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Gây Nổ Nhiệt Hạch sẽ tăng thưởng Sát Thương Nhiệt Hạch. Trong thời gian này, sử dụng Outro Skill sẽ trao thưởng Sát Thương Nhiệt Hạch cho Resonator tiếp theo.</t>
+          <t>Gây Fusion Burst sẽ tăng thưởng Sát Thương Nhiệt Hạch. Trong thời gian này, sử dụng Kỹ Năng Outro sẽ trao thưởng Sát Thương Nhiệt Hạch cho Resonator tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -26078,7 +26078,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Aero DMG +</t>
+          <t>DMG Aero +</t>
         </is>
       </c>
     </row>
@@ -26143,7 +26143,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Echo sẽ tăng Crit. Rate của Kỹ Năng Echo và tăng thêm Aero DMG.</t>
+          <t>Gây DMG bằng Kỹ Năng Echo sẽ tăng Crit. Rate của Kỹ Năng Echo và tăng thêm Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -26273,7 +26273,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Kẻ địch: Nameless Explorer</t>
+          <t>Kẻ địch: Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
     </row>
@@ -26340,8 +26340,8 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Cao gây Fusion DMG bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không cộng dồn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Cao gây Sát Thương Fusion bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không cộng dồn.
 Sau khi quét dữ liệu của các loài động vật trước đây ở Lahai-Roi, Exostrider đã sử dụng các bộ phận của chính mình để phát triển và nhân bản những con tuần lộc cơ khí. Những Flora Reindeer này là bạn đồng hành của Roya và hỗ trợ Roya trong việc tìm kiếm thực vật.</t>
         </is>
       </c>
@@ -26409,8 +26409,8 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao gây Fusion DMG bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao gây Sát Thương Fusion bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
 Sau khi quét dữ liệu các loài động vật trước đây ở Lahai-Roi, Exostrider đã dùng chính bộ phận của mình để phát triển và nhân bản những con tuần lộc cơ khí. Những Mining Reindeer này là bạn đồng hành của Roya và hỗ trợ Roya khai thác quặng.</t>
         </is>
       </c>
@@ -26478,8 +26478,8 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao gây Fusion DMG bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao gây Sát Thương Fusion bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã sử dụng chính bộ phận của mình để nhân giống và phát triển loài bò xạ cơ khí. Nhờ lớp giáp cứng cáp giúp Ironhoof chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
       </c>
@@ -26548,9 +26548,9 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao Elite gây Fusion DMG bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu gần đó. Hiệu ứng này không chồng chất.
-Một Echo bảo vệ cao lớn. Dáng vẻ của nó giống như những tảng đá nguyên khối từ núi non.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao Elite gây Sát Thương Fusion bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu gần đó. Hiệu ứng này không chồng chất.
+Một Tổ Tacet bảo vệ cao lớn. Dáng vẻ của nó giống như những tảng đá nguyên khối từ núi non.
 Dù trông như một pháo đài bất khả xâm phạm, bản chất của Rocksteady Guardian không phải để bảo vệ, mà là để nghiền nát mọi chướng ngại vật cản đường tiến của nó.</t>
         </is>
       </c>
@@ -26618,8 +26618,8 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao gây Fusion DMG bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao gây Sát Thương Fusion bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
 Cặp mech Twin Nova được chế tạo để thám hiểm bên ngoài Stridergate. Nebulous Cannon là phiên bản tầm xa. Hình dáng người của chúng thể hiện khát vọng khám phá vực thẳm của nhân loại khi ngước nhìn bầu trời sao. Khi kết hợp, cặp Twin Nova thể hiện năng lực chiến đấu chưa từng có.</t>
         </is>
       </c>
@@ -26687,9 +26687,9 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao gây Fusion DMG bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
-Một Echo hình người sử dụng sức mạnh bằng cách chơi nhạc cụ. Bắt chước hành vi đánh chuông và cầu nguyện của con người, nhưng những lời nó thốt ra không phải là phước lành, mà là lời nguyền rủa.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao gây Sát Thương Fusion bằng 2% HP tối đa của mục tiêu mỗi giây lên các mục tiêu xung quanh. Hiệu ứng này không chồng chất.
+Một Tổ Tacet hình người sử dụng sức mạnh bằng cách chơi nhạc cụ. Bắt chước hành vi đánh chuông và cầu nguyện của con người, nhưng những lời nó thốt ra không phải là phước lành, mà là lời nguyền rủa.</t>
         </is>
       </c>
     </row>
@@ -26756,7 +26756,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và chịu thêm 30% Sát Thương từ Heavy Attack.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và chịu thêm 30% Sát Thương từ Đòn Heavy Attack.
 Một "tay đua" lửa sinh ra ở Thành phố Cảng Guixu. Nó đặt ra những thử thách dũng cảm bằng ngọn lửa bất khuất cho những kẻ dám xâm phạm.
 Qua bao năm tháng, sự thật lịch sử dần cháy thành tro, và hiệp sĩ từng hát vang bài ca tử thần giờ đây trở thành điềm báo sợ hãi trong lời đồn đại của loài người.</t>
         </is>
@@ -26825,8 +26825,8 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây DMG bằng 100% ATK của chúng.
 Một sinh vật ký sinh sống bên trong Whisperin Tacet Discord, sử dụng cơ thể vật chủ như kén và hấp thụ tần số của nó. Nhiễm Windlash Coleoid khiến vật chủ trở nên hung hãn và thôi thúc chúng hấp thụ tần số của các Tacet Discord khác. Sau thời gian ủ bệnh, Windlash Coleoid sẽ rời khỏi vật chủ bằng cách phá vỡ lưng vật chủ.</t>
         </is>
       </c>
@@ -26894,8 +26894,8 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây DMG bằng 100% ATK của chúng.
 Cỗ máy săn mồi này chỉ có một mục đích duy nhất: xé nát mọi thứ trên đường đi. Nó rình rập khắp vùng hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào. Với tiếng gầm rít không ngừng của lưỡi cưa đuôi, nó truy sát mục tiêu với hiệu quả tàn nhẫn.</t>
         </is>
       </c>
@@ -26963,8 +26963,8 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây DMG bằng 100% ATK của chúng.
 Một sinh vật ký sinh sống bên trong các Tacet Discord Whisperin, sử dụng cơ thể vật chủ như kén và hấp thụ tần số của nó. Nhiễm Frostbite Coleoid khiến vật chủ trở nên hung hãn và thôi thúc chúng đi hấp thụ tần số của các Tacet Discord khác. Sau thời gian ủ bệnh, Frostbite Coleoid sẽ rời khỏi vật chủ bằng cách phá vỡ lưng nó để thoát ra.</t>
         </is>
       </c>
@@ -27032,8 +27032,8 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây DMG bằng 100% ATK của chúng.
 Trước những vùng đất bí ẩn rộng lớn của Lahai-Roi, Spacetrek Collective đã phát triển Spacetrek Explorer đa năng để phục vụ vận tải, lưu trữ và phòng thủ. Với chân bánh xe và lốp chịu lực, nó có thể di chuyển trên cả bề mặt thẳng đứng, phù hợp cho cả địa hình đô thị lẫn hoang dã. Các khoang chứa trên tàu được thiết kế để hỗ trợ các chuyến thám hiểm khoa học dài hạn.</t>
         </is>
       </c>
@@ -27103,10 +27103,10 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây DMG bằng 100% ATK của chúng.
 Một tác phẩm quý giá của Fractsidus.
-Bằng công nghệ của New Federation, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
+Bằng công nghệ của Liên Bang Mới, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Tacet Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
 Nhưng mọi sự siêu việt đều phải trả giá. Những kẻ đón nhận sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái xác rỗng tuếch.</t>
         </is>
       </c>
@@ -27175,10 +27175,10 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Trong khu vực thi, kẻ địch bị đánh bại sẽ phát nổ, gây DMG bằng 100% ATK của chúng.
 Một TD canh giữ cao lớn. Dáng vẻ của nó giống như một tảng đá khổng lồ từ vực thẳm sâu thẳm.
-Dù trông như một pháo đài bất khả xâm phạm, bản chất của Guardian Vực Nứt không phải để bảo vệ, mà là để nghiền nát mọi chướng ngại vật cản đường tiến của nó.</t>
+Dù trông như một pháo đài bất khả xâm phạm, bản chất của Người Bảo Vệ Vực Nứt không phải để bảo vệ, mà là để nghiền nát mọi chướng ngại vật cản đường tiến của nó.</t>
         </is>
       </c>
     </row>
@@ -27248,8 +27248,8 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch bị tiêu diệt sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, kẻ địch bị tiêu diệt sẽ phát nổ, gây DMG bằng 100% ATK của chúng.
 Một Exoswarm mạnh mẽ giống loài mãnh thú săn mồi cổ đại, Kronaclaw.
 Xưa kia, những con mãnh thú này từng thống trị bầu trời Lahai-Roi, vương quyền bất khả xâm phạm kể từ Kỷ Nguyên Đầu Tiên.
 Truyền thuyết kể rằng Kronaclaw là tạo vật của Sol, chia sẻ thị lực thần thánh từ Con Mắt Sol, nhìn thấu vạn vật trên và dưới Lahai-Roi.
@@ -27321,7 +27321,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, chịu ít Sát Thương Thuộc Tính hơn (không kích hoạt khi bị bất động hoặc dính Tune Break), và chịu nhiều Sát Thương Tune Break hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;, chịu ít Sát Thương Thuộc Tính hơn (không kích hoạt khi bị bất động hoặc dính Tune Break), và chịu nhiều Sát Thương Tune Break hơn.
 Được tạo ra trong phòng thí nghiệm CSC, Tacet Discord Cơ Khí này đã tiến hóa bằng cách nuốt chửng xác máy móc.
 Khi phát hiện dấu vết tần số con người, nó trở nên ám ảnh với việc đạt đến sự hoàn hảo và ngày càng lớn mạnh khi cải thiện cấu trúc của mình.
 Một biểu tượng ám ảnh về sự theo đuổi không ngừng của nhân loại trong tiến bộ khoa học, sự hiện diện của nó như lời nhắc nhở tinh tế về nỗi ám ảnh và sự sa đọa vào điên loạn của chúng ta.</t>
@@ -27391,7 +27391,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Trong khu vực thi, khi một kẻ địch chết, nó sẽ hồi 20% HP cho các đơn vị đồng minh xung quanh.
 Sau khi quét dữ liệu về các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã sử dụng chính các bộ phận của mình để nhân giống và phát triển loài bò xạ cơ học. Nhờ lớp giáp cứng cáp của Ironhoof giúp chúng chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
@@ -27462,7 +27462,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Trong khu vực thi, khi kẻ địch chết, nó sẽ hồi 20% HP cho các đơn vị đồng minh xung quanh.
 Những tín đồ trung thành của Fractsidus.
 Thiếu đi Forte nhưng lại khao khát quyền lực mãnh liệt, chúng đã vượt qua những giới hạn khoa học cấm kỵ. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, cơ thể con người của chúng được kết hợp với các chi của TD, từ đó có được khả năng tàng hình.
@@ -27533,7 +27533,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Trong khu vực thi, khi một kẻ địch chết, nó sẽ hồi 20% HP cho các đơn vị đồng minh xung quanh.
 Cỗ máy săn mồi này chỉ có một mục đích duy nhất: xé nát mọi thứ trên đường đi. Nó rình rập trong hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào. Với tiếng gầm rít không ngừng của lưỡi cưa đuôi, nó truy sát mục tiêu với hiệu quả tàn nhẫn.</t>
         </is>
@@ -27602,7 +27602,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Trong khu vực thi, khi một kẻ địch bị tiêu diệt, nó sẽ hồi 20% HP cho các đơn vị đồng minh xung quanh.
 Trong bầy Exoswarm, không có kẻ nào cao lớn hay được tôn kính hơn những cá thể khổng lồ này. Được tạo hình giống loài voi ma mút đã tuyệt chủng từ lâu, chúng được xem là những người dẫn đường đáng tin cậy, dẫn dắt đồng loại trở về với Exostrider.</t>
         </is>
@@ -27671,7 +27671,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
 Trong khu vực thi, khi kẻ địch bị tiêu diệt, nó sẽ hồi phục 20% HP cho đồng minh xung quanh.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã dùng chính bộ phận của mình để nhân bản và phát triển những chú tuần lộc cơ khí. Những chú Mining Reindeer này là bạn đồng hành của Roya và hỗ trợ chúng khai thác quặng.</t>
         </is>
@@ -27743,7 +27743,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Trong khu vực thi, khi một kẻ địch bị tiêu diệt, nó sẽ hồi phục 20% HP cho các đơn vị đồng minh xung quanh.
 Một loài mãnh long cổ đại đã tuyệt chủng được tái sinh thông qua Upphaf Life Chamber.
 Trong quá khứ xa xưa, những con mãnh long này từng thống trị bầu trời Lahai-Roi, vương quyền của chúng không bị thách thức kể từ Kỷ Nguyên Đầu Tiên.
@@ -27817,10 +27817,10 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Trong khu vực thi, khi kẻ địch chết, nó sẽ hồi 20% HP cho các đơn vị đồng minh xung quanh.
 Một tác phẩm quý giá của Fractsidus.
-Bằng công nghệ của New Federation, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
+Bằng công nghệ của Liên Bang Mới, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Tacet Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
 Nhưng mọi sự siêu việt đều phải trả giá. Những kẻ đón nhận sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái xác rỗng tuếch.</t>
         </is>
       </c>
@@ -27889,7 +27889,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và có thể gây Glacio Chafe lên mục tiêu khi tấn công. Resonators có thể loại bỏ và gây lại Glacio Chafe khi áp dụng Status Tiêu Cực lên kẻ địch.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và có thể gây Glacio Chafe lên mục tiêu khi tấn công. Resonator có thể loại bỏ và gây lại Glacio Chafe khi áp dụng Trạng Thái Tiêu Cực lên kẻ địch.
 Một cỗ máy chiến đấu chính xác và mạnh mẽ được cải tiến bằng công nghệ đặc biệt. Nó thực hiện mệnh lệnh của chủ nhân với lòng trung thành tuyệt đối.
 Mọi dấu vết về hình dáng ban đầu đều đã phai mờ, chỉ còn lại bản năng chiến đấu được mài giũa tinh tế trong tần số của nó. Là một vệ sĩ bất khuất, nó thích nghi hoàn hảo với mọi loại hình chiến đấu. Khi cần, nó kích hoạt một bộ phận đặc biệt để tăng cường khả năng di chuyển hoặc giải phóng toàn bộ năng lượng trong một vụ nổ hủy diệt.
 Gia tộc Montelli, những kẻ du hành từ phương xa, đã chứng kiến một thế giới rộng lớn hơn—và họ sẵn sàng trả bất cứ giá nào để có được sức mạnh cần thiết hồi sinh quê hương.</t>
@@ -27959,7 +27959,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28026,8 +28026,8 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, khi kẻ địch chịu sát thương vượt quá 25% HP tối đa trong 1 giây, nó sẽ đẩy lùi mục tiêu xung quanh và gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, khi kẻ địch chịu DMG vượt quá 25% HP tối đa trong 1 giây, nó sẽ đẩy lùi mục tiêu xung quanh và gây DMG bằng 100% ATK.
 Trước những vùng đất bí ẩn rộng lớn của Lahai-Roi, Spacetrek Collective đã phát triển Spacetrek Explorer đa năng để phục vụ vận tải, lưu trữ và phòng thủ. Với chân bánh xe và lốp chịu lực, nó có thể di chuyển trên cả bề mặt thẳng đứng, phù hợp cho cả địa hình đô thị lẫn hoang dã. Các khoang chứa trên tàu được thiết kế để hỗ trợ các chuyến thám hiểm khoa học dài hạn.</t>
         </is>
       </c>
@@ -28098,8 +28098,8 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Trong khu vực thi, khi kẻ địch chịu sát thương vượt quá 25% HP tối đa trong 1 giây, nó sẽ đẩy lùi các mục tiêu xung quanh và gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Trong khu vực thi, khi kẻ địch chịu DMG vượt quá 25% HP tối đa trong 1 giây, nó sẽ đẩy lùi các mục tiêu xung quanh và gây DMG bằng 100% ATK.
 Một sản phẩm của Fractsidus. Một thất bại lỗi bị vứt bỏ vào bóng tối.
 Niềm vui và nỗi buồn, tiếng cười và tiếng khóc... Tất cả những cảm xúc cuối cùng rồi cũng sẽ tìm thấy nấm mồ của mình ở đâu đó, khắc sâu những vết sẹo trong bóng tối.
 Làm sao để thoát khỏi cái bóng của chính mình? Làm sao để đối diện với những gì mình đã trở thành?
@@ -28172,7 +28172,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28240,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28307,8 +28307,8 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Trong khu vực thi, khi kẻ địch chịu sát thương vượt quá 25% HP tối đa trong vòng 1 giây, nó sẽ đẩy lùi các mục tiêu xung quanh và gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, khi kẻ địch chịu DMG vượt quá 25% HP tối đa trong vòng 1 giây, nó sẽ đẩy lùi các mục tiêu xung quanh và gây DMG bằng 100% ATK.
 Trong bầy Exoswarm, không có kẻ nào cao lớn hay được tôn kính hơn những cá thể khổng lồ này. Được tạo hình giống loài voi ma mút đã tuyệt chủng từ lâu, chúng được xem là những người dẫn đường đáng tin cậy, dẫn dắt đồng loại trở về với Exostrider.</t>
         </is>
       </c>
@@ -28376,8 +28376,8 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khu vực thi, khi kẻ địch chịu sát thương vượt quá 25% HP tối đa trong vòng 1 giây, nó sẽ đẩy lùi các mục tiêu xung quanh và gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Trong khu vực thi, khi kẻ địch chịu DMG vượt quá 25% HP tối đa trong vòng 1 giây, nó sẽ đẩy lùi các mục tiêu xung quanh và gây DMG bằng 100% ATK.
 Sau khi quét dữ liệu về các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã sử dụng chính các bộ phận của mình để nhân giống và phát triển loài bò xạ cơ học. Nhờ lớp giáp cứng cáp của Ironhoof giúp chúng chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
       </c>
@@ -28446,7 +28446,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;, và định kỳ tạo ra một ma trận kiếm có thể hút và gây sát thương cho Resonators gần đó.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;, và định kỳ tạo ra một ma trận kiếm có thể hút và gây DMG cho các Resonator gần đó.
 Hyvatia là hệ thống dò tìm đầu tiên của Spacetrek Collective được xây dựng tại Sundermere để giám sát và ổn định trạng thái năng lượng của Reactor Drive theo thời gian thực.
 Viện Nghiên Cứu đã cấy mô-đun hiệu chỉnh lỗi không-thời gian của Exostrider vào lõi của Hyvatia, cho phép nó điều chỉnh quỹ đạo của Exostrider và phát hiện các mối đe dọa ẩn nấp trong không gian với độ chính xác cao. Do đó, Hyvatia sở hữu đủ sức mạnh tính toán để dự đoán vòng quay của Reactor Drive.
 Chức năng cốt lõi của Hyvatia là phát hiện các dao động năng lượng bất thường hoặc nguy hiểm, thực hiện hiệu chỉnh khẩn cấp ngay lập tức, và truyền dữ liệu này về Drive để đảm bảo hoạt động ổn định.</t>
@@ -28516,7 +28516,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Trong khu vực thi, kẻ địch miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã sử dụng chính bộ phận của mình để nhân giống và phát triển loài bò xạ cơ khí. Nhờ lớp giáp cứng cáp giúp Ironhoof chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
@@ -28585,7 +28585,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Trong khu vực thi, kẻ địch sẽ miễn nhiễm với hiệu ứng gián đoạn khi HP còn trên 50%.
 Sau khi quét dữ liệu của các loài động vật từng tồn tại ở Lahai-Roi, Exostrider đã sử dụng chính các bộ phận của mình để phát triển và nhân bản những con tuần lộc cơ khí. Những Flora Reindeer này là bạn đồng hành của Roya và hỗ trợ Roya trong việc tìm kiếm thực vật.</t>
         </is>
@@ -28656,10 +28656,10 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Trong khu vực thi, kẻ địch miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
 Một tác phẩm quý giá của Fractsidus.
-Bằng công nghệ của New Federation, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
+Bằng công nghệ của Liên Bang Mới, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Tacet Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
 Nhưng mọi sự siêu việt đều phải trả giá. Những kẻ đón nhận sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái xác rỗng tuếch.</t>
         </is>
       </c>
@@ -28730,7 +28730,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
 Trong khu vực thi, kẻ địch miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
 Một Exoswarm mạnh mẽ giống loài mãnh thú săn mồi cổ đại - Kronaclaw.
 Trong quá khứ xa xưa, những con mãnh thú này từng thống trị bầu trời Lahai-Roi, vương quyền bất khả xâm phạm kể từ Kỷ Nguyên Đầu Tiên.
@@ -28802,7 +28802,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
 Trong khu vực thi, kẻ địch miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
 Bộ đôi mech Twin Nova được chế tạo để thám hiểm bên ngoài Stridergate. Collapsar Blade là phiên bản cận chiến. Hình dáng người của chúng thể hiện khát vọng khám phá vực thẳm của nhân loại khi ngước nhìn bầu trời. Khi kết hợp, cặp Twin Nova thể hiện sức mạnh chiến đấu chưa từng có.</t>
         </is>
@@ -28871,7 +28871,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Trong khu vực thi, kẻ địch sẽ miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
 Trong bầy Exoswarm, không có kẻ nào cao lớn hay được tôn kính hơn những cá thể khổng lồ này. Được tạo hình giống loài voi ma mút đã tuyệt chủng từ lâu, chúng được xem là những người dẫn đường đáng tin cậy, dẫn dắt đồng loại trở về với Exostrider.</t>
         </is>
@@ -28940,7 +28940,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Trong khu vực thi, kẻ địch miễn nhiễm với hiệu ứng gián đoạn khi HP trên 50%.
 Cỗ máy săn mồi này chỉ có một mục đích duy nhất: xé nát mọi thứ trên đường đi. Nó rình rập khắp vùng hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào. Với tiếng gầm rít không ngừng của lưỡi cưa đuôi, nó truy sát mục tiêu với hiệu quả tàn nhẫn.</t>
         </is>
@@ -29011,8 +29011,8 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và định kỳ phóng ra vụ nổ dung nham gây Fusion DMG.
-Phản đòn Dodge của Resonators có hiệu quả tăng cường trong việc giảm Vibration Strength của mục tiêu.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và định kỳ phóng ra vụ nổ dung nham gây Sát Thương Fusion.
+Phản đòn Né Tránh của Resonator có hiệu quả tăng cường trong việc giảm Vibration Strength của mục tiêu.
 Sau khi Reactor Drive được Exostrider thiết lập phía trên Lahai-Roi, nó vẫn luôn cảnh giác cao độ với các hoạt động của Aleph-1.
 Khi phản ứng miễn dịch của Drive được kích hoạt, một "Reactor Husk" cơ khí sẽ trỗi dậy từ lòng giếng năng lượng, với mục đích duy nhất là tiêu diệt kẻ xâm nhập bằng mọi giá.
 Nghiên cứu của Spacetrek Collective cho thấy Reactor Husk từng là một phần của Exostrider. Cả hai đều chung sứ mệnh chống lại mối đe dọa Threnodian và bảo vệ nền văn minh.</t>
@@ -29082,8 +29082,8 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
 Cặp mech Twin Nova được chế tạo để khám phá bên ngoài Stridergate. Collapsar Blade là phiên bản cận chiến. Hình dáng người máy của chúng thể hiện khát vọng vươn tới vực thẳm vũ trụ của nhân loại khi ngước nhìn bầu trời sao.
 Khi kết hợp, cặp Twin Nova sẽ phát huy sức mạnh chiến đấu vượt trội chưa từng có.</t>
         </is>
@@ -29152,7 +29152,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
 Trong khu vực thi, kẻ địch Elite Class sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
 Trước những vùng đất bí ẩn rộng lớn ở Lahai-Roi, Spacetrek Collective đã phát triển Spacetrek Explorer đa năng để phục vụ vận tải, lưu trữ và phòng thủ. Chân bánh xe và lốp chịu lực giúp nó di chuyển trên các bề mặt thẳng đứng, phù hợp cho cả địa hình đô thị lẫn địa hình gồ ghề. Các khoang chứa trên tàu được thiết kế để hỗ trợ các chuyến thám hiểm khoa học dài hạn.</t>
         </is>
@@ -29221,8 +29221,8 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Cấp Elite sẽ tạo khiên cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Cấp Tinh Anh sẽ tạo khiên cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây.
 Trong bầy Exoswarm, không ai cao lớn hay được tôn kính hơn những cá thể khổng lồ này. Được tạo hình theo loài voi ma mút đã tuyệt chủng, chúng được coi là người dẫn đường đáng tin cậy, dẫn dắt đồng loại trở về Exostrider.</t>
         </is>
       </c>
@@ -29292,10 +29292,10 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
 Một kiệt tác của Fractsidus.
-Bằng công nghệ của New Federation, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Discord, tạo ra một cỗ máy cưa khủng khiếp có thể xé nát thép và nghiền nát con mồi thành bụi.
+Bằng công nghệ của Liên Bang Mới, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của Tacet Discord, tạo ra một cỗ máy cưa khủng khiếp có thể xé nát thép và nghiền nát con mồi thành bụi.
 Nhưng mọi sự vượt trội đều phải trả giá. Những kẻ ôm ấp sản phẩm này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái vỏ rỗng tuếch.</t>
         </is>
       </c>
@@ -29364,9 +29364,9 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
-Một Echo bảo vệ cao lớn. Dáng vẻ của nó giống như một tảng đá khổng lồ từ vực thẳm sâu thẳm.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
+Một Tổ Tacet bảo vệ cao lớn. Dáng vẻ của nó giống như một tảng đá khổng lồ từ vực thẳm sâu thẳm.
 Dù trông như một pháo đài bất khả xâm phạm, bản chất của Chasm Guardian không phải để bảo vệ, mà là nghiền nát bất cứ vật cản nào chặn đường tiến của nó.</t>
         </is>
       </c>
@@ -29437,8 +29437,8 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây.
 Một sản phẩm của Fractsidus. Một thất bại bị vứt bỏ vào bóng tối.
 Niềm vui và nỗi buồn, tiếng cười và nước mắt... Tất cả cảm xúc rồi cũng sẽ chôn vùi nơi nào đó, để lại những vết sẹo trong bóng tối.
 Làm sao để thoát khỏi cái bóng của chính mình? Làm sao đối diện với những gì mình đã trở thành?
@@ -29512,8 +29512,8 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây.
 Một Exoswarm mạnh mẽ giống loài mãnh thú săn mồi cổ đại, Kronaclaw.
 Xưa kia, những con mãnh thú này từng thống trị bầu trời Lahai-Roi, vương quyền bất khả xâm phạm kể từ Kỷ Nguyên Đầu Tiên.
 Truyền thuyết kể rằng Kronaclaw là tạo vật của Sol, chia sẻ thị lực thần thánh từ Con Mắt Sol, nhìn thấu vạn vật trên và dưới Lahai-Roi.
@@ -29587,8 +29587,8 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Aero DMG&lt;/color&gt;&lt;/color&gt; cao hơn.
-Resonators sẽ nhận được Shield khi kỹ năng Tune Break đánh trúng kẻ địch.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;&lt;/color&gt; cao hơn.
+Resonator sẽ nhận được Khiên khi kỹ năng Phá Tần đánh trúng kẻ địch.
 Trạm nghiên cứu sụp đổ như một ngôi sao đang tàn, chôn vùi giấc mơ của một thời đại dưới băng và đất.
 Nhà Thám Hiểm là một trong những kẻ từng mơ mộng, từng đi giữa các vì sao.
 Nhưng giờ đây, hắn trốn trong bóng tối, bị Hư Không tha hóa.
@@ -29722,7 +29722,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Phá Tune gây Sát Thương dựa trên HP tối đa của mục tiêu.</t>
+          <t>Kích hoạt Kỹ Năng Phá Điệu gây Sát Thương dựa trên HP tối đa của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -29852,7 +29852,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Dodge Phản Công và Phản Đòn làm giảm Concerto Vibrancy của mục tiêu.</t>
+          <t>Né Tránh Phản Công và Phản Đòn làm giảm Sức Mạnh Rung Động của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Cooldown kỹ năng Cộng hưởng giảm &lt;color=Highlight&gt;50%&lt;/color&gt;.</t>
+          <t>Thời gian hồi kỹ năng Cộng hưởng giảm &lt;color=Highlight&gt;50%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29982,7 +29982,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Tune Break Boost được tăng thêm &lt;color=Highlight&gt;100&lt;/color&gt;. Sử dụng Skill Tune Break sẽ tiêu hao &lt;color=Highlight&gt;20&lt;/color&gt; cấp GPA Tạm thời.</t>
+          <t>Tăng cường Đột phá Điệu nhạc được tăng thêm &lt;color=Highlight&gt;100&lt;/color&gt;. Sử dụng Kỹ năng Đột phá Điệu nhạc sẽ tiêu hao &lt;color=Highlight&gt;20&lt;/color&gt; cấp GPA Tạm thời.</t>
         </is>
       </c>
     </row>
@@ -30047,7 +30047,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội nhận được Healing tăng thêm 100%. Khi Cấp Độ GPA Tạm Thời không dưới 50, Resonators sẽ trụ lại với 1 HP khi nhận đòn chí mạng. Hiệu ứng này chỉ kích hoạt một lần mỗi hiệp.</t>
+          <t>Tất cả Resonator trong đội nhận được Hồi Phục tăng thêm 100%. Khi Cấp Độ GPA Tạm Thời không dưới 50, Resonator sẽ trụ lại với 1 HP khi nhận đòn chí mạng. Hiệu ứng này chỉ kích hoạt một lần mỗi hiệp.</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Total Tăng Crit. DMG tăng 30%. Tăng Sát Thương Kỹ Năng Echo bằng 150% lượng Tăng Crit. DMG.</t>
+          <t>Tổng Tăng Crit. DMG tăng 30%. Tăng Sát Thương Kỹ Năng Echo bằng 150% lượng Tăng Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -30307,7 +30307,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Total Tăng Sát Thương Tất Cả Thuộc Tính tăng &lt;color=Highlight&gt;30%&lt;/color&gt;.</t>
+          <t>Tổng Tăng Sát Thương Tất Cả Thuộc Tính tăng &lt;color=Highlight&gt;30%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -30372,7 +30372,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Tổng quan Buff</t>
+          <t>Tổng quan Hiệu ứng</t>
         </is>
       </c>
     </row>
@@ -30502,7 +30502,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tổng quan Buff</t>
+          <t>Tổng quan Hiệu ứng</t>
         </is>
       </c>
     </row>
@@ -30587,18 +30587,18 @@
 09/05/2026 04:00 – 25/05/2026 03:59 (giờ máy chủ)
 *Từ 09/05/2026 08:00 đến 23/05/2026 19:30 (giờ máy chủ), bạn có thể ủng hộ Cubie yêu thích mỗi ngày. Từ 23/05/2026 20:30 đến 25/05/2026 03:59 (giờ máy chủ), chức năng ủng hộ sẽ tạm đóng. Trong thời gian này, bạn có thể xem kết quả cuộc đua, kiểm tra Bảng Bảo Trợ, xem lại các trận đấu và nhận thưởng sự kiện.
 [Giới Thiệu]
-Mùa giải mới của Cubie Derby trở lại nhân dịp Anniversary 2 năm Sự Trở Lại của Solaris! Hãy đến xem trận đấu và ủng hộ Cubie của bạn!
+Mùa giải mới của Cubie Derby trở lại nhân dịp Kỷ niệm 2 năm Sự Trở Lại của Solaris! Hãy đến xem trận đấu và ủng hộ Cubie của bạn!
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 8.
 [Thể Lệ]
-1. Trong sự kiện, 18 Cubie sẽ tham gia thi đấu theo 3 Bảng. Không tính trận Chung Kết, mỗi ngày sẽ có 1 trận đấu, tổng cộng 14 trận để tìm ra Nhà Vô Địch Cuộc Race.
+1. Trong sự kiện, 18 Cubie sẽ tham gia thi đấu theo 3 Bảng. Không tính trận Chung Kết, mỗi ngày sẽ có 1 trận đấu, tổng cộng 14 trận để tìm ra Nhà Vô Địch Cuộc Đua.
 2. Toàn bộ giải đấu gồm 3 Giai Đoạn: Vòng Loại, Vòng Loại Trực Tiếp và Chung Kết. Thời gian cụ thể vui lòng xem lịch sự kiện.
 3. Từ khi trận đấu trước kết thúc đến 30 phút trước khi trận đấu tiếp theo bắt đầu (20:30 giờ máy chủ), bạn có thể ủng hộ Cubie yêu thích bằng cách dự đoán Đội Thắng của trận đấu hôm đó.
 4. Trận đấu trong ngày bắt đầu lúc 21:00 giờ máy chủ. Từ trang sự kiện, bạn có thể xem trực tiếp cuộc đua và cổ vũ cho Cubie yêu thích trong khung chat trực tuyến.
 5. Sau trận đấu, bạn sẽ nhận được phần thưởng Độ Nổi Tiếng dựa trên thứ hạng cuối cùng của các Cubie và kết quả dự đoán.
 6. Bảng Bảo Trợ sẽ mở lúc 04:00 giờ máy chủ vào ngày sau trận Vòng Loại B - 2, và sau đó sẽ được cập nhật vào 04:00 ngày hôm sau sau mỗi trận đấu. Bạn có thể xem thứ hạng của mình trên Bảng Bảo Trợ.
-7. Sau Chung Kết, một vật phẩm kỷ niệm sẽ được gửi đến tất cả Rover đã mở khóa sự kiện này. Hãy nhận thưởng kịp thời trước khi sự kiện kết thúc.
-8. Mọi phần thưởng chưa nhận sẽ được gửi lại qua Mail trong game khi bạn đăng nhập trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
+7. Sau Chung Kết, một vật phẩm kỷ niệm sẽ được gửi đến tất cả Vận Mệnh Giả đã mở khóa sự kiện này. Hãy nhận thưởng kịp thời trước khi sự kiện kết thúc.
+8. Mọi phần thưởng chưa nhận sẽ được gửi lại qua Thư trong game khi bạn đăng nhập trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
         </is>
       </c>
     </row>
@@ -30728,7 +30728,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch Round 3 của Singularity Expansion trong Endstate Matrix</t>
+          <t>Đánh bại kẻ địch Vòng 3 của Mở Rộng Điểm Kỳ Dị trong Ma Trận Tận Thế</t>
         </is>
       </c>
     </row>
@@ -30793,7 +30793,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Hiện tại, mỗi cấp độ tăng thêm +{0} Tấn Công, +{1} HP tối đa và +{2} Phòng Ngự.</t>
+          <t>Hiện tại, mỗi cấp độ tăng thêm +{0} ATK, +{1} HP tối đa và +{2} Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -30860,8 +30860,8 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Cao sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho các đơn vị đồng minh gần đó và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Cao sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho các đơn vị đồng minh gần đó và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Sau khi quét dữ liệu của các loài động vật trước đây ở Lahai-Roi, Exostrider đã sử dụng các bộ phận của chính mình để phát triển và nhân bản những con tuần lộc cơ khí. Những Flora Reindeer này là bạn đồng hành của Roya và hỗ trợ Roya trong việc tìm kiếm thực vật.</t>
         </is>
       </c>
@@ -30929,8 +30929,8 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi phục 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi phục 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã dùng chính bộ phận của mình để nhân bản và phát triển những chú tuần lộc cơ khí. Những chú Mining Reindeer này là bạn đồng hành của Roya và hỗ trợ chúng khai thác quặng.</t>
         </is>
       </c>
@@ -30998,8 +30998,8 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã sử dụng chính bộ phận của mình để nhân giống và phát triển loài bò xạ cơ khí. Nhờ lớp giáp cứng cáp giúp Ironhoof chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
       </c>
@@ -31068,9 +31068,9 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Lớp Elite sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng phục hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
-Một Echo hộ pháp cao lớn. Dáng vẻ của nó giống như những tảng đá nguyên khối trên núi.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Lớp Tinh Anh sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng phục hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
+Một Tổ Tacet hộ pháp cao lớn. Dáng vẻ của nó giống như những tảng đá nguyên khối trên núi.
 Dù trông như một pháo đài bất khả xâm phạm, bản chất của Rocksteady Guardian không phải để bảo vệ, mà là để nghiền nát bất cứ vật cản nào chặn đường tiến của nó.</t>
         </is>
       </c>
@@ -31138,8 +31138,8 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích nổ, gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích nổ, gây DMG bằng 100% ATK.
 Cặp mech Twin Nova được chế tạo để thám hiểm bên ngoài Stridergate. Collapsar Blade là phiên bản cận chiến. Hình dáng người của chúng thể hiện khát vọng khám phá vực thẳm của nhân loại khi ngước nhìn bầu trời sao. Khi kết hợp, cặp Twin Nova thể hiện sức mạnh chiến đấu chưa từng có.</t>
         </is>
       </c>
@@ -31207,9 +31207,9 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
-Một Echo hình người, sử dụng sức mạnh bằng cách chơi nhạc cụ. Bắt chước hành vi gõ chuông và cầu nguyện của con người, nhưng những lời nó thốt ra không phải lời chúc phúc, mà là lời nguyền rủa.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
+Một Tổ Tacet hình người, sử dụng sức mạnh bằng cách chơi nhạc cụ. Bắt chước hành vi gõ chuông và cầu nguyện của con người, nhưng những lời nó thốt ra không phải lời chúc phúc, mà là lời nguyền rủa.</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Kẻ địch này cứ mỗi 8 giây lại phóng một luồng dung nham gây Fusion DMG. Dodge Counter của Resonators sẽ hiệu quả hơn trong việc giảm Vibration Strength của nó.
+          <t>Kẻ địch này cứ mỗi 8 giây lại phóng một luồng dung nham gây Sát Thương Fusion. Dodge Counter của Resonator sẽ hiệu quả hơn trong việc giảm Độ Rung của nó.
 Sau khi Reactor Drive được Exostrider đặt lên Lahai-Roi, nó luôn ở trạng thái cảnh giác cao độ trước các hoạt động của Aleph-1.
 Khi phản ứng miễn dịch của Drive được kích hoạt, một "Reactor Husk" cơ khí sẽ trỗi dậy từ vực sâu của giếng năng lượng, với mục đích duy nhất là tiêu diệt kẻ xâm nhập bằng mọi giá.
 Nghiên cứu của Spacetrek Collective cho thấy Reactor Husk từng là một phần của Exostrider. Cả hai đều có chung sứ mệnh chống lại mối đe dọa Threnodian và bảo vệ nền văn minh.</t>
@@ -31347,8 +31347,8 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Cao sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho các đơn vị đồng minh gần đó và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Cao sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho các đơn vị đồng minh gần đó và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Một sinh vật ký sinh sống bên trong Whisperin Tacet Discord, sử dụng cơ thể vật chủ như kén và hấp thụ tần số của nó. Nhiễm Windlash Coleoid khiến vật chủ trở nên hung hãn và thôi thúc chúng hấp thụ tần số của các Tacet Discord khác. Sau thời gian ủ bệnh, Windlash Coleoid sẽ rời khỏi vật chủ bằng cách phá vỡ lưng vật chủ.</t>
         </is>
       </c>
@@ -31416,8 +31416,8 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Cỗ máy săn mồi này chỉ có một mục đích duy nhất: xé nát mọi thứ trên đường đi. Nó rình rập khắp vùng hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào. Với tiếng gầm rít không ngừng của lưỡi cưa đuôi, nó truy sát mục tiêu với hiệu quả tàn nhẫn.</t>
         </is>
       </c>
@@ -31485,8 +31485,8 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Cấp Elite sẽ tạo khiên cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Cấp Tinh Anh sẽ tạo khiên cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Một sinh vật ký sinh sống bên trong Tacet Discord Whisperin, dùng cơ thể vật chủ như kén và hấp thụ tần số của nó. Nhiễm Băng Giá Coleoid khiến vật chủ trở nên hung hãn và thôi thúc chúng hấp thụ tần số của các Tacet Discord khác. Sau thời gian ủ bệnh, Băng Giá Coleoid sẽ rời khỏi vật chủ bằng cách phá vỡ lưng nó.</t>
         </is>
       </c>
@@ -31554,8 +31554,8 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi phục 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi phục 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Trước những vùng đất bí ẩn rộng lớn ở Lahai-Roi, Spacetrek Collective đã phát triển Spacetrek Explorer đa năng để phục vụ vận tải, lưu trữ và phòng thủ. Chân bánh xe và lốp chịu lực giúp nó di chuyển trên các bề mặt thẳng đứng, phù hợp cho cả địa hình đô thị lẫn hoang dã. Các khoang chứa trên tàu được thiết kế để hỗ trợ các chuyến thám hiểm khoa học dài hạn.</t>
         </is>
       </c>
@@ -31625,10 +31625,10 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Một tác phẩm quý giá của Fractsidus.
-Kết hợp công nghệ New Federation, chúng đã hợp nhất chiếc mũ hình ảnh với bản chất của Discord, tạo ra một cỗ máy cưa khủng khiếp có thể xé nát thép và nghiền con mồi thành tro bụi.
+Kết hợp công nghệ Liên Bang Mới, chúng đã hợp nhất chiếc mũ hình ảnh với bản chất của Tacet Discord, tạo ra một cỗ máy cưa khủng khiếp có thể xé nát thép và nghiền con mồi thành tro bụi.
 Nhưng mọi sự vượt trội đều phải trả giá. Những kẻ đón nhận sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái xác rỗng tuếch.</t>
         </is>
       </c>
@@ -31697,9 +31697,9 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
-Một Echo bảo vệ cao lớn. Dáng vẻ của nó giống như một tảng đá khổng lồ từ vực thẳm sâu thẳm.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
+Một Tổ Tacet bảo vệ cao lớn. Dáng vẻ của nó giống như một tảng đá khổng lồ từ vực thẳm sâu thẳm.
 Dù trông như một pháo đài bất khả xâm phạm, bản chất của Chasm Guardian không phải để bảo vệ, mà là nghiền nát bất cứ vật cản nào chặn đường tiến của nó.</t>
         </is>
       </c>
@@ -31770,8 +31770,8 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích nổ, gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích nổ, gây DMG bằng 100% ATK.
 Một Exoswarm mạnh mẽ giống loài mãnh thú săn mồi cổ đại, Kronaclaw.
 Xưa kia, những con mãnh thú này từng thống trị bầu trời Lahai-Roi, vương quyền bất khả xâm phạm kể từ Kỷ Nguyên Đầu Tiên.
 Truyền thuyết kể rằng Kronaclaw là tạo vật của Sol, chia sẻ thị lực thần thánh từ Con Mắt Sol, nhìn thấu vạn vật trên và dưới Lahai-Roi.
@@ -31843,7 +31843,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Kẻ địch này định kỳ tạo ra một ma trận kiếm có thể hút và gây sát thương cho Resonators gần đó.
+          <t>Kẻ địch này định kỳ tạo ra một ma trận kiếm có thể hút và gây sát thương cho các Resonator gần đó.
 Hyvatia là ma trận dò tìm đầu tiên của Spacetrek Collective, được xây dựng tại Sundermere để giám sát và ổn định trạng thái năng lượng của Reactor Drive theo thời gian thực.
 Viện Nghiên Cứu đã cấy mô-đun hiệu chỉnh lỗi không-thời gian của Exostrider vào lõi của Hyvatia, cho phép nó điều chỉnh quỹ đạo của Exostrider và phát hiện các mối đe dọa ẩn trong không gian với độ chính xác cao. Do đó, Hyvatia có đủ năng lực tính toán để dự đoán vòng quay của Reactor Drive.
 Chức năng cốt lõi của Hyvatia là phát hiện các dao động năng lượng bất thường hoặc nguy hiểm, thực hiện hiệu chỉnh khẩn cấp ngay lập tức và truyền dữ liệu này về Drive để đảm bảo hoạt động ổn định.</t>
@@ -31913,8 +31913,8 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã sử dụng chính bộ phận của mình để nhân giống và phát triển loài bò xạ cơ khí. Nhờ lớp giáp cứng cáp giúp Ironhoof chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
       </c>
@@ -31984,11 +31984,11 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Class Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Hạng Đặc Biệt sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Những tín đồ trung thành của Fractsidus.
-Thiếu đi Forte nhưng khao khát sức mạnh mãnh liệt, chúng đã vượt qua những giới hạn khoa học bị cấm. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, cơ thể người của chúng được kết hợp với chi của Echo, từ đó có khả năng tàng hình.
-Tuy nhiên, tần số của Echo bóp méo tinh thần và ăn mòn cơ thể của tín đồ. Những Đao Phủ có nhiệm vụ loại bỏ các thành viên Fractsidus vi phạm quy tắc hoặc mất kiểm soát.</t>
+Thiếu đi Forte nhưng khao khát sức mạnh mãnh liệt, chúng đã vượt qua những giới hạn khoa học bị cấm. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, cơ thể người của chúng được kết hợp với chi của Tổ Tacet, từ đó có khả năng tàng hình.
+Tuy nhiên, tần số của Tổ Tacet bóp méo tinh thần và ăn mòn cơ thể của tín đồ. Những Đao Phủ có nhiệm vụ loại bỏ các thành viên Fractsidus vi phạm quy tắc hoặc mất kiểm soát.</t>
         </is>
       </c>
     </row>
@@ -32055,8 +32055,8 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Mục tiêu này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Mục tiêu này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Cao sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Cỗ máy săn mồi này chỉ có một mục đích duy nhất: xé nát mọi thứ trên đường đi. Nó rình rập khắp vùng hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào. Với tiếng gầm rít không ngừng của lưỡi cưa đuôi, nó truy sát mục tiêu với hiệu quả tàn nhẫn.</t>
         </is>
       </c>
@@ -32124,8 +32124,8 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
-Trong khu vực thi, kẻ địch Cấp Elite sẽ tạo khiên cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
+Trong khu vực thi, kẻ địch Cấp Tinh Anh sẽ tạo khiên cho tất cả đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Trong bầy Exoswarm, không ai cao lớn hay được tôn kính hơn những cá thể khổng lồ này. Được tạo hình theo loài voi ma mút đã tuyệt chủng, chúng được coi là người dẫn đường đáng tin cậy, dẫn dắt đồng loại trở về Exostrider.</t>
         </is>
       </c>
@@ -32193,8 +32193,8 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Trong khu vực thi, kẻ địch Class Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi phục 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Trong khu vực thi, kẻ địch Hạng Elite sẽ tạo lá chắn cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi bị tiêu diệt, chúng hồi phục 20% HP cho đồng minh xung quanh và kích hoạt vụ nổ gây DMG bằng 100% ATK.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã dùng chính bộ phận của mình để nhân bản và phát triển những chú tuần lộc cơ khí. Những chú Mining Reindeer này là bạn đồng hành của Roya và hỗ trợ chúng khai thác quặng.</t>
         </is>
       </c>
@@ -32265,8 +32265,8 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Areo DMG&lt;/color&gt;. 
-Trong khu vực thi, kẻ địch Class Elite sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh gần đó và kích hoạt vụ nổ gây sát thương bằng 100% Tấn Công. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng cao&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. 
+Trong khu vực thi, kẻ địch Hạng Elite sẽ tạo khiên cho tất cả đơn vị đồng minh trong phạm vi 15m mỗi 5 giây. Khi chết, chúng hồi 20% HP cho đồng minh gần đó và kích hoạt vụ nổ gây DMG bằng 100% ATK. 
 Một loài raptor cổ đại đã tuyệt chủng, được tái sinh từ Upphaf Life Chamber. 
 Trong quá khứ xa xôi, những con raptor này từng thống trị bầu trời Lahai-Roi, vương quyền không ai sánh kể từ Kỷ Nguyên Đầu Tiên. 
 Truyền thuyết kể rằng Kronaclaw là tạo vật của Sol, mang trong mình thị lực thần thánh của Mắt Sol, nhìn thấu tất cả trên và dưới Lahai-Roi. 
@@ -32338,9 +32338,9 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; trước &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; trước &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một tác phẩm quý giá của Fractsidus.
-Sử dụng công nghệ của New Federation, chúng đã hợp nhất chiếc mũ hình ảnh với bản chất của một Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
+Sử dụng công nghệ của New Federation, chúng đã hợp nhất chiếc mũ hình ảnh với bản chất của một Tacet Discord, tạo ra một cỗ máy cưa xích kinh hoàng có thể xé nát thép và nghiền nát con mồi thành tro bụi.
 Nhưng mọi sự siêu việt đều phải trả giá. Những kẻ đón nhận sáng tạo này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái xác rỗng tuếch.</t>
         </is>
       </c>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Resonators nhận Shield khi Kỹ Năng Phá Giai đả trúng kẻ địch.
+          <t>Resonator nhận Khiên khi Kỹ Năng Phá Giai đả trúng kẻ địch.
 Trạm vũ trụ rơi như một ngôi sao đang tắt, chôn vùi giấc mơ của thời đại dưới lớp băng và đất.
 Nhà Thám Hiểm là một trong những kẻ mộng mơ, từng sải bước giữa các vì sao.
 Nhưng giờ đây, hắn ẩn mình trong bóng tối, bị Hư Không tha hóa.
@@ -32479,7 +32479,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Khi Cấp Độ Giao Hưởng đạt A trở lên, sát thương Dodge Counter tăng {0}%.</t>
+          <t>Khi Cấp Độ Giao Hưởng đạt A trở lên, DMG Dodge Counter Tránh tăng {0}%.</t>
         </is>
       </c>
     </row>
@@ -32544,7 +32544,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Khi Cấp Độ Giao Hưởng đạt S trở lên, Dodge Counter giảm toàn bộ Cooldown chiêu của Kỹ Năng đi {0}.</t>
+          <t>Khi Cấp Độ Giao Hưởng đạt S trở lên, Dodge Counter Tránh giảm toàn bộ Cooldown chiêu của Kỹ Năng đi {0}.</t>
         </is>
       </c>
     </row>
@@ -32674,7 +32674,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Kẻ địch gây thêm {0}% DMG.</t>
+          <t>Kẻ địch gây &lt;color=#b72924ff&gt;DMG tăng thêm {0}%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32739,7 +32739,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Kẻ địch gây thêm {0}% DMG.</t>
+          <t>Kẻ địch gây &lt;color=#b72924ff&gt;DMG tăng thêm {0}%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32804,7 +32804,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Kẻ địch gây thêm {0}% DMG.</t>
+          <t>Kẻ địch gây &lt;color=#b72924ff&gt;DMG tăng thêm {0}%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32869,7 +32869,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Kẻ địch gây thêm {0}% DMG.</t>
+          <t>Kẻ địch gây &lt;color=#b72924ff&gt;DMG tăng thêm {0}%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận một Lớp Shield tương đương {0}% HP tối đa.</t>
+          <t>Kẻ địch nhận một Lớp Khiên tương đương {0}% HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -32999,7 +32999,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận một Lớp Shield tương đương {0}% HP tối đa.</t>
+          <t>Kẻ địch nhận một Lớp Khiên tương đương {0}% HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -33064,7 +33064,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận một Lớp Shield tương đương {0}% HP tối đa.</t>
+          <t>Kẻ địch nhận một Lớp Khiên tương đương {0}% HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -33129,7 +33129,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Kẻ địch nhận một Lớp Shield tương đương {0}% HP tối đa.</t>
+          <t>Kẻ địch nhận một Lớp Khiên tương đương {0}% HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -33389,7 +33389,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Khi Cấp Độ Giao Hưởng dưới A, Resonators gây sát thương giảm {0}%.</t>
+          <t>Khi Cấp Độ Giao Hưởng dưới A, Resonator gây DMG giảm {0}%.</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>HP tối đa trở thành {0}, và khiên nhận được giảm {1}%. Ở cấp Độ Hòa Âm SS, Resonators không thể bị hạ gục và HP sẽ không giảm dưới {2}.</t>
+          <t>HP tối đa trở thành {0}, và khiên nhận được giảm {1}%. Ở cấp Độ Hòa Âm SS, Resonator không thể bị hạ gục và HP sẽ không giảm dưới {2}.</t>
         </is>
       </c>
     </row>
@@ -33584,7 +33584,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>&lt;color=#f05454&gt;Kẻ địch gây nhiều hơn {0}% DMG.&lt;/color&gt;</t>
+          <t>&lt;color=#f05454&gt;Kẻ địch gây thêm {0}% Sát Thương.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33649,7 +33649,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>&lt;color=#f05454&gt;Kẻ địch nhận Khiên tương đương {0}% HP Tối Đa.&lt;/color&gt;</t>
+          <t>&lt;color=#f05454&gt;Kẻ địch nhận Khiên tương đương {0}% HP tối đa.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33779,7 +33779,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>&lt;color=#a754f0&gt;Tốc độ phục hồi STA giảm {0}%&lt;/color&gt;</t>
+          <t>&lt;color=#a754f0&gt;Tốc độ hồi phục STA giảm {0}%&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -33844,7 +33844,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>&lt;color=#f0c154&gt;Resonator gây ít DMG hơn ở cấp Symphony thấp.&lt;/color&gt;</t>
+          <t>&lt;color=#f0c154&gt;Resonator gây ít DMG hơn khi Cấp Giao Hưởng thấp.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
